--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ28"/>
+  <dimension ref="A1:AQ30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0664</v>
+        <v>0.0578</v>
       </c>
       <c r="E2">
-        <v>0.0737</v>
+        <v>0.05299999999999999</v>
       </c>
       <c r="F2">
-        <v>0.132</v>
+        <v>-0.03490000000000001</v>
       </c>
       <c r="G2">
-        <v>0.1242374061106294</v>
+        <v>0.3541512049331756</v>
       </c>
       <c r="H2">
-        <v>0.1231889824276416</v>
+        <v>0.3226027763920116</v>
       </c>
       <c r="I2">
-        <v>0.1307339251443035</v>
+        <v>0.05897801368576295</v>
       </c>
       <c r="J2">
-        <v>0.1086842858817035</v>
+        <v>0.05296300614496161</v>
       </c>
       <c r="K2">
-        <v>1060.61</v>
+        <v>2876.54</v>
       </c>
       <c r="L2">
-        <v>0.02425231499266447</v>
+        <v>0.1638169239635798</v>
       </c>
       <c r="M2">
-        <v>1646.7351</v>
+        <v>2048.199</v>
       </c>
       <c r="N2">
-        <v>0.02287125730206305</v>
+        <v>0.03283648394543325</v>
       </c>
       <c r="O2">
-        <v>1.552630184516457</v>
+        <v>0.71203564003977</v>
       </c>
       <c r="P2">
-        <v>1421.7831</v>
+        <v>1794.792</v>
       </c>
       <c r="Q2">
-        <v>0.01974693264740932</v>
+        <v>0.0287738929144053</v>
       </c>
       <c r="R2">
-        <v>1.340533372304617</v>
+        <v>0.6239412627670743</v>
       </c>
       <c r="S2">
-        <v>224.952</v>
+        <v>253.4069999999999</v>
       </c>
       <c r="T2">
-        <v>0.1366048491952348</v>
+        <v>0.1237218649164461</v>
       </c>
       <c r="U2">
-        <v>21322.741</v>
+        <v>55557.103</v>
       </c>
       <c r="V2">
-        <v>0.296148357921228</v>
+        <v>0.8906848996187778</v>
       </c>
       <c r="W2">
-        <v>0.1197839054229486</v>
+        <v>0.06571883055549829</v>
       </c>
       <c r="X2">
-        <v>0.02595980389135583</v>
+        <v>0.05410321375043788</v>
       </c>
       <c r="Y2">
-        <v>0.09382410153159278</v>
+        <v>0.01161561680506042</v>
       </c>
       <c r="Z2">
-        <v>1.52164075090644</v>
+        <v>0.2143043904380419</v>
       </c>
       <c r="AA2">
-        <v>1.014527370443571e-05</v>
+        <v>0.0004421959471560448</v>
       </c>
       <c r="AB2">
-        <v>0.02598109608541764</v>
+        <v>0.0502328728939544</v>
       </c>
       <c r="AC2">
-        <v>-0.02496546440626468</v>
+        <v>-0.04935262566975019</v>
       </c>
       <c r="AD2">
-        <v>42345.859</v>
+        <v>85348.22200000001</v>
       </c>
       <c r="AE2">
-        <v>0.1907536663631357</v>
+        <v>0.09374122559691486</v>
       </c>
       <c r="AF2">
-        <v>42346.04975366636</v>
+        <v>85348.3157412256</v>
       </c>
       <c r="AG2">
-        <v>21023.30875366636</v>
+        <v>29791.2127412256</v>
       </c>
       <c r="AH2">
-        <v>0.370331776030185</v>
+        <v>0.5777551438432489</v>
       </c>
       <c r="AI2">
-        <v>0.4656668671186726</v>
+        <v>0.572122378401259</v>
       </c>
       <c r="AJ2">
-        <v>0.2259999545850045</v>
+        <v>0.3232310665819833</v>
       </c>
       <c r="AK2">
-        <v>0.3019999409606776</v>
+        <v>0.3182096969893293</v>
       </c>
       <c r="AL2">
-        <v>675.5119999999999</v>
+        <v>688.061</v>
       </c>
       <c r="AM2">
-        <v>-3316.642</v>
+        <v>676.2750000000001</v>
       </c>
       <c r="AN2">
-        <v>6.416986234029082</v>
+        <v>37.31929585526371</v>
       </c>
       <c r="AO2">
-        <v>8.463432181811722</v>
+        <v>1.505013363640724</v>
       </c>
       <c r="AP2">
-        <v>3.185819960955808</v>
+        <v>13.02648205345039</v>
       </c>
       <c r="AQ2">
-        <v>-1.723776639142844</v>
+        <v>1.531242467930945</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vector Capital Plc (AIM:VCAP)</t>
+          <t>IntegraFin Holdings plc (LSE:IHP)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,95 +724,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.107</v>
+      </c>
+      <c r="E3">
+        <v>0.08039999999999999</v>
+      </c>
+      <c r="F3">
+        <v>0.01</v>
+      </c>
       <c r="G3">
-        <v>0.7080745341614906</v>
+        <v>0.1202149093351242</v>
       </c>
       <c r="H3">
-        <v>0.7080745341614906</v>
+        <v>0.1202149093351242</v>
       </c>
       <c r="I3">
-        <v>0.7313664596273292</v>
+        <v>0.1128274009402283</v>
       </c>
       <c r="J3">
-        <v>0.5926284584980237</v>
+        <v>0.1128274009402283</v>
       </c>
       <c r="K3">
-        <v>2.67</v>
+        <v>49</v>
       </c>
       <c r="L3">
-        <v>0.4145962732919254</v>
+        <v>0.3290799194089993</v>
       </c>
       <c r="M3">
-        <v>0.83</v>
+        <v>38.157</v>
       </c>
       <c r="N3">
-        <v>0.03132075471698113</v>
+        <v>0.03162881299734748</v>
       </c>
       <c r="O3">
-        <v>0.3108614232209738</v>
+        <v>0.7787142857142858</v>
       </c>
       <c r="P3">
-        <v>0.83</v>
+        <v>37.6</v>
       </c>
       <c r="Q3">
-        <v>0.03132075471698113</v>
+        <v>0.03116710875331565</v>
       </c>
       <c r="R3">
-        <v>0.3108614232209738</v>
+        <v>0.7673469387755102</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.5570000000000022</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.01459758366747915</v>
       </c>
       <c r="U3">
-        <v>1.34</v>
+        <v>203.9</v>
       </c>
       <c r="V3">
-        <v>0.05056603773584906</v>
+        <v>0.1690152519893899</v>
+      </c>
+      <c r="W3">
+        <v>0.2223230490018149</v>
       </c>
       <c r="X3">
-        <v>0.02997659287041679</v>
+        <v>0.04978907181466406</v>
+      </c>
+      <c r="Y3">
+        <v>0.1725339771871508</v>
       </c>
       <c r="AB3">
-        <v>0.02966817916517894</v>
+        <v>0.0497812340474739</v>
       </c>
       <c r="AD3">
-        <v>21.3</v>
+        <v>3.12</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>21.3</v>
+        <v>3.12</v>
       </c>
       <c r="AG3">
-        <v>19.96</v>
+        <v>-200.78</v>
       </c>
       <c r="AH3">
-        <v>0.4456066945606695</v>
+        <v>0.002579535683576956</v>
       </c>
       <c r="AI3">
-        <v>0.3996247654784241</v>
+        <v>0.01590862737099735</v>
       </c>
       <c r="AJ3">
-        <v>0.4296168747309514</v>
+        <v>-0.1996579224756866</v>
       </c>
       <c r="AK3">
-        <v>0.3841416474210931</v>
+        <v>25.80719794344473</v>
       </c>
       <c r="AL3">
-        <v>1.46</v>
+        <v>0.111</v>
       </c>
       <c r="AM3">
-        <v>1.46</v>
+        <v>-0.78</v>
+      </c>
+      <c r="AN3">
+        <v>0.1743016759776536</v>
       </c>
       <c r="AO3">
-        <v>3.226027397260274</v>
+        <v>151.3513513513514</v>
+      </c>
+      <c r="AP3">
+        <v>-11.21675977653631</v>
       </c>
       <c r="AQ3">
-        <v>3.226027397260274</v>
+        <v>-21.53846153846154</v>
       </c>
     </row>
     <row r="4">
@@ -823,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADVFN Plc (AIM:AFN)</t>
+          <t>Curtis Banks Group PLC (AIM:CBP)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,118 +853,109 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0176</v>
+        <v>-0.32</v>
       </c>
       <c r="G4">
-        <v>0.1944</v>
+        <v>0.2535286458333333</v>
       </c>
       <c r="H4">
-        <v>0.1688</v>
+        <v>0.2486979166666667</v>
       </c>
       <c r="I4">
-        <v>0.1616</v>
+        <v>0.1640625</v>
       </c>
       <c r="J4">
-        <v>0.1616</v>
+        <v>0.1640625</v>
       </c>
       <c r="K4">
-        <v>2.23</v>
+        <v>-4.67</v>
       </c>
       <c r="L4">
-        <v>0.1784</v>
+        <v>-0.06080729166666667</v>
       </c>
       <c r="M4">
-        <v>0.5481</v>
+        <v>8.41</v>
       </c>
       <c r="N4">
-        <v>0.02149411764705882</v>
+        <v>0.03303220738413197</v>
       </c>
       <c r="O4">
-        <v>0.2457847533632287</v>
+        <v>-1.800856531049251</v>
       </c>
       <c r="P4">
-        <v>0.5481</v>
+        <v>7.27</v>
       </c>
       <c r="Q4">
-        <v>0.02149411764705882</v>
+        <v>0.02855459544383346</v>
       </c>
       <c r="R4">
-        <v>0.2457847533632287</v>
+        <v>-1.556745182012848</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.140000000000001</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.1355529131985732</v>
       </c>
       <c r="U4">
-        <v>2.68</v>
+        <v>487.6</v>
       </c>
       <c r="V4">
-        <v>0.1050980392156863</v>
+        <v>1.91516103692066</v>
       </c>
       <c r="W4">
-        <v>1.198924731182796</v>
+        <v>-0.04218608852755194</v>
       </c>
       <c r="X4">
-        <v>0.02421195188462254</v>
+        <v>0.05357055680560217</v>
       </c>
       <c r="Y4">
-        <v>1.174712779298173</v>
-      </c>
-      <c r="Z4">
-        <v>106.8376068376066</v>
-      </c>
-      <c r="AA4">
-        <v>17.26495726495723</v>
+        <v>-0.09575664533315412</v>
       </c>
       <c r="AB4">
-        <v>0.02428159971411203</v>
-      </c>
-      <c r="AC4">
-        <v>17.24067566524312</v>
+        <v>0.04958876040851903</v>
       </c>
       <c r="AD4">
-        <v>0.355</v>
+        <v>117.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.355</v>
+        <v>117.7</v>
       </c>
       <c r="AG4">
-        <v>-2.325</v>
+        <v>-369.9</v>
       </c>
       <c r="AH4">
-        <v>0.01373041964803713</v>
+        <v>0.3161428955143701</v>
       </c>
       <c r="AI4">
-        <v>0.07609860664523045</v>
+        <v>0.5803747534516766</v>
       </c>
       <c r="AJ4">
-        <v>-0.1003236245954693</v>
+        <v>3.208152645273199</v>
       </c>
       <c r="AK4">
-        <v>-1.171284634760706</v>
+        <v>1.298806179775281</v>
       </c>
       <c r="AL4">
-        <v>0.03</v>
+        <v>0.749</v>
       </c>
       <c r="AM4">
-        <v>-0.194</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AN4">
-        <v>0.1682464454976303</v>
+        <v>7.35625</v>
       </c>
       <c r="AO4">
-        <v>67.33333333333334</v>
+        <v>16.82242990654206</v>
       </c>
       <c r="AP4">
-        <v>-1.101895734597157</v>
+        <v>-23.11875</v>
       </c>
       <c r="AQ4">
-        <v>-10.41237113402062</v>
+        <v>18.20809248554913</v>
       </c>
     </row>
     <row r="5">
@@ -954,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aquis Exchange PLC (AIM:AQX)</t>
+          <t>Amigo Holdings PLC (LSE:AMGO)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,31 +975,31 @@
         </is>
       </c>
       <c r="G5">
-        <v>0.1028804347826087</v>
+        <v>4.470588235294118</v>
       </c>
       <c r="H5">
-        <v>0.06467391304347826</v>
+        <v>4.470588235294118</v>
       </c>
       <c r="I5">
-        <v>0.1125</v>
+        <v>3.308823529411765</v>
       </c>
       <c r="J5">
-        <v>0.1125</v>
+        <v>3.308823529411765</v>
       </c>
       <c r="K5">
-        <v>2.73</v>
+        <v>171.2</v>
       </c>
       <c r="L5">
-        <v>0.1483695652173913</v>
+        <v>3.147058823529412</v>
       </c>
       <c r="M5">
-        <v>0.098</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.0004177323103154306</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.0358974358974359</v>
+        <v>-0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -999,79 +1011,67 @@
         <v>-0</v>
       </c>
       <c r="S5">
-        <v>0.098</v>
-      </c>
-      <c r="T5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>19.1</v>
+        <v>143.1</v>
       </c>
       <c r="V5">
-        <v>0.0814151747655584</v>
+        <v>5.568093385214008</v>
       </c>
       <c r="W5">
-        <v>0.1587209302325581</v>
+        <v>-1.07808564231738</v>
       </c>
       <c r="X5">
-        <v>0.02415732291139535</v>
+        <v>0.06781985481135901</v>
       </c>
       <c r="Y5">
-        <v>0.1345636073211628</v>
-      </c>
-      <c r="Z5">
-        <v>3.687374749498999</v>
-      </c>
-      <c r="AA5">
-        <v>0.4148296593186374</v>
+        <v>-1.145905497128739</v>
       </c>
       <c r="AB5">
-        <v>0.02415040871745762</v>
-      </c>
-      <c r="AC5">
-        <v>0.3906792506011798</v>
+        <v>0.1046109115961805</v>
       </c>
       <c r="AD5">
-        <v>1.51</v>
+        <v>56.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.51</v>
+        <v>56.4</v>
       </c>
       <c r="AG5">
-        <v>-17.59</v>
+        <v>-86.69999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.006395324213290416</v>
+        <v>0.6869671132764921</v>
       </c>
       <c r="AI5">
-        <v>0.06013540422142572</v>
+        <v>0.5899581589958159</v>
       </c>
       <c r="AJ5">
-        <v>-0.08105617252661168</v>
+        <v>1.421311475409836</v>
       </c>
       <c r="AK5">
-        <v>-2.926788685524126</v>
+        <v>1.825263157894737</v>
       </c>
       <c r="AL5">
-        <v>0.054</v>
+        <v>9.69</v>
       </c>
       <c r="AM5">
-        <v>0.044</v>
+        <v>9.356</v>
       </c>
       <c r="AN5">
-        <v>0.58984375</v>
+        <v>0.3122923588039867</v>
       </c>
       <c r="AO5">
-        <v>38.33333333333333</v>
+        <v>18.57585139318886</v>
       </c>
       <c r="AP5">
-        <v>-6.87109375</v>
+        <v>-0.4800664451827242</v>
       </c>
       <c r="AQ5">
-        <v>47.04545454545455</v>
+        <v>19.23899102180419</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>London Stock Exchange Group plc (LSE:LSEG)</t>
+          <t>Aquis Exchange PLC (AIM:AQX)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1090,125 +1090,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.248</v>
-      </c>
-      <c r="E6">
-        <v>0.254</v>
-      </c>
-      <c r="F6">
-        <v>0.143</v>
-      </c>
       <c r="G6">
-        <v>0.2514428226567121</v>
+        <v>0.2457847533632287</v>
       </c>
       <c r="H6">
-        <v>0.2514428226567121</v>
+        <v>0.2192825112107623</v>
       </c>
       <c r="I6">
-        <v>0.2987482214512958</v>
+        <v>0.1609865470852018</v>
       </c>
       <c r="J6">
-        <v>0.1729058075107686</v>
+        <v>0.1609865470852018</v>
       </c>
       <c r="K6">
-        <v>609.1</v>
+        <v>4.86</v>
       </c>
       <c r="L6">
-        <v>0.09737654074275391</v>
+        <v>0.2179372197309417</v>
       </c>
       <c r="M6">
-        <v>560.7</v>
+        <v>2.47</v>
       </c>
       <c r="N6">
-        <v>0.01073009421126057</v>
+        <v>0.01980753809141941</v>
       </c>
       <c r="O6">
-        <v>0.9205384994253818</v>
+        <v>0.5082304526748971</v>
       </c>
       <c r="P6">
-        <v>509.6</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.00975219548788726</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.8366442291906091</v>
+        <v>-0</v>
       </c>
       <c r="S6">
-        <v>51.10000000000002</v>
+        <v>2.47</v>
       </c>
       <c r="T6">
-        <v>0.09113607990012487</v>
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>3795.3</v>
+        <v>16.2</v>
       </c>
       <c r="V6">
-        <v>0.07263050929195157</v>
+        <v>0.1299117882919006</v>
       </c>
       <c r="W6">
-        <v>0.131356480483071</v>
+        <v>0.2059322033898305</v>
       </c>
       <c r="X6">
-        <v>0.02594579101065354</v>
+        <v>0.0500600234820618</v>
       </c>
       <c r="Y6">
-        <v>0.1054106894724174</v>
+        <v>0.1558721799077687</v>
       </c>
       <c r="Z6">
-        <v>2.00941244498699</v>
+        <v>3.78286683630195</v>
       </c>
       <c r="AA6">
-        <v>0.3474390814226632</v>
+        <v>0.6089906700593722</v>
       </c>
       <c r="AB6">
-        <v>0.02587918661108705</v>
+        <v>0.04994648975733356</v>
       </c>
       <c r="AC6">
-        <v>0.3215598948115761</v>
+        <v>0.5590441803020387</v>
       </c>
       <c r="AD6">
-        <v>13141.4</v>
+        <v>4.43</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>13141.4</v>
+        <v>4.43</v>
       </c>
       <c r="AG6">
-        <v>9346.099999999999</v>
+        <v>-11.77</v>
       </c>
       <c r="AH6">
-        <v>0.2009502066630681</v>
+        <v>0.03430651281654147</v>
       </c>
       <c r="AI6">
-        <v>0.2766074781305515</v>
+        <v>0.1569252568189869</v>
       </c>
       <c r="AJ6">
-        <v>0.1517199396113699</v>
+        <v>-0.1042238554856991</v>
       </c>
       <c r="AK6">
-        <v>0.2138015596869645</v>
+        <v>-0.9783873649210306</v>
       </c>
       <c r="AL6">
-        <v>164.4</v>
+        <v>0.09</v>
       </c>
       <c r="AM6">
-        <v>143.7</v>
+        <v>0.051</v>
       </c>
       <c r="AN6">
-        <v>5.050499615680246</v>
+        <v>1.08578431372549</v>
       </c>
       <c r="AO6">
-        <v>11.36678832116788</v>
+        <v>39.88888888888889</v>
       </c>
       <c r="AP6">
-        <v>3.591890853189853</v>
+        <v>-2.884803921568627</v>
       </c>
       <c r="AQ6">
-        <v>13.00417536534447</v>
+        <v>70.3921568627451</v>
       </c>
     </row>
     <row r="7">
@@ -1219,7 +1210,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Duke Royalty Limited (AIM:DUKE)</t>
+          <t>Appreciate Group plc (AIM:APP)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1227,41 +1218,47 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D7">
+        <v>-0.148</v>
+      </c>
+      <c r="E7">
+        <v>-0.0839</v>
+      </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.08679525222551927</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.08679525222551927</v>
       </c>
       <c r="I7">
-        <v>0.8734567901234569</v>
+        <v>0.07863501483679525</v>
       </c>
       <c r="J7">
-        <v>0.7799752576267729</v>
+        <v>0.06173664779006025</v>
       </c>
       <c r="K7">
-        <v>21.6</v>
+        <v>6.44</v>
       </c>
       <c r="L7">
-        <v>0.6666666666666667</v>
+        <v>0.04777448071216617</v>
       </c>
       <c r="M7">
-        <v>6.08</v>
+        <v>3.66</v>
       </c>
       <c r="N7">
-        <v>0.03012884043607532</v>
+        <v>0.03935483870967742</v>
       </c>
       <c r="O7">
-        <v>0.2814814814814814</v>
+        <v>0.5683229813664596</v>
       </c>
       <c r="P7">
-        <v>6.08</v>
+        <v>3.66</v>
       </c>
       <c r="Q7">
-        <v>0.03012884043607532</v>
+        <v>0.03935483870967742</v>
       </c>
       <c r="R7">
-        <v>0.2814814814814814</v>
+        <v>0.5683229813664596</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1270,67 +1267,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="V7">
-        <v>0.07185332011892963</v>
+        <v>0.156989247311828</v>
       </c>
       <c r="W7">
-        <v>0.217741935483871</v>
+        <v>0.331958762886598</v>
       </c>
       <c r="X7">
-        <v>0.02459136019266394</v>
+        <v>0.05023658298585082</v>
       </c>
       <c r="Y7">
-        <v>0.193150575291207</v>
+        <v>0.2817221799007472</v>
       </c>
       <c r="Z7">
-        <v>0.2764811796530332</v>
+        <v>6.439285373077292</v>
       </c>
       <c r="AA7">
-        <v>0.2156484793288286</v>
+        <v>0.3975398930973594</v>
       </c>
       <c r="AB7">
-        <v>0.02472895223366009</v>
+        <v>0.05004863235578875</v>
       </c>
       <c r="AC7">
-        <v>0.1909195270951685</v>
+        <v>0.3474912607415707</v>
       </c>
       <c r="AD7">
-        <v>13.3</v>
+        <v>5.3</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>13.3</v>
+        <v>5.3</v>
       </c>
       <c r="AG7">
-        <v>-1.199999999999999</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.06183170618317062</v>
+        <v>0.05391658189216684</v>
       </c>
       <c r="AI7">
-        <v>0.07455156950672646</v>
+        <v>0.2663316582914573</v>
       </c>
       <c r="AJ7">
-        <v>-0.005982053838484542</v>
+        <v>-0.1111111111111111</v>
       </c>
       <c r="AK7">
-        <v>-0.007321537522879801</v>
+        <v>-1.754716981132076</v>
       </c>
       <c r="AL7">
-        <v>1.37</v>
+        <v>0.51</v>
       </c>
       <c r="AM7">
-        <v>1.37</v>
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="AN7">
+        <v>0.456896551724138</v>
       </c>
       <c r="AO7">
-        <v>20.65693430656934</v>
+        <v>20.78431372549019</v>
+      </c>
+      <c r="AP7">
+        <v>-0.8017241379310346</v>
       </c>
       <c r="AQ7">
-        <v>20.65693430656934</v>
+        <v>-17.66666666666666</v>
       </c>
     </row>
     <row r="8">
@@ -1341,7 +1344,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M&amp;G plc (LSE:MNG)</t>
+          <t>Duke Royalty Limited (AIM:DUKE)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1349,119 +1352,113 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="F8">
-        <v>-0.0375</v>
+      <c r="D8">
+        <v>1.363</v>
       </c>
       <c r="G8">
-        <v>0.1310256581301281</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>0.1310256581301281</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>0.1204828410117708</v>
+        <v>0.8854166666666667</v>
       </c>
       <c r="J8">
-        <v>0.06024142050588541</v>
+        <v>0.8487573099415205</v>
       </c>
       <c r="K8">
-        <v>87</v>
+        <v>27.3</v>
       </c>
       <c r="L8">
-        <v>0.00263797839889872</v>
+        <v>0.7109375</v>
       </c>
       <c r="M8">
-        <v>751.4</v>
+        <v>10.3</v>
       </c>
       <c r="N8">
-        <v>0.1098939670932358</v>
+        <v>0.0612730517549078</v>
       </c>
       <c r="O8">
-        <v>8.636781609195403</v>
+        <v>0.3772893772893773</v>
       </c>
       <c r="P8">
-        <v>638.1</v>
+        <v>10.3</v>
       </c>
       <c r="Q8">
-        <v>0.09332358318098721</v>
+        <v>0.0612730517549078</v>
       </c>
       <c r="R8">
-        <v>7.33448275862069</v>
+        <v>0.3772893772893773</v>
       </c>
       <c r="S8">
-        <v>113.3</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>0.1507852009582113</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>8379.299999999999</v>
+        <v>5.65</v>
       </c>
       <c r="V8">
-        <v>1.225491773308958</v>
+        <v>0.03361094586555622</v>
       </c>
       <c r="W8">
-        <v>0.01270833637651733</v>
+        <v>0.1653543307086614</v>
       </c>
       <c r="X8">
-        <v>0.03725148899582746</v>
+        <v>0.05166155380270943</v>
       </c>
       <c r="Y8">
-        <v>-0.02454315261931013</v>
+        <v>0.113692776905952</v>
       </c>
       <c r="Z8">
-        <v>3.297320535892822</v>
+        <v>0.2346815298302226</v>
       </c>
       <c r="AA8">
-        <v>0.1986352729454109</v>
+        <v>0.1991876639516604</v>
       </c>
       <c r="AB8">
-        <v>0.02976964227370997</v>
+        <v>0.0496618186829745</v>
       </c>
       <c r="AC8">
-        <v>0.168865630671701</v>
+        <v>0.1495258452686859</v>
       </c>
       <c r="AD8">
-        <v>12311.3</v>
+        <v>38.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>12311.3</v>
+        <v>38.7</v>
       </c>
       <c r="AG8">
-        <v>3932</v>
+        <v>33.05</v>
       </c>
       <c r="AH8">
-        <v>0.6429280163770054</v>
+        <v>0.187137330754352</v>
       </c>
       <c r="AI8">
-        <v>0.636259334866534</v>
+        <v>0.1807566557683326</v>
       </c>
       <c r="AJ8">
-        <v>0.3651051580853336</v>
+        <v>0.1643052448421576</v>
       </c>
       <c r="AK8">
-        <v>0.3584255528613881</v>
+        <v>0.1585512113216599</v>
       </c>
       <c r="AL8">
-        <v>390.9</v>
+        <v>3.35</v>
       </c>
       <c r="AM8">
-        <v>390.9</v>
-      </c>
-      <c r="AN8">
-        <v>2.985281280310378</v>
+        <v>3.35</v>
       </c>
       <c r="AO8">
-        <v>10.16500383729854</v>
-      </c>
-      <c r="AP8">
-        <v>0.953443258971872</v>
+        <v>10.14925373134328</v>
       </c>
       <c r="AQ8">
-        <v>10.16500383729854</v>
+        <v>10.14925373134328</v>
       </c>
     </row>
     <row r="9">
@@ -1472,7 +1469,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H&amp;T Group plc (AIM:HAT)</t>
+          <t>International Personal Finance plc (LSE:IPF)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1481,121 +1478,121 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0664</v>
+        <v>-0.0603</v>
       </c>
       <c r="E9">
-        <v>0.145</v>
+        <v>-0.0596</v>
       </c>
       <c r="G9">
-        <v>0.1602082128397918</v>
+        <v>0.243262311274164</v>
       </c>
       <c r="H9">
-        <v>0.1602082128397918</v>
+        <v>0.243262311274164</v>
       </c>
       <c r="I9">
-        <v>0.1330248698669751</v>
+        <v>0.1995202483420347</v>
       </c>
       <c r="J9">
-        <v>0.1073025253618918</v>
+        <v>0.1707351488641174</v>
       </c>
       <c r="K9">
-        <v>17</v>
+        <v>60.5</v>
       </c>
       <c r="L9">
-        <v>0.09832272990167727</v>
+        <v>0.0853675744320587</v>
       </c>
       <c r="M9">
-        <v>4.68</v>
+        <v>25.25</v>
       </c>
       <c r="N9">
-        <v>0.02939698492462312</v>
+        <v>0.128892291985707</v>
       </c>
       <c r="O9">
-        <v>0.2752941176470588</v>
+        <v>0.4173553719008264</v>
       </c>
       <c r="P9">
-        <v>4.68</v>
+        <v>21.6</v>
       </c>
       <c r="Q9">
-        <v>0.02939698492462312</v>
+        <v>0.110260336906585</v>
       </c>
       <c r="R9">
-        <v>0.2752941176470588</v>
+        <v>0.3570247933884298</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>3.649999999999999</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>0.1445544554455445</v>
       </c>
       <c r="U9">
-        <v>44.9</v>
+        <v>53.1</v>
       </c>
       <c r="V9">
-        <v>0.282035175879397</v>
+        <v>0.2710566615620215</v>
       </c>
       <c r="W9">
-        <v>0.1082113303628262</v>
+        <v>0.1206862158388191</v>
       </c>
       <c r="X9">
-        <v>0.0253893974193666</v>
+        <v>0.07667081576531239</v>
       </c>
       <c r="Y9">
-        <v>0.08282193294345963</v>
+        <v>0.04401540007350668</v>
       </c>
       <c r="Z9">
-        <v>1.199861207494796</v>
+        <v>0.7036338363780779</v>
       </c>
       <c r="AA9">
-        <v>0.1287481376479604</v>
+        <v>0.1201350277998411</v>
       </c>
       <c r="AB9">
-        <v>0.02504445631703757</v>
+        <v>0.05375680363335313</v>
       </c>
       <c r="AC9">
-        <v>0.1037036813309228</v>
+        <v>0.06637822416648802</v>
       </c>
       <c r="AD9">
-        <v>27.9</v>
+        <v>640.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>27.9</v>
+        <v>640.7</v>
       </c>
       <c r="AG9">
-        <v>-17</v>
+        <v>587.6</v>
       </c>
       <c r="AH9">
-        <v>0.1491181186531267</v>
+        <v>0.7658379153717428</v>
       </c>
       <c r="AI9">
-        <v>0.1294063079777366</v>
+        <v>0.566289552766484</v>
       </c>
       <c r="AJ9">
-        <v>-0.119549929676512</v>
+        <v>0.7499680918953414</v>
       </c>
       <c r="AK9">
-        <v>-0.09958992384299942</v>
+        <v>0.5449318371510712</v>
       </c>
       <c r="AL9">
-        <v>1.89</v>
+        <v>70.7</v>
       </c>
       <c r="AM9">
-        <v>1.883</v>
+        <v>70.7</v>
       </c>
       <c r="AN9">
-        <v>1.007220216606498</v>
+        <v>4.314478114478114</v>
       </c>
       <c r="AO9">
-        <v>12.16931216931217</v>
+        <v>2</v>
       </c>
       <c r="AP9">
-        <v>-0.6137184115523466</v>
+        <v>3.956902356902357</v>
       </c>
       <c r="AQ9">
-        <v>12.2145512480085</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1606,7 +1603,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ramsdens Holdings PLC (AIM:RFX)</t>
+          <t>London Stock Exchange Group plc (LSE:LSEG)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1614,41 +1611,50 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D10">
+        <v>0.326</v>
+      </c>
+      <c r="E10">
+        <v>0.228</v>
+      </c>
+      <c r="F10">
+        <v>0.119</v>
+      </c>
       <c r="G10">
-        <v>0.1688102893890675</v>
+        <v>0.4350038074007041</v>
       </c>
       <c r="H10">
-        <v>0.1688102893890675</v>
+        <v>0.3762705130610398</v>
       </c>
       <c r="I10">
-        <v>0.08890675241157556</v>
+        <v>0.231191992318983</v>
       </c>
       <c r="J10">
-        <v>0.07022595618501883</v>
+        <v>0.1907746139408612</v>
       </c>
       <c r="K10">
-        <v>4.06</v>
+        <v>1156.8</v>
       </c>
       <c r="L10">
-        <v>0.0652733118971061</v>
+        <v>0.1276638009998565</v>
       </c>
       <c r="M10">
-        <v>0.978</v>
+        <v>642.8</v>
       </c>
       <c r="N10">
-        <v>0.01385269121813031</v>
+        <v>0.01349759466479643</v>
       </c>
       <c r="O10">
-        <v>0.2408866995073892</v>
+        <v>0.5556708160442601</v>
       </c>
       <c r="P10">
-        <v>0.978</v>
+        <v>642.8</v>
       </c>
       <c r="Q10">
-        <v>0.01385269121813031</v>
+        <v>0.01349759466479643</v>
       </c>
       <c r="R10">
-        <v>0.2408866995073892</v>
+        <v>0.5556708160442601</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1657,73 +1663,73 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>20.7</v>
+        <v>3062.2</v>
       </c>
       <c r="V10">
-        <v>0.2932011331444759</v>
+        <v>0.06430045796910334</v>
       </c>
       <c r="W10">
-        <v>0.08768898488120951</v>
+        <v>0.0363249272276808</v>
       </c>
       <c r="X10">
-        <v>0.02536120264725225</v>
+        <v>0.05151364021358638</v>
       </c>
       <c r="Y10">
-        <v>0.06232778223395725</v>
+        <v>-0.01518871298590558</v>
       </c>
       <c r="Z10">
-        <v>1.407239819004525</v>
+        <v>0.5285837620897647</v>
       </c>
       <c r="AA10">
-        <v>0.0988247618712256</v>
+        <v>0.1008403631480829</v>
       </c>
       <c r="AB10">
-        <v>0.02557414864720152</v>
+        <v>0.05041711343212005</v>
       </c>
       <c r="AC10">
-        <v>0.07325061322402408</v>
+        <v>0.05042324971596284</v>
       </c>
       <c r="AD10">
-        <v>12.1</v>
+        <v>10107.5</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>12.1</v>
+        <v>10107.5</v>
       </c>
       <c r="AG10">
-        <v>-8.6</v>
+        <v>7045.3</v>
       </c>
       <c r="AH10">
-        <v>0.1463119709794438</v>
+        <v>0.1750798533884859</v>
       </c>
       <c r="AI10">
-        <v>0.1983606557377049</v>
+        <v>0.229892508335949</v>
       </c>
       <c r="AJ10">
-        <v>-0.1387096774193549</v>
+        <v>0.1288728813249287</v>
       </c>
       <c r="AK10">
-        <v>-0.2133995037220844</v>
+        <v>0.1722398787404655</v>
       </c>
       <c r="AL10">
-        <v>0.719</v>
+        <v>198.1</v>
       </c>
       <c r="AM10">
-        <v>0.719</v>
+        <v>189.59</v>
       </c>
       <c r="AN10">
-        <v>1.628532974427995</v>
+        <v>3.172373748469916</v>
       </c>
       <c r="AO10">
-        <v>7.691237830319889</v>
+        <v>10.57496214033317</v>
       </c>
       <c r="AP10">
-        <v>-1.157469717362046</v>
+        <v>2.211261416779135</v>
       </c>
       <c r="AQ10">
-        <v>7.691237830319889</v>
+        <v>11.04963341948415</v>
       </c>
     </row>
     <row r="11">
@@ -1734,7 +1740,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>International Personal Finance plc (LSE:IPF)</t>
+          <t>H&amp;T Group plc (AIM:HAT)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1743,121 +1749,121 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.057</v>
+        <v>0.0573</v>
       </c>
       <c r="E11">
-        <v>-0.115</v>
+        <v>-0.0334</v>
       </c>
       <c r="G11">
-        <v>0.06102783725910064</v>
+        <v>0.1108017817371938</v>
       </c>
       <c r="H11">
-        <v>0.06102783725910064</v>
+        <v>0.1108017817371938</v>
       </c>
       <c r="I11">
-        <v>0.2099839400428266</v>
+        <v>0.09020044543429843</v>
       </c>
       <c r="J11">
-        <v>0.1161177938848273</v>
+        <v>0.06873124850448195</v>
       </c>
       <c r="K11">
-        <v>45.4</v>
+        <v>9.18</v>
       </c>
       <c r="L11">
-        <v>0.06076017130620984</v>
+        <v>0.05111358574610245</v>
       </c>
       <c r="M11">
-        <v>8.395999999999999</v>
+        <v>5.74</v>
       </c>
       <c r="N11">
-        <v>0.02173440331348692</v>
+        <v>0.02263406940063092</v>
       </c>
       <c r="O11">
-        <v>0.1849339207048458</v>
+        <v>0.6252723311546842</v>
       </c>
       <c r="P11">
-        <v>6.635999999999999</v>
+        <v>5.74</v>
       </c>
       <c r="Q11">
-        <v>0.01717835878850634</v>
+        <v>0.02263406940063092</v>
       </c>
       <c r="R11">
-        <v>0.1461674008810573</v>
+        <v>0.6252723311546842</v>
       </c>
       <c r="S11">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>0.2096236303001429</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>124.9</v>
+        <v>15.4</v>
       </c>
       <c r="V11">
-        <v>0.3233238415739063</v>
+        <v>0.06072555205047319</v>
       </c>
       <c r="W11">
-        <v>0.09438669438669438</v>
+        <v>0.04890783164624401</v>
       </c>
       <c r="X11">
-        <v>0.03649284487108422</v>
+        <v>0.05133122827414036</v>
       </c>
       <c r="Y11">
-        <v>0.05789384951561016</v>
+        <v>-0.002423396627896354</v>
       </c>
       <c r="Z11">
-        <v>0.6724262059035276</v>
+        <v>1.247222222222222</v>
       </c>
       <c r="AA11">
-        <v>0.0780806475798623</v>
+        <v>0.08572314049586777</v>
       </c>
       <c r="AB11">
-        <v>0.03040491819517118</v>
+        <v>0.04967735219250544</v>
       </c>
       <c r="AC11">
-        <v>0.04767572938469113</v>
+        <v>0.03604578830336232</v>
       </c>
       <c r="AD11">
-        <v>655.4</v>
+        <v>48.2</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>655.4</v>
+        <v>48.2</v>
       </c>
       <c r="AG11">
-        <v>530.5</v>
+        <v>32.8</v>
       </c>
       <c r="AH11">
-        <v>0.6291638667562638</v>
+        <v>0.1597084161696488</v>
       </c>
       <c r="AI11">
-        <v>0.5651461584892644</v>
+        <v>0.2219152854511971</v>
       </c>
       <c r="AJ11">
-        <v>0.5786431064572426</v>
+        <v>0.1145251396648045</v>
       </c>
       <c r="AK11">
-        <v>0.5126594511016622</v>
+        <v>0.1625371655104064</v>
       </c>
       <c r="AL11">
-        <v>74.5</v>
+        <v>1.6</v>
       </c>
       <c r="AM11">
-        <v>74.5</v>
+        <v>1.59</v>
       </c>
       <c r="AN11">
-        <v>3.924550898203593</v>
+        <v>2.362745098039216</v>
       </c>
       <c r="AO11">
-        <v>2.106040268456376</v>
+        <v>10.125</v>
       </c>
       <c r="AP11">
-        <v>3.176646706586826</v>
+        <v>1.607843137254902</v>
       </c>
       <c r="AQ11">
-        <v>2.106040268456376</v>
+        <v>10.18867924528302</v>
       </c>
     </row>
     <row r="12">
@@ -1868,7 +1874,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Funding Circle Holdings plc (LSE:FCH)</t>
+          <t>Vector Capital Plc (AIM:VCAP)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1877,112 +1883,115 @@
         </is>
       </c>
       <c r="G12">
-        <v>-0.2296909843899332</v>
+        <v>0.7837837837837838</v>
       </c>
       <c r="H12">
-        <v>-0.3628544122331953</v>
+        <v>0.7837837837837838</v>
       </c>
       <c r="I12">
-        <v>0.1987894233832431</v>
+        <v>0.7937411095305832</v>
       </c>
       <c r="J12">
-        <v>0.188951721543458</v>
+        <v>0.642824466571835</v>
       </c>
       <c r="K12">
-        <v>55.7</v>
+        <v>3.04</v>
       </c>
       <c r="L12">
-        <v>0.1774450461930551</v>
+        <v>0.4324324324324324</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>1.35</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.0574468085106383</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0.4440789473684211</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>1.35</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.0574468085106383</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0.4440789473684211</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
       <c r="U12">
-        <v>232.2</v>
+        <v>0.896</v>
       </c>
       <c r="V12">
-        <v>0.4302390216787104</v>
+        <v>0.03812765957446809</v>
       </c>
       <c r="W12">
-        <v>0.2073715562174237</v>
+        <v>0.095</v>
       </c>
       <c r="X12">
-        <v>0.0342188143295599</v>
+        <v>0.06033888854711289</v>
       </c>
       <c r="Y12">
-        <v>0.1731527418878638</v>
+        <v>0.03466111145288711</v>
       </c>
       <c r="Z12">
-        <v>0.3020302126431252</v>
+        <v>0.1352963818321786</v>
       </c>
       <c r="AA12">
-        <v>0.0570691286370552</v>
+        <v>0.08697182448036954</v>
       </c>
       <c r="AB12">
-        <v>0.03135335370854778</v>
+        <v>0.05269707502834805</v>
       </c>
       <c r="AC12">
-        <v>0.02571577492850741</v>
+        <v>0.03427474945202149</v>
       </c>
       <c r="AD12">
-        <v>747.5</v>
+        <v>30.2</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>747.5</v>
+        <v>30.2</v>
       </c>
       <c r="AG12">
-        <v>515.3</v>
+        <v>29.304</v>
       </c>
       <c r="AH12">
-        <v>0.5807178371659416</v>
+        <v>0.5623836126629422</v>
       </c>
       <c r="AI12">
-        <v>0.680535324107793</v>
+        <v>0.5033333333333333</v>
       </c>
       <c r="AJ12">
-        <v>0.488436018957346</v>
+        <v>0.554957957730475</v>
       </c>
       <c r="AK12">
-        <v>0.5948972523666589</v>
+        <v>0.4958040064970222</v>
       </c>
       <c r="AL12">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AM12">
-        <v>1.384</v>
+        <v>1.828</v>
       </c>
       <c r="AN12">
-        <v>11.44716692189893</v>
+        <v>5.412186379928316</v>
       </c>
       <c r="AO12">
-        <v>37.59036144578313</v>
+        <v>3.049180327868852</v>
       </c>
       <c r="AP12">
-        <v>7.891271056661561</v>
+        <v>5.251612903225806</v>
       </c>
       <c r="AQ12">
-        <v>45.08670520231214</v>
+        <v>3.052516411378556</v>
       </c>
     </row>
     <row r="13">
@@ -1993,7 +2002,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IntegraFin Holdings plc (LSE:IHP)</t>
+          <t>ADVFN Plc (AIM:AFN)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2002,124 +2011,118 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.126</v>
-      </c>
-      <c r="E13">
-        <v>0.197</v>
-      </c>
-      <c r="F13">
-        <v>0.121</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="G13">
-        <v>-0.8574850299401197</v>
+        <v>0.04433962264150944</v>
       </c>
       <c r="H13">
-        <v>-0.8574850299401197</v>
+        <v>0.0159329140461216</v>
       </c>
       <c r="I13">
-        <v>-0.8826347305389222</v>
+        <v>0.005345911949685535</v>
       </c>
       <c r="J13">
-        <v>-0.4765398779904979</v>
+        <v>0.005345911949685535</v>
       </c>
       <c r="K13">
-        <v>69</v>
+        <v>-1.66</v>
       </c>
       <c r="L13">
-        <v>0.4131736526946108</v>
+        <v>-0.1740041928721174</v>
       </c>
       <c r="M13">
-        <v>39.68</v>
+        <v>0.716</v>
       </c>
       <c r="N13">
-        <v>0.01577984570110554</v>
+        <v>0.06754716981132075</v>
       </c>
       <c r="O13">
-        <v>0.5750724637681159</v>
+        <v>-0.4313253012048193</v>
       </c>
       <c r="P13">
-        <v>38.4</v>
+        <v>0.716</v>
       </c>
       <c r="Q13">
-        <v>0.01527081842042472</v>
+        <v>0.06754716981132075</v>
       </c>
       <c r="R13">
-        <v>0.5565217391304348</v>
+        <v>-0.4313253012048193</v>
       </c>
       <c r="S13">
-        <v>1.280000000000001</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>0.03225806451612906</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>1947.4</v>
+        <v>1.11</v>
       </c>
       <c r="V13">
-        <v>0.77443728624831</v>
+        <v>0.1047169811320755</v>
       </c>
       <c r="W13">
-        <v>0.3439680957128614</v>
+        <v>-0.3851508120649652</v>
       </c>
       <c r="X13">
-        <v>0.02413008330824799</v>
+        <v>0.04990049807805914</v>
       </c>
       <c r="Y13">
-        <v>0.3198380124046134</v>
+        <v>-0.4350513101430243</v>
       </c>
       <c r="Z13">
-        <v>-0.09193149727233192</v>
+        <v>12.15286624203823</v>
       </c>
       <c r="AA13">
-        <v>0.04380902449364085</v>
+        <v>0.06496815286624212</v>
       </c>
       <c r="AB13">
-        <v>0.02412724104884853</v>
+        <v>0.05003028618354206</v>
       </c>
       <c r="AC13">
-        <v>0.01968178344479232</v>
+        <v>0.01493786668270006</v>
       </c>
       <c r="AD13">
-        <v>6.8</v>
+        <v>0.171</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>6.8</v>
+        <v>0.171</v>
       </c>
       <c r="AG13">
-        <v>-1940.6</v>
+        <v>-0.9390000000000001</v>
       </c>
       <c r="AH13">
-        <v>0.002696914412627905</v>
+        <v>0.01587596323461146</v>
       </c>
       <c r="AI13">
-        <v>0.02992957746478873</v>
+        <v>0.09601347557551937</v>
       </c>
       <c r="AJ13">
-        <v>-3.3808362369338</v>
+        <v>-0.0971949073594866</v>
       </c>
       <c r="AK13">
-        <v>1.128124636670155</v>
+        <v>-1.399403874813711</v>
       </c>
       <c r="AL13">
-        <v>0.225</v>
+        <v>0.017</v>
       </c>
       <c r="AM13">
-        <v>-3969.575</v>
+        <v>0.017</v>
       </c>
       <c r="AN13">
-        <v>-0.04748603351955308</v>
+        <v>1.125</v>
       </c>
       <c r="AO13">
-        <v>-655.1111111111111</v>
+        <v>3</v>
       </c>
       <c r="AP13">
-        <v>13.55167597765363</v>
+        <v>-6.177631578947369</v>
       </c>
       <c r="AQ13">
-        <v>0.03713243861118633</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -2130,7 +2133,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mortgage Advice Bureau (Holdings) plc (AIM:MAB1)</t>
+          <t>Ramsdens Holdings PLC (AIM:RFX)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2138,50 +2141,41 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D14">
-        <v>0.152</v>
-      </c>
-      <c r="E14">
-        <v>0.104</v>
-      </c>
-      <c r="F14">
-        <v>0.23</v>
-      </c>
       <c r="G14">
-        <v>0</v>
+        <v>0.0106015037593985</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>0.0106015037593985</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>0.03233082706766917</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>0.02464909008814464</v>
       </c>
       <c r="K14">
-        <v>22</v>
+        <v>2.92</v>
       </c>
       <c r="L14">
-        <v>0.08997955010224949</v>
+        <v>0.04390977443609023</v>
       </c>
       <c r="M14">
-        <v>18.8</v>
+        <v>0.496</v>
       </c>
       <c r="N14">
-        <v>0.01799731954815241</v>
+        <v>0.006500655307994757</v>
       </c>
       <c r="O14">
-        <v>0.8545454545454546</v>
+        <v>0.1698630136986301</v>
       </c>
       <c r="P14">
-        <v>18.8</v>
+        <v>0.496</v>
       </c>
       <c r="Q14">
-        <v>0.01799731954815241</v>
+        <v>0.006500655307994757</v>
       </c>
       <c r="R14">
-        <v>0.8545454545454546</v>
+        <v>0.1698630136986301</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2190,64 +2184,73 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>46.9</v>
+        <v>14.1</v>
       </c>
       <c r="V14">
-        <v>0.04489756844725254</v>
+        <v>0.1847968545216252</v>
       </c>
       <c r="W14">
-        <v>0.632183908045977</v>
+        <v>0.05971370143149284</v>
       </c>
       <c r="X14">
-        <v>0.02413480067070641</v>
+        <v>0.05132025179237969</v>
       </c>
       <c r="Y14">
-        <v>0.6080491073752706</v>
+        <v>0.008393449639113156</v>
       </c>
       <c r="Z14">
-        <v>-25.20618556701029</v>
+        <v>1.650124069478908</v>
       </c>
       <c r="AA14">
-        <v>-0</v>
+        <v>0.04067405684520146</v>
       </c>
       <c r="AB14">
-        <v>0.02413126557243322</v>
+        <v>0.04967788637626656</v>
       </c>
       <c r="AC14">
-        <v>-0.02413126557243322</v>
+        <v>-0.009003829531065106</v>
       </c>
       <c r="AD14">
-        <v>3.5</v>
+        <v>14.4</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>3.5</v>
+        <v>14.4</v>
       </c>
       <c r="AG14">
-        <v>-43.4</v>
+        <v>0.3000000000000007</v>
       </c>
       <c r="AH14">
-        <v>0.003339376013739147</v>
+        <v>0.1587651598676957</v>
       </c>
       <c r="AI14">
-        <v>0.06340579710144927</v>
+        <v>0.2253521126760563</v>
       </c>
       <c r="AJ14">
-        <v>-0.04334798242109469</v>
+        <v>0.003916449086161889</v>
       </c>
       <c r="AK14">
-        <v>-5.2289156626506</v>
+        <v>0.006024096385542183</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>0.618</v>
       </c>
       <c r="AM14">
-        <v>-0.099</v>
+        <v>0.618</v>
+      </c>
+      <c r="AN14">
+        <v>3.645569620253164</v>
+      </c>
+      <c r="AO14">
+        <v>3.478964401294498</v>
+      </c>
+      <c r="AP14">
+        <v>0.07594936708860778</v>
       </c>
       <c r="AQ14">
-        <v>-0</v>
+        <v>3.478964401294498</v>
       </c>
     </row>
     <row r="15">
@@ -2258,7 +2261,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Distribution Finance Capital Holdings plc (AIM:DFCH)</t>
+          <t>Funding Circle Holdings plc (LSE:FCH)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2266,32 +2269,35 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="F15">
+        <v>-0.232</v>
+      </c>
       <c r="G15">
-        <v>0</v>
+        <v>0.461729490022173</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>0.4186252771618625</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>0.1596452328159645</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>0.1596452328159645</v>
       </c>
       <c r="K15">
-        <v>-12</v>
+        <v>42.4</v>
       </c>
       <c r="L15">
-        <v>-1.540436456996149</v>
+        <v>0.1880266075388027</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>5.59</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>0.02386848847139197</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>0.1318396226415094</v>
       </c>
       <c r="P15">
         <v>-0</v>
@@ -2300,67 +2306,82 @@
         <v>-0</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>5.59</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
       </c>
       <c r="U15">
-        <v>48.2</v>
+        <v>243.9</v>
       </c>
       <c r="V15">
-        <v>0.4137339055793992</v>
+        <v>1.041417591801879</v>
       </c>
       <c r="W15">
-        <v>-0.1702127659574468</v>
+        <v>0.1208321459105158</v>
       </c>
       <c r="X15">
-        <v>0.02416259460971511</v>
+        <v>0.05463587069527358</v>
       </c>
       <c r="Y15">
-        <v>-0.1943753605671619</v>
+        <v>0.06619627521524224</v>
       </c>
       <c r="Z15">
-        <v>0.03766924564796906</v>
+        <v>0.2603324867236204</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>0.04156084045255137</v>
       </c>
       <c r="AB15">
-        <v>0.02415487254072751</v>
+        <v>0.05170428738347061</v>
       </c>
       <c r="AC15">
-        <v>-0.02415487254072751</v>
+        <v>-0.01014344693091924</v>
       </c>
       <c r="AD15">
-        <v>0.834</v>
+        <v>138.6</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0.834</v>
+        <v>138.6</v>
       </c>
       <c r="AG15">
-        <v>-47.366</v>
+        <v>-105.3</v>
       </c>
       <c r="AH15">
-        <v>0.007107914159578638</v>
+        <v>0.3717811158798284</v>
       </c>
       <c r="AI15">
-        <v>0.006862277222834762</v>
+        <v>0.2759307186940076</v>
       </c>
       <c r="AJ15">
-        <v>-0.6851332195446524</v>
+        <v>-0.8169123351435224</v>
       </c>
       <c r="AK15">
-        <v>-0.6458941282351979</v>
+        <v>-0.4075077399380806</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>0.612</v>
+      </c>
+      <c r="AN15">
+        <v>3.818181818181818</v>
+      </c>
+      <c r="AO15">
+        <v>29.50819672131147</v>
+      </c>
+      <c r="AP15">
+        <v>-2.900826446280992</v>
+      </c>
+      <c r="AQ15">
+        <v>58.82352941176471</v>
       </c>
     </row>
     <row r="16">
@@ -2371,7 +2392,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Morses Club PLC (AIM:MCL)</t>
+          <t>Paragon Banking Group PLC (LSE:PAG)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2380,10 +2401,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.00601</v>
+        <v>0.0885</v>
       </c>
       <c r="E16">
-        <v>-0.297</v>
+        <v>0.218</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2392,103 +2413,97 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0.0002835448124712771</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>0.0002120422075872159</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>1.55</v>
+        <v>349.4</v>
       </c>
       <c r="L16">
-        <v>0.01176024279210926</v>
+        <v>0.7835837631755999</v>
       </c>
       <c r="M16">
-        <v>7.26</v>
+        <v>165.4</v>
       </c>
       <c r="N16">
-        <v>0.06842601319509896</v>
+        <v>0.1059645076558396</v>
       </c>
       <c r="O16">
-        <v>4.683870967741935</v>
+        <v>0.4733829421866056</v>
       </c>
       <c r="P16">
-        <v>7.26</v>
+        <v>76.8</v>
       </c>
       <c r="Q16">
-        <v>0.06842601319509896</v>
+        <v>0.04920238324043821</v>
       </c>
       <c r="R16">
-        <v>4.683870967741935</v>
+        <v>0.2198053806525472</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>88.59999999999998</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>0.5356711003627569</v>
       </c>
       <c r="U16">
-        <v>9.49</v>
+        <v>2151.6</v>
       </c>
       <c r="V16">
-        <v>0.08944392082940622</v>
+        <v>1.378435517970402</v>
       </c>
       <c r="W16">
-        <v>0.01617954070981211</v>
+        <v>0.2083730916030534</v>
       </c>
       <c r="X16">
-        <v>0.02590282825446</v>
+        <v>0.07395155039203966</v>
       </c>
       <c r="Y16">
-        <v>-0.009723287544647886</v>
+        <v>0.1344215412110138</v>
       </c>
       <c r="Z16">
-        <v>1.447585796427449</v>
+        <v>0.0782198365084377</v>
       </c>
       <c r="AA16">
-        <v>0.0003069492879463745</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.02608300555974823</v>
+        <v>0.0493452160921329</v>
       </c>
       <c r="AC16">
-        <v>-0.02577605627180185</v>
+        <v>-0.0493452160921329</v>
       </c>
       <c r="AD16">
-        <v>26</v>
+        <v>4589</v>
       </c>
       <c r="AE16">
-        <v>0.05814396858142837</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>26.05814396858143</v>
+        <v>4589</v>
       </c>
       <c r="AG16">
-        <v>16.56814396858143</v>
+        <v>2437.4</v>
       </c>
       <c r="AH16">
-        <v>0.197173955278733</v>
+        <v>0.7461909949755281</v>
       </c>
       <c r="AI16">
-        <v>0.2168654001129963</v>
+        <v>0.743965111943323</v>
       </c>
       <c r="AJ16">
-        <v>0.135064764433258</v>
+        <v>0.6096090838606407</v>
       </c>
       <c r="AK16">
-        <v>0.1497101457966541</v>
+        <v>0.606816540941569</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
         <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>530.6122448979592</v>
-      </c>
-      <c r="AP16">
-        <v>338.1253871139068</v>
       </c>
     </row>
     <row r="17">
@@ -2499,7 +2514,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>S&amp;U plc (LSE:SUS)</t>
+          <t>OSB Group Plc (LSE:OSB)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2508,10 +2523,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.09279999999999999</v>
+        <v>0.268</v>
       </c>
       <c r="E17">
-        <v>0.0737</v>
+        <v>0.3</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2526,85 +2541,85 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>35.8</v>
+        <v>477.2</v>
       </c>
       <c r="L17">
-        <v>0.3205013428827215</v>
+        <v>0.5689079637577492</v>
       </c>
       <c r="M17">
-        <v>15.2</v>
+        <v>195.4</v>
       </c>
       <c r="N17">
-        <v>0.03423423423423423</v>
+        <v>0.07878396903475526</v>
       </c>
       <c r="O17">
-        <v>0.4245810055865922</v>
+        <v>0.4094719195305951</v>
       </c>
       <c r="P17">
-        <v>15.2</v>
+        <v>147.3</v>
       </c>
       <c r="Q17">
-        <v>0.03423423423423423</v>
+        <v>0.05939037174421419</v>
       </c>
       <c r="R17">
-        <v>0.4245810055865922</v>
+        <v>0.3086756077116513</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>48.09999999999999</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>0.2461617195496417</v>
       </c>
       <c r="U17">
-        <v>0.001</v>
+        <v>3600.6</v>
       </c>
       <c r="V17">
-        <v>2.252252252252252e-06</v>
+        <v>1.451737763083622</v>
       </c>
       <c r="W17">
-        <v>0.1564685314685315</v>
+        <v>0.2014692223254243</v>
       </c>
       <c r="X17">
-        <v>0.02676176332996038</v>
+        <v>0.07092244382264945</v>
       </c>
       <c r="Y17">
-        <v>0.1297067681385711</v>
+        <v>0.1305467785027749</v>
       </c>
       <c r="Z17">
-        <v>0.3002324987568708</v>
+        <v>0.1630542542231207</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.02577963390806707</v>
+        <v>0.04936003524736748</v>
       </c>
       <c r="AC17">
-        <v>-0.02577963390806707</v>
+        <v>-0.04936003524736748</v>
       </c>
       <c r="AD17">
-        <v>161.3</v>
+        <v>6378.4</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>161.3</v>
+        <v>6378.4</v>
       </c>
       <c r="AG17">
-        <v>161.299</v>
+        <v>2777.8</v>
       </c>
       <c r="AH17">
-        <v>0.2664794316867669</v>
+        <v>0.7200234800081278</v>
       </c>
       <c r="AI17">
-        <v>0.3804245283018868</v>
+        <v>0.7203894241086052</v>
       </c>
       <c r="AJ17">
-        <v>0.2664782198549808</v>
+        <v>0.5282997337390642</v>
       </c>
       <c r="AK17">
-        <v>0.3804230670355355</v>
+        <v>0.52875226039783</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2621,7 +2636,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Time Finance plc (AIM:TIME)</t>
+          <t>Orchard Funding Group plc (AIM:ORCH)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2630,13 +2645,13 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.135</v>
+        <v>0.06</v>
       </c>
       <c r="E18">
-        <v>-0.09119999999999999</v>
+        <v>0.0256</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>0.001596516690856313</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -2648,88 +2663,91 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>2.52</v>
+        <v>1.85</v>
       </c>
       <c r="L18">
-        <v>0.07522388059701493</v>
+        <v>0.2685050798258345</v>
       </c>
       <c r="M18">
-        <v>-0</v>
+        <v>0.78</v>
       </c>
       <c r="N18">
-        <v>-0</v>
+        <v>0.06446280991735538</v>
       </c>
       <c r="O18">
-        <v>-0</v>
+        <v>0.4216216216216216</v>
       </c>
       <c r="P18">
-        <v>-0</v>
+        <v>0.78</v>
       </c>
       <c r="Q18">
-        <v>-0</v>
+        <v>0.06446280991735538</v>
       </c>
       <c r="R18">
-        <v>-0</v>
+        <v>0.4216216216216216</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
       <c r="U18">
-        <v>11.3</v>
+        <v>5.84</v>
       </c>
       <c r="V18">
-        <v>0.3883161512027491</v>
+        <v>0.4826446280991736</v>
       </c>
       <c r="W18">
-        <v>0.03695014662756598</v>
+        <v>0.08409090909090909</v>
       </c>
       <c r="X18">
-        <v>0.02597381677205812</v>
+        <v>0.07091026831185523</v>
       </c>
       <c r="Y18">
-        <v>0.01097632985550787</v>
+        <v>0.01318064077905386</v>
       </c>
       <c r="Z18">
-        <v>0.9517045454545452</v>
+        <v>0.1909645232815965</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.0261452397039909</v>
+        <v>0.04936010098146149</v>
       </c>
       <c r="AC18">
-        <v>-0.0261452397039909</v>
+        <v>-0.04936010098146149</v>
       </c>
       <c r="AD18">
-        <v>7.43</v>
+        <v>31.1</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>7.43</v>
+        <v>31.1</v>
       </c>
       <c r="AG18">
-        <v>-3.870000000000001</v>
+        <v>25.26</v>
       </c>
       <c r="AH18">
-        <v>0.2033944702983849</v>
+        <v>0.7199074074074074</v>
       </c>
       <c r="AI18">
-        <v>0.0839263526488196</v>
+        <v>0.6050583657587548</v>
       </c>
       <c r="AJ18">
-        <v>-0.1533888228299644</v>
+        <v>0.6761241970021413</v>
       </c>
       <c r="AK18">
-        <v>-0.05011006085717987</v>
+        <v>0.5544337137840211</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="AQ18">
         <v>-0</v>
@@ -2743,7 +2761,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Orchard Funding Group plc (AIM:ORCH)</t>
+          <t>S&amp;U plc (LSE:SUS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2752,13 +2770,13 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.066</v>
+        <v>0.0583</v>
       </c>
       <c r="E19">
-        <v>-0.0353</v>
+        <v>0.117</v>
       </c>
       <c r="G19">
-        <v>0.002750809061488673</v>
+        <v>0</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -2770,28 +2788,28 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>1.17</v>
+        <v>47.4</v>
       </c>
       <c r="L19">
-        <v>0.1893203883495146</v>
+        <v>0.4336688014638609</v>
       </c>
       <c r="M19">
-        <v>0.891</v>
+        <v>18.6</v>
       </c>
       <c r="N19">
-        <v>0.0597986577181208</v>
+        <v>0.0607843137254902</v>
       </c>
       <c r="O19">
-        <v>0.7615384615384616</v>
+        <v>0.3924050632911393</v>
       </c>
       <c r="P19">
-        <v>0.891</v>
+        <v>18.6</v>
       </c>
       <c r="Q19">
-        <v>0.0597986577181208</v>
+        <v>0.0607843137254902</v>
       </c>
       <c r="R19">
-        <v>0.7615384615384616</v>
+        <v>0.3924050632911393</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2800,55 +2818,55 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>3.02</v>
+        <v>1.39</v>
       </c>
       <c r="V19">
-        <v>0.2026845637583893</v>
+        <v>0.004542483660130718</v>
       </c>
       <c r="W19">
-        <v>0.05707317073170731</v>
+        <v>0.1804339550818424</v>
       </c>
       <c r="X19">
-        <v>0.03248634132832596</v>
+        <v>0.05487803927626576</v>
       </c>
       <c r="Y19">
-        <v>0.02458682940338135</v>
+        <v>0.1255559158055767</v>
       </c>
       <c r="Z19">
-        <v>0.192643391521197</v>
+        <v>0.2577836268481765</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.02745779184162348</v>
+        <v>0.04955079101201422</v>
       </c>
       <c r="AC19">
-        <v>-0.02745779184162348</v>
+        <v>-0.04955079101201422</v>
       </c>
       <c r="AD19">
-        <v>17.1</v>
+        <v>190.1</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>17.1</v>
+        <v>190.1</v>
       </c>
       <c r="AG19">
-        <v>14.08</v>
+        <v>188.71</v>
       </c>
       <c r="AH19">
-        <v>0.534375</v>
+        <v>0.3831888732110461</v>
       </c>
       <c r="AI19">
-        <v>0.4373401534526855</v>
+        <v>0.4236683753064407</v>
       </c>
       <c r="AJ19">
-        <v>0.4858523119392685</v>
+        <v>0.3814558023892786</v>
       </c>
       <c r="AK19">
-        <v>0.3902439024390245</v>
+        <v>0.4218774451722518</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2865,7 +2883,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OSB Group Plc (LSE:OSB)</t>
+          <t>Distribution Finance Capital Holdings plc (AIM:DFCH)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2873,15 +2891,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D20">
-        <v>0.217</v>
-      </c>
-      <c r="E20">
-        <v>0.187</v>
-      </c>
-      <c r="F20">
-        <v>0.302</v>
-      </c>
       <c r="G20">
         <v>0</v>
       </c>
@@ -2889,103 +2898,94 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0.0001450033606033056</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>0.0001082180090098016</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>394.7</v>
+        <v>-1.62</v>
       </c>
       <c r="L20">
-        <v>0.5180469877936738</v>
+        <v>-0.09818181818181819</v>
       </c>
       <c r="M20">
-        <v>89.5</v>
+        <v>-0</v>
       </c>
       <c r="N20">
-        <v>0.02657047856549103</v>
+        <v>-0</v>
       </c>
       <c r="O20">
-        <v>0.2267544970863947</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>89.5</v>
+        <v>-0</v>
       </c>
       <c r="Q20">
-        <v>0.02657047856549103</v>
+        <v>-0</v>
       </c>
       <c r="R20">
-        <v>0.2267544970863947</v>
+        <v>0</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
       <c r="U20">
-        <v>3043.9</v>
+        <v>83.2</v>
       </c>
       <c r="V20">
-        <v>0.9036634603966275</v>
+        <v>1.170182841068917</v>
       </c>
       <c r="W20">
-        <v>0.2059590899603423</v>
+        <v>-0.01342170671085336</v>
       </c>
       <c r="X20">
-        <v>0.03672008042975807</v>
+        <v>0.04983790867631634</v>
       </c>
       <c r="Y20">
-        <v>0.1692390095305842</v>
+        <v>-0.0632596153871697</v>
       </c>
       <c r="Z20">
-        <v>0.187496957248896</v>
+        <v>0.2249979545640494</v>
       </c>
       <c r="AA20">
-        <v>2.029054740887142e-05</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.03044726596904983</v>
+        <v>0.04976301200890947</v>
       </c>
       <c r="AC20">
-        <v>-0.03042697542164096</v>
+        <v>-0.04976301200890947</v>
       </c>
       <c r="AD20">
-        <v>5819.6</v>
+        <v>0.606</v>
       </c>
       <c r="AE20">
-        <v>0.1326096977817074</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>5819.732609697782</v>
+        <v>0.606</v>
       </c>
       <c r="AG20">
-        <v>2775.832609697782</v>
+        <v>-82.59400000000001</v>
       </c>
       <c r="AH20">
-        <v>0.6333966712186151</v>
+        <v>0.008451175633838173</v>
       </c>
       <c r="AI20">
-        <v>0.7036112855627242</v>
+        <v>0.005760127749367907</v>
       </c>
       <c r="AJ20">
-        <v>0.4517785679722691</v>
+        <v>7.185836088393937</v>
       </c>
       <c r="AK20">
-        <v>0.5310227637988904</v>
+        <v>-3.753249113878036</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
         <v>0</v>
-      </c>
-      <c r="AN20">
-        <v>42478.83211678832</v>
-      </c>
-      <c r="AP20">
-        <v>20261.55189560425</v>
       </c>
     </row>
     <row r="21">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Provident Financial plc (LSE:PFG)</t>
+          <t>Time Finance plc (AIM:TIME)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3005,7 +3005,10 @@
         </is>
       </c>
       <c r="D21">
-        <v>-0.174</v>
+        <v>0.05690000000000001</v>
+      </c>
+      <c r="E21">
+        <v>-0.225</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3020,19 +3023,19 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>-151.6</v>
+        <v>1.16</v>
       </c>
       <c r="L21">
-        <v>-0.27222122463638</v>
+        <v>0.04142857142857143</v>
       </c>
       <c r="M21">
-        <v>0.414</v>
+        <v>-0</v>
       </c>
       <c r="N21">
-        <v>0.000339344262295082</v>
+        <v>-0</v>
       </c>
       <c r="O21">
-        <v>-0.002730870712401056</v>
+        <v>-0</v>
       </c>
       <c r="P21">
         <v>-0</v>
@@ -3041,70 +3044,70 @@
         <v>-0</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S21">
-        <v>0.414</v>
-      </c>
-      <c r="T21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>670.9</v>
+        <v>3.99</v>
       </c>
       <c r="V21">
-        <v>0.5499180327868852</v>
+        <v>0.1734782608695652</v>
       </c>
       <c r="W21">
-        <v>-0.1637149028077754</v>
+        <v>0.01430332922318126</v>
       </c>
       <c r="X21">
-        <v>0.03811546161945085</v>
+        <v>0.05168477842645464</v>
       </c>
       <c r="Y21">
-        <v>-0.2018303644272262</v>
+        <v>-0.03738144920327338</v>
       </c>
       <c r="Z21">
-        <v>0.2139372286888709</v>
+        <v>0.7541071909507137</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.03068750345511838</v>
+        <v>0.05075223147187594</v>
       </c>
       <c r="AC21">
-        <v>-0.03068750345511838</v>
+        <v>-0.05075223147187594</v>
       </c>
       <c r="AD21">
-        <v>2341.1</v>
+        <v>5.36</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>2341.1</v>
+        <v>5.36</v>
       </c>
       <c r="AG21">
-        <v>1670.2</v>
+        <v>1.37</v>
       </c>
       <c r="AH21">
-        <v>0.6574092274858891</v>
+        <v>0.1889985895627645</v>
       </c>
       <c r="AI21">
-        <v>0.7376098805885504</v>
+        <v>0.06831506500127454</v>
       </c>
       <c r="AJ21">
-        <v>0.577883883468272</v>
+        <v>0.05621665982765696</v>
       </c>
       <c r="AK21">
-        <v>0.6672792648821414</v>
+        <v>0.01839666979991943</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>-0.001</v>
+      </c>
+      <c r="AQ21">
+        <v>-0</v>
       </c>
     </row>
     <row r="22">
@@ -3115,7 +3118,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Paragon Banking Group PLC (LSE:PAG)</t>
+          <t>Nationwide Building Society (LSE:NBS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3124,13 +3127,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.0697</v>
+        <v>0.0507</v>
       </c>
       <c r="E22">
-        <v>0.07240000000000001</v>
-      </c>
-      <c r="F22">
-        <v>0.06</v>
+        <v>0.123</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3145,85 +3145,85 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>222.1</v>
+        <v>1443</v>
       </c>
       <c r="L22">
-        <v>0.4724526696447564</v>
+        <v>0.3215742205780759</v>
       </c>
       <c r="M22">
-        <v>130.7</v>
+        <v>207.3</v>
       </c>
       <c r="N22">
-        <v>0.06900010558547143</v>
+        <v>0.1302790346907994</v>
       </c>
       <c r="O22">
-        <v>0.5884736605132823</v>
+        <v>0.1436590436590437</v>
       </c>
       <c r="P22">
-        <v>73.7</v>
+        <v>207.3</v>
       </c>
       <c r="Q22">
-        <v>0.0389082462253194</v>
+        <v>0.1302790346907994</v>
       </c>
       <c r="R22">
-        <v>0.3318325078793337</v>
+        <v>0.1436590436590437</v>
       </c>
       <c r="S22">
-        <v>56.99999999999999</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>0.4361132364192807</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>1836.4</v>
+        <v>37507.1</v>
       </c>
       <c r="V22">
-        <v>0.9694857987540915</v>
+        <v>23.5715811965812</v>
       </c>
       <c r="W22">
-        <v>0.1485718108234664</v>
+        <v>0.07172395967950375</v>
       </c>
       <c r="X22">
-        <v>0.04754515491521076</v>
+        <v>0.3020690273052963</v>
       </c>
       <c r="Y22">
-        <v>0.1010266559082557</v>
+        <v>-0.2303450676257925</v>
       </c>
       <c r="Z22">
-        <v>0.06689529555738966</v>
+        <v>0.1254350238581759</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.03173914559730122</v>
+        <v>0.05197937462730839</v>
       </c>
       <c r="AC22">
-        <v>-0.03173914559730122</v>
+        <v>-0.05197937462730839</v>
       </c>
       <c r="AD22">
-        <v>6082.2</v>
+        <v>48804.9</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>6082.2</v>
+        <v>48804.9</v>
       </c>
       <c r="AG22">
-        <v>4245.799999999999</v>
+        <v>11297.8</v>
       </c>
       <c r="AH22">
-        <v>0.762524447119001</v>
+        <v>0.9684261282123022</v>
       </c>
       <c r="AI22">
-        <v>0.7838896765047042</v>
+        <v>0.7289263604388054</v>
       </c>
       <c r="AJ22">
-        <v>0.6914983713355048</v>
+        <v>0.8765458918457599</v>
       </c>
       <c r="AK22">
-        <v>0.7168810995171039</v>
+        <v>0.383660357111324</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Non-Standard Finance plc (LSE:NSF)</t>
+          <t>Provident Financial plc (LSE:PFG)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3248,8 +3248,14 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D23">
+        <v>-0.0668</v>
+      </c>
+      <c r="E23">
+        <v>-0.283</v>
+      </c>
       <c r="G23">
-        <v>0.01390374331550802</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -3261,82 +3267,85 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>-56.2</v>
+        <v>47.4</v>
       </c>
       <c r="L23">
-        <v>-0.3005347593582888</v>
+        <v>0.08735716918540361</v>
       </c>
       <c r="M23">
-        <v>-0</v>
+        <v>36.6</v>
       </c>
       <c r="N23">
-        <v>-0</v>
+        <v>0.06329989622967831</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>0.7721518987341772</v>
       </c>
       <c r="P23">
-        <v>-0</v>
+        <v>36.6</v>
       </c>
       <c r="Q23">
-        <v>-0</v>
+        <v>0.06329989622967831</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>0.7721518987341772</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
       <c r="U23">
-        <v>143.2</v>
+        <v>679.9</v>
       </c>
       <c r="V23">
-        <v>13.38317757009346</v>
+        <v>1.175890695261155</v>
       </c>
       <c r="W23">
-        <v>-2.058608058608059</v>
+        <v>0.0569164265129683</v>
       </c>
       <c r="X23">
-        <v>0.3423061188015258</v>
+        <v>0.08098533434674891</v>
       </c>
       <c r="Y23">
-        <v>-2.400914177409585</v>
+        <v>-0.02406890783378061</v>
       </c>
       <c r="Z23">
-        <v>0.5080141265960336</v>
+        <v>0.2256414521561942</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.03630318869799194</v>
+        <v>0.05389021797611744</v>
       </c>
       <c r="AC23">
-        <v>-0.03630318869799194</v>
+        <v>-0.05389021797611744</v>
       </c>
       <c r="AD23">
-        <v>466.5</v>
+        <v>2194.3</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>466.5</v>
+        <v>2194.3</v>
       </c>
       <c r="AG23">
-        <v>323.3</v>
+        <v>1514.4</v>
       </c>
       <c r="AH23">
-        <v>0.9775775356244761</v>
+        <v>0.7914517583408477</v>
       </c>
       <c r="AI23">
-        <v>1.057343608340888</v>
+        <v>0.7501880341880343</v>
       </c>
       <c r="AJ23">
-        <v>0.9679640718562874</v>
+        <v>0.7236930134760584</v>
       </c>
       <c r="AK23">
-        <v>1.08489932885906</v>
+        <v>0.6745356554273751</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3353,7 +3362,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Curtis Banks Group plc (AIM:CBP)</t>
+          <t>LendInvest plc (AIM:LINV)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3361,47 +3370,41 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D24">
-        <v>-0.016</v>
-      </c>
-      <c r="E24">
-        <v>0.152</v>
-      </c>
       <c r="G24">
-        <v>0.2266903914590747</v>
+        <v>0.02453245324532453</v>
       </c>
       <c r="H24">
-        <v>0.2218268090154211</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>0.1862396204033215</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>0.1527164887307236</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>9.02</v>
+        <v>16.7</v>
       </c>
       <c r="L24">
-        <v>0.1069988137603796</v>
+        <v>0.1837183718371837</v>
       </c>
       <c r="M24">
-        <v>8.26</v>
+        <v>6.8</v>
       </c>
       <c r="N24">
-        <v>0.03441666666666666</v>
+        <v>0.05</v>
       </c>
       <c r="O24">
-        <v>0.9157427937915743</v>
+        <v>0.407185628742515</v>
       </c>
       <c r="P24">
-        <v>8.26</v>
+        <v>6.8</v>
       </c>
       <c r="Q24">
-        <v>0.03441666666666666</v>
+        <v>0.05</v>
       </c>
       <c r="R24">
-        <v>0.9157427937915743</v>
+        <v>0.407185628742515</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -3410,73 +3413,64 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>554</v>
+        <v>126.2</v>
       </c>
       <c r="V24">
-        <v>2.308333333333333</v>
+        <v>0.9279411764705883</v>
       </c>
       <c r="W24">
-        <v>0.1340267459138187</v>
+        <v>0.1160528144544823</v>
       </c>
       <c r="X24">
-        <v>0.02823697325584315</v>
+        <v>0.1324557212632135</v>
       </c>
       <c r="Y24">
-        <v>0.1057897726579756</v>
+        <v>-0.0164029068087312</v>
       </c>
       <c r="Z24">
-        <v>-0.2063142437591777</v>
+        <v>0.06283265362549251</v>
       </c>
       <c r="AA24">
-        <v>-0.03150758688203623</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.02637293744278734</v>
+        <v>0.05450519949981583</v>
       </c>
       <c r="AC24">
-        <v>-0.05788052432482357</v>
+        <v>-0.05450519949981583</v>
       </c>
       <c r="AD24">
-        <v>135.7</v>
+        <v>1367.1</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>135.7</v>
+        <v>1367.1</v>
       </c>
       <c r="AG24">
-        <v>-418.3</v>
+        <v>1240.9</v>
       </c>
       <c r="AH24">
-        <v>0.3611924407772159</v>
+        <v>0.9095203246623644</v>
       </c>
       <c r="AI24">
-        <v>0.5505070993914807</v>
+        <v>0.9532143355180589</v>
       </c>
       <c r="AJ24">
-        <v>2.346045989904655</v>
+        <v>0.9012273948725398</v>
       </c>
       <c r="AK24">
-        <v>1.360325203252033</v>
+        <v>0.9487003058103977</v>
       </c>
       <c r="AL24">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AM24">
-        <v>2.006</v>
-      </c>
-      <c r="AN24">
-        <v>7.031088082901554</v>
-      </c>
-      <c r="AO24">
-        <v>7.621359223300971</v>
-      </c>
-      <c r="AP24">
-        <v>-21.67357512953368</v>
+        <v>-0.223</v>
       </c>
       <c r="AQ24">
-        <v>7.826520438683947</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="25">
@@ -3487,7 +3481,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TruFin plc (AIM:TRU)</t>
+          <t>Morses Club PLC (AIM:MCL)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3495,113 +3489,113 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D25">
+        <v>-0.0108</v>
+      </c>
       <c r="G25">
-        <v>-0.1427906976744186</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>-0.1427906976744186</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>-0.1288372093023256</v>
+        <v>0.0006976399905056576</v>
       </c>
       <c r="J25">
-        <v>-0.1288372093023256</v>
+        <v>0.0006976399905056576</v>
       </c>
       <c r="K25">
-        <v>-14.9</v>
+        <v>-60.7</v>
       </c>
       <c r="L25">
-        <v>-0.6930232558139535</v>
+        <v>-0.5148430873621713</v>
       </c>
       <c r="M25">
-        <v>-0</v>
+        <v>1.58</v>
       </c>
       <c r="N25">
-        <v>-0</v>
+        <v>0.8229166666666667</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>-0.02602965403624382</v>
       </c>
       <c r="P25">
-        <v>-0</v>
+        <v>1.58</v>
       </c>
       <c r="Q25">
-        <v>-0</v>
+        <v>0.8229166666666667</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>-0.02602965403624382</v>
       </c>
       <c r="S25">
         <v>0</v>
       </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
       <c r="U25">
-        <v>16.9</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="V25">
-        <v>0.1918274687854711</v>
+        <v>4.875</v>
       </c>
       <c r="W25">
-        <v>-0.2754158964879852</v>
+        <v>-0.6450584484590861</v>
       </c>
       <c r="X25">
-        <v>0.02549380853261911</v>
+        <v>0.1264298841819819</v>
       </c>
       <c r="Y25">
-        <v>-0.3009097050206043</v>
+        <v>-0.771488332641068</v>
       </c>
       <c r="Z25">
-        <v>0.7026143790849673</v>
+        <v>1.267690938518407</v>
       </c>
       <c r="AA25">
-        <v>-0.09052287581699346</v>
+        <v>0.0008843918943120895</v>
       </c>
       <c r="AB25">
-        <v>0.02570460116385204</v>
+        <v>0.06469932512492069</v>
       </c>
       <c r="AC25">
-        <v>-0.1162274769808455</v>
+        <v>-0.06381493323060859</v>
       </c>
       <c r="AD25">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>0.09374122559691486</v>
       </c>
       <c r="AF25">
-        <v>16.7</v>
+        <v>17.89374122559692</v>
       </c>
       <c r="AG25">
-        <v>-0.1999999999999993</v>
+        <v>8.533741225596916</v>
       </c>
       <c r="AH25">
-        <v>0.1593511450381679</v>
+        <v>0.9030975534534793</v>
       </c>
       <c r="AI25">
-        <v>0.2585139318885449</v>
+        <v>0.4916708374299167</v>
       </c>
       <c r="AJ25">
-        <v>-0.002275312855517626</v>
+        <v>0.8163336973275453</v>
       </c>
       <c r="AK25">
-        <v>-0.004192872117400404</v>
+        <v>0.3156700049165499</v>
       </c>
       <c r="AL25">
-        <v>9.18</v>
+        <v>0</v>
       </c>
       <c r="AM25">
-        <v>9.18</v>
+        <v>0</v>
       </c>
       <c r="AN25">
-        <v>-9.542857142857143</v>
-      </c>
-      <c r="AO25">
-        <v>-0.3017429193899782</v>
+        <v>176.2376237623762</v>
       </c>
       <c r="AP25">
-        <v>0.1142857142857139</v>
-      </c>
-      <c r="AQ25">
-        <v>-0.3017429193899782</v>
+        <v>84.49248738214769</v>
       </c>
     </row>
     <row r="26">
@@ -3612,7 +3606,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>City of London Group plc (AIM:CIN)</t>
+          <t>Non-Standard Finance plc (LSE:NSF)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3620,23 +3614,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D26">
+        <v>0.0756</v>
+      </c>
       <c r="G26">
-        <v>-5.394190871369294</v>
+        <v>0.07415730337078652</v>
       </c>
       <c r="H26">
-        <v>-5.394190871369294</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>-6.597510373443983</v>
+        <v>0</v>
       </c>
       <c r="J26">
-        <v>-6.597510373443983</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>-21.6</v>
+        <v>-70.90000000000001</v>
       </c>
       <c r="L26">
-        <v>-8.962655601659751</v>
+        <v>-0.6127917026793431</v>
       </c>
       <c r="M26">
         <v>-0</v>
@@ -3660,73 +3657,61 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>33.4</v>
+        <v>135.4</v>
       </c>
       <c r="V26">
-        <v>0.4684431977559607</v>
+        <v>71.64021164021165</v>
       </c>
       <c r="W26">
-        <v>-0.6813880126182966</v>
+        <v>2.802371541501977</v>
       </c>
       <c r="X26">
-        <v>0.02466309953379174</v>
+        <v>1.836822515088024</v>
       </c>
       <c r="Y26">
-        <v>-0.7060511121520884</v>
+        <v>0.9655490264139523</v>
       </c>
       <c r="Z26">
-        <v>0.02284576737131482</v>
+        <v>0.388255033557047</v>
       </c>
       <c r="AA26">
-        <v>-0.1507251872215376</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.02498846343435097</v>
+        <v>0.06622572312752834</v>
       </c>
       <c r="AC26">
-        <v>-0.1757136506558885</v>
+        <v>-0.06622572312752834</v>
       </c>
       <c r="AD26">
-        <v>5.4</v>
+        <v>410.6</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>5.4</v>
+        <v>410.6</v>
       </c>
       <c r="AG26">
-        <v>-28</v>
+        <v>275.2</v>
       </c>
       <c r="AH26">
-        <v>0.07040417209908735</v>
+        <v>0.9954180707411089</v>
       </c>
       <c r="AI26">
-        <v>0.08294930875576036</v>
+        <v>1.296904611497157</v>
       </c>
       <c r="AJ26">
-        <v>-0.6466512702078523</v>
+        <v>0.9931791114800246</v>
       </c>
       <c r="AK26">
-        <v>-0.8832807570977917</v>
+        <v>1.518763796909492</v>
       </c>
       <c r="AL26">
-        <v>0.594</v>
+        <v>0</v>
       </c>
       <c r="AM26">
-        <v>0.594</v>
-      </c>
-      <c r="AN26">
-        <v>-0.3439490445859873</v>
-      </c>
-      <c r="AO26">
-        <v>-26.76767676767677</v>
-      </c>
-      <c r="AP26">
-        <v>1.78343949044586</v>
-      </c>
-      <c r="AQ26">
-        <v>-26.76767676767677</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3737,7 +3722,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Amigo Holdings PLC (LSE:AMGO)</t>
+          <t>TruFin plc (AIM:TRU)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3745,23 +3730,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D27">
+        <v>0.421</v>
+      </c>
       <c r="G27">
-        <v>-1.905101481075151</v>
+        <v>-0.07613636363636364</v>
       </c>
       <c r="H27">
-        <v>-1.905101481075151</v>
+        <v>-0.07613636363636364</v>
       </c>
       <c r="I27">
-        <v>-1.466264399341744</v>
+        <v>-0.1443181818181818</v>
       </c>
       <c r="J27">
-        <v>-1.466264399341744</v>
+        <v>-0.1443181818181818</v>
       </c>
       <c r="K27">
-        <v>-294.2</v>
+        <v>-6.99</v>
       </c>
       <c r="L27">
-        <v>-1.613823368074602</v>
+        <v>-0.3971590909090909</v>
       </c>
       <c r="M27">
         <v>-0</v>
@@ -3785,73 +3773,73 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>316.6</v>
+        <v>15.7</v>
       </c>
       <c r="V27">
-        <v>8.223376623376623</v>
+        <v>0.2079470198675497</v>
       </c>
       <c r="W27">
-        <v>-2.28416149068323</v>
+        <v>-0.1509719222462203</v>
       </c>
       <c r="X27">
-        <v>0.08384333055671166</v>
+        <v>0.05199041145181046</v>
       </c>
       <c r="Y27">
-        <v>-2.368004821239941</v>
+        <v>-0.2029623336980308</v>
       </c>
       <c r="Z27">
-        <v>0.3846803123021734</v>
+        <v>0.7242798353909465</v>
       </c>
       <c r="AA27">
-        <v>-0.5640430470563409</v>
+        <v>-0.1045267489711934</v>
       </c>
       <c r="AB27">
-        <v>0.0510010520679615</v>
+        <v>0.05087579699253563</v>
       </c>
       <c r="AC27">
-        <v>-0.6150440991243024</v>
+        <v>-0.155402545963729</v>
       </c>
       <c r="AD27">
-        <v>315.1</v>
+        <v>20.4</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>315.1</v>
+        <v>20.4</v>
       </c>
       <c r="AG27">
-        <v>-1.5</v>
+        <v>4.699999999999999</v>
       </c>
       <c r="AH27">
-        <v>0.8911199095022625</v>
+        <v>0.2127215849843587</v>
       </c>
       <c r="AI27">
-        <v>2.015994881637876</v>
+        <v>0.2837273991655076</v>
       </c>
       <c r="AJ27">
-        <v>-0.04054054054054054</v>
+        <v>0.05860349127182043</v>
       </c>
       <c r="AK27">
-        <v>0.009357454772301934</v>
+        <v>0.08362989323843414</v>
       </c>
       <c r="AL27">
-        <v>26.2</v>
+        <v>7.25</v>
       </c>
       <c r="AM27">
-        <v>25.93</v>
+        <v>7.25</v>
       </c>
       <c r="AN27">
-        <v>-1.183251971460759</v>
+        <v>-17.14285714285714</v>
       </c>
       <c r="AO27">
-        <v>-10.20229007633588</v>
+        <v>-0.3503448275862069</v>
       </c>
       <c r="AP27">
-        <v>0.005632745024408562</v>
+        <v>-3.949579831932773</v>
       </c>
       <c r="AQ27">
-        <v>-10.30852294639414</v>
+        <v>-0.3503448275862069</v>
       </c>
     </row>
     <row r="28">
@@ -3862,7 +3850,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Appreciate Group plc (AIM:APP)</t>
+          <t>M&amp;G plc (LSE:MNG)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3870,122 +3858,354 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D28">
-        <v>-0.168</v>
-      </c>
-      <c r="E28">
-        <v>-0.16</v>
-      </c>
-      <c r="G28">
-        <v>0.02121771217712177</v>
-      </c>
-      <c r="H28">
-        <v>0.02121771217712177</v>
-      </c>
-      <c r="I28">
-        <v>0.0472939729397294</v>
-      </c>
-      <c r="J28">
-        <v>0.03692641730206206</v>
+      <c r="F28">
+        <v>-0.07980000000000001</v>
       </c>
       <c r="K28">
-        <v>5.76</v>
-      </c>
-      <c r="L28">
-        <v>0.03542435424354243</v>
+        <v>-871.3</v>
       </c>
       <c r="M28">
-        <v>2.32</v>
+        <v>670.8</v>
       </c>
       <c r="N28">
-        <v>0.03706070287539936</v>
+        <v>0.1292012558023074</v>
       </c>
       <c r="O28">
-        <v>0.4027777777777778</v>
+        <v>-0.7698840812578905</v>
       </c>
       <c r="P28">
-        <v>2.32</v>
+        <v>567.5</v>
       </c>
       <c r="Q28">
-        <v>0.03706070287539936</v>
+        <v>0.1093048787534429</v>
       </c>
       <c r="R28">
-        <v>0.4027777777777778</v>
+        <v>-0.6513256054171928</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>0.1539952295766249</v>
       </c>
       <c r="U28">
-        <v>6.21</v>
+        <v>6911.7</v>
       </c>
       <c r="V28">
-        <v>0.09920127795527156</v>
+        <v>1.331246749744795</v>
       </c>
       <c r="W28">
-        <v>0.3310344827586207</v>
+        <v>-0.1239420190898875</v>
       </c>
       <c r="X28">
-        <v>0.02510483883036813</v>
+        <v>0.06581833473781512</v>
       </c>
       <c r="Y28">
-        <v>0.3059296439282526</v>
+        <v>-0.1897603538277026</v>
       </c>
       <c r="Z28">
-        <v>-15.97249508840865</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>-0.5898070189897143</v>
+        <v>-0.1363449766919969</v>
       </c>
       <c r="AB28">
-        <v>0.0253101186385209</v>
+        <v>0.05221982390853745</v>
       </c>
       <c r="AC28">
-        <v>-0.6151171376282353</v>
+        <v>-0.1885648006005343</v>
       </c>
       <c r="AD28">
-        <v>8.529999999999999</v>
+        <v>10130.6</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>8.529999999999999</v>
+        <v>10130.6</v>
       </c>
       <c r="AG28">
-        <v>2.319999999999999</v>
+        <v>3218.900000000001</v>
       </c>
       <c r="AH28">
-        <v>0.1199212709124139</v>
+        <v>0.6611584271496166</v>
       </c>
       <c r="AI28">
-        <v>0.305406373075546</v>
+        <v>0.6775278719661859</v>
       </c>
       <c r="AJ28">
-        <v>0.03573629081947011</v>
+        <v>0.382710324820469</v>
       </c>
       <c r="AK28">
-        <v>0.1068139963167587</v>
+        <v>0.4003308210830038</v>
       </c>
       <c r="AL28">
-        <v>0.27</v>
+        <v>390.1</v>
       </c>
       <c r="AM28">
-        <v>-0.4399999999999999</v>
+        <v>390.1</v>
       </c>
       <c r="AN28">
-        <v>1.01668653158522</v>
+        <v>-7.655558074510694</v>
       </c>
       <c r="AO28">
-        <v>28.48148148148148</v>
+        <v>-3.831325301204819</v>
       </c>
       <c r="AP28">
-        <v>0.2765196662693682</v>
+        <v>-2.432479407541752</v>
       </c>
       <c r="AQ28">
-        <v>-17.47727272727273</v>
+        <v>-3.831325301204819</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Insig AI Plc (AIM:INSG)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G29">
+        <v>-1.360406091370558</v>
+      </c>
+      <c r="H29">
+        <v>-1.360406091370558</v>
+      </c>
+      <c r="I29">
+        <v>-3.548223350253807</v>
+      </c>
+      <c r="J29">
+        <v>-3.548223350253807</v>
+      </c>
+      <c r="K29">
+        <v>-7.07</v>
+      </c>
+      <c r="L29">
+        <v>-3.588832487309645</v>
+      </c>
+      <c r="M29">
+        <v>-0</v>
+      </c>
+      <c r="N29">
+        <v>-0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>-0</v>
+      </c>
+      <c r="Q29">
+        <v>-0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0.167</v>
+      </c>
+      <c r="V29">
+        <v>0.008652849740932642</v>
+      </c>
+      <c r="W29">
+        <v>-0.1526997840172786</v>
+      </c>
+      <c r="X29">
+        <v>0.05050087887194694</v>
+      </c>
+      <c r="Y29">
+        <v>-0.2032006628892256</v>
+      </c>
+      <c r="Z29">
+        <v>0.04482162358937022</v>
+      </c>
+      <c r="AA29">
+        <v>-0.1590371314160903</v>
+      </c>
+      <c r="AB29">
+        <v>0.05042721441917038</v>
+      </c>
+      <c r="AC29">
+        <v>-0.2094643458352607</v>
+      </c>
+      <c r="AD29">
+        <v>1.72</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>1.72</v>
+      </c>
+      <c r="AG29">
+        <v>1.553</v>
+      </c>
+      <c r="AH29">
+        <v>0.08182683158896289</v>
+      </c>
+      <c r="AI29">
+        <v>0.04709748083242059</v>
+      </c>
+      <c r="AJ29">
+        <v>0.0744736968301923</v>
+      </c>
+      <c r="AK29">
+        <v>0.04271999559871262</v>
+      </c>
+      <c r="AL29">
+        <v>0.016</v>
+      </c>
+      <c r="AM29">
+        <v>0.016</v>
+      </c>
+      <c r="AN29">
+        <v>-0.296551724137931</v>
+      </c>
+      <c r="AO29">
+        <v>-436.875</v>
+      </c>
+      <c r="AP29">
+        <v>-0.2677586206896552</v>
+      </c>
+      <c r="AQ29">
+        <v>-436.875</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>City of London Group plc (AIM:CIN)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G30">
+        <v>-2.582677165354331</v>
+      </c>
+      <c r="H30">
+        <v>-2.582677165354331</v>
+      </c>
+      <c r="I30">
+        <v>-2.236220472440945</v>
+      </c>
+      <c r="J30">
+        <v>-2.236220472440945</v>
+      </c>
+      <c r="K30">
+        <v>-16.3</v>
+      </c>
+      <c r="L30">
+        <v>-2.566929133858268</v>
+      </c>
+      <c r="M30">
+        <v>-0</v>
+      </c>
+      <c r="N30">
+        <v>-0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>-0</v>
+      </c>
+      <c r="Q30">
+        <v>-0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>63.2</v>
+      </c>
+      <c r="V30">
+        <v>1.726775956284153</v>
+      </c>
+      <c r="W30">
+        <v>-0.2730318257956449</v>
+      </c>
+      <c r="X30">
+        <v>0.04995096928615156</v>
+      </c>
+      <c r="Y30">
+        <v>-0.3229827950817964</v>
+      </c>
+      <c r="Z30">
+        <v>0.2003154574132491</v>
+      </c>
+      <c r="AA30">
+        <v>-0.44794952681388</v>
+      </c>
+      <c r="AB30">
+        <v>0.04988125724766303</v>
+      </c>
+      <c r="AC30">
+        <v>-0.497830784061543</v>
+      </c>
+      <c r="AD30">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AG30">
+        <v>-62.38500000000001</v>
+      </c>
+      <c r="AH30">
+        <v>0.02178270747026594</v>
+      </c>
+      <c r="AI30">
+        <v>0.01798521460884917</v>
+      </c>
+      <c r="AJ30">
+        <v>2.419429901105294</v>
+      </c>
+      <c r="AK30">
+        <v>3.488118535085266</v>
+      </c>
+      <c r="AL30">
+        <v>2.11</v>
+      </c>
+      <c r="AM30">
+        <v>2.11</v>
+      </c>
+      <c r="AN30">
+        <v>-0.05821428571428571</v>
+      </c>
+      <c r="AO30">
+        <v>-6.729857819905213</v>
+      </c>
+      <c r="AP30">
+        <v>4.456071428571429</v>
+      </c>
+      <c r="AQ30">
+        <v>-6.729857819905213</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ30"/>
+  <dimension ref="A1:AQ36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0578</v>
+        <v>0.05690000000000001</v>
       </c>
       <c r="E2">
-        <v>0.05299999999999999</v>
+        <v>0.0655</v>
       </c>
       <c r="F2">
-        <v>-0.03490000000000001</v>
+        <v>0.141</v>
       </c>
       <c r="G2">
-        <v>0.3541512049331756</v>
+        <v>0.1624687098522762</v>
       </c>
       <c r="H2">
-        <v>0.3226027763920116</v>
+        <v>0.131042812172904</v>
       </c>
       <c r="I2">
-        <v>0.05897801368576295</v>
+        <v>0.1303669503897925</v>
       </c>
       <c r="J2">
-        <v>0.05296300614496161</v>
+        <v>0.1128499497648811</v>
       </c>
       <c r="K2">
-        <v>2876.54</v>
+        <v>3875.455</v>
       </c>
       <c r="L2">
-        <v>0.1638169239635798</v>
+        <v>0.146279116931158</v>
       </c>
       <c r="M2">
-        <v>2048.199</v>
+        <v>4040.614</v>
       </c>
       <c r="N2">
-        <v>0.03283648394543325</v>
+        <v>0.0428430619312626</v>
       </c>
       <c r="O2">
-        <v>0.71203564003977</v>
+        <v>1.042616673397059</v>
       </c>
       <c r="P2">
-        <v>1794.792</v>
+        <v>2043.604</v>
       </c>
       <c r="Q2">
-        <v>0.0287738929144053</v>
+        <v>0.02166855154562549</v>
       </c>
       <c r="R2">
-        <v>0.6239412627670743</v>
+        <v>0.5273197598733568</v>
       </c>
       <c r="S2">
-        <v>253.4069999999999</v>
+        <v>1997.01</v>
       </c>
       <c r="T2">
-        <v>0.1237218649164461</v>
+        <v>0.4942342921150103</v>
       </c>
       <c r="U2">
-        <v>55557.103</v>
+        <v>57389.305</v>
       </c>
       <c r="V2">
-        <v>0.8906848996187778</v>
+        <v>0.6085049322472077</v>
       </c>
       <c r="W2">
-        <v>0.06571883055549829</v>
+        <v>0.08183299456345527</v>
       </c>
       <c r="X2">
-        <v>0.05410321375043788</v>
+        <v>0.05407220800291207</v>
       </c>
       <c r="Y2">
-        <v>0.01161561680506042</v>
+        <v>0.0277607865605432</v>
       </c>
       <c r="Z2">
-        <v>0.2143043904380419</v>
+        <v>0.3772353012608923</v>
       </c>
       <c r="AA2">
-        <v>0.0004421959471560448</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0502328728939544</v>
+        <v>0.05191803360587496</v>
       </c>
       <c r="AC2">
-        <v>-0.04935262566975019</v>
+        <v>-0.05008599076553655</v>
       </c>
       <c r="AD2">
-        <v>85348.22200000001</v>
+        <v>88592.655</v>
       </c>
       <c r="AE2">
-        <v>0.09374122559691486</v>
+        <v>38.04493365078613</v>
       </c>
       <c r="AF2">
-        <v>85348.3157412256</v>
+        <v>88630.69993365079</v>
       </c>
       <c r="AG2">
-        <v>29791.2127412256</v>
+        <v>31241.39493365079</v>
       </c>
       <c r="AH2">
-        <v>0.5777551438432489</v>
+        <v>0.4844725132800895</v>
       </c>
       <c r="AI2">
-        <v>0.572122378401259</v>
+        <v>0.5585766541312916</v>
       </c>
       <c r="AJ2">
-        <v>0.3232310665819833</v>
+        <v>0.248829591001918</v>
       </c>
       <c r="AK2">
-        <v>0.3182096969893293</v>
+        <v>0.3084561547882018</v>
       </c>
       <c r="AL2">
-        <v>688.061</v>
+        <v>1022.419</v>
       </c>
       <c r="AM2">
-        <v>676.2750000000001</v>
+        <v>888.9549999999999</v>
       </c>
       <c r="AN2">
-        <v>37.31929585526371</v>
+        <v>14.72711273458944</v>
       </c>
       <c r="AO2">
-        <v>1.505013363640724</v>
+        <v>3.375233637090078</v>
       </c>
       <c r="AP2">
-        <v>13.02648205345039</v>
+        <v>5.193382512057084</v>
       </c>
       <c r="AQ2">
-        <v>1.531242467930945</v>
+        <v>3.88197715294925</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IntegraFin Holdings plc (LSE:IHP)</t>
+          <t>Fonix Mobile plc (AIM:FNX)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,115 +725,112 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.107</v>
+        <v>0.244</v>
       </c>
       <c r="E3">
-        <v>0.08039999999999999</v>
-      </c>
-      <c r="F3">
-        <v>0.01</v>
+        <v>0.303</v>
       </c>
       <c r="G3">
-        <v>0.1202149093351242</v>
+        <v>0.1778909090909091</v>
       </c>
       <c r="H3">
-        <v>0.1202149093351242</v>
+        <v>0.166060606060606</v>
       </c>
       <c r="I3">
-        <v>0.1128274009402283</v>
+        <v>0.1624242424242424</v>
       </c>
       <c r="J3">
-        <v>0.1128274009402283</v>
+        <v>0.1317048748353096</v>
       </c>
       <c r="K3">
-        <v>49</v>
+        <v>11.2</v>
       </c>
       <c r="L3">
-        <v>0.3290799194089993</v>
+        <v>0.1357575757575757</v>
       </c>
       <c r="M3">
-        <v>38.157</v>
+        <v>9.349</v>
       </c>
       <c r="N3">
-        <v>0.03162881299734748</v>
+        <v>0.02939937106918239</v>
       </c>
       <c r="O3">
-        <v>0.7787142857142858</v>
+        <v>0.8347321428571429</v>
       </c>
       <c r="P3">
-        <v>37.6</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="Q3">
-        <v>0.03116710875331565</v>
+        <v>0.02742138364779875</v>
       </c>
       <c r="R3">
-        <v>0.7673469387755102</v>
+        <v>0.7785714285714287</v>
       </c>
       <c r="S3">
-        <v>0.5570000000000022</v>
+        <v>0.6289999999999996</v>
       </c>
       <c r="T3">
-        <v>0.01459758366747915</v>
+        <v>0.06727992298641561</v>
       </c>
       <c r="U3">
-        <v>203.9</v>
+        <v>26.2</v>
       </c>
       <c r="V3">
-        <v>0.1690152519893899</v>
+        <v>0.08238993710691823</v>
       </c>
       <c r="W3">
-        <v>0.2223230490018149</v>
+        <v>1.178947368421053</v>
       </c>
       <c r="X3">
-        <v>0.04978907181466406</v>
+        <v>0.05191743648085267</v>
       </c>
       <c r="Y3">
-        <v>0.1725339771871508</v>
+        <v>1.1270299319402</v>
       </c>
       <c r="AB3">
-        <v>0.0497812340474739</v>
+        <v>0.05191652074385916</v>
       </c>
       <c r="AD3">
-        <v>3.12</v>
+        <v>0.022</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.12</v>
+        <v>0.022</v>
       </c>
       <c r="AG3">
-        <v>-200.78</v>
+        <v>-26.178</v>
       </c>
       <c r="AH3">
-        <v>0.002579535683576956</v>
+        <v>6.917760406512757e-05</v>
       </c>
       <c r="AI3">
-        <v>0.01590862737099735</v>
+        <v>0.001845327965106526</v>
       </c>
       <c r="AJ3">
-        <v>-0.1996579224756866</v>
+        <v>-0.08970536834097498</v>
       </c>
       <c r="AK3">
-        <v>25.80719794344473</v>
+        <v>1.833450063034038</v>
       </c>
       <c r="AL3">
-        <v>0.111</v>
+        <v>0.006</v>
       </c>
       <c r="AM3">
-        <v>-0.78</v>
+        <v>-0.427</v>
       </c>
       <c r="AN3">
-        <v>0.1743016759776536</v>
+        <v>0.001605839416058394</v>
       </c>
       <c r="AO3">
-        <v>151.3513513513514</v>
+        <v>2233.333333333333</v>
       </c>
       <c r="AP3">
-        <v>-11.21675977653631</v>
+        <v>-1.910802919708029</v>
       </c>
       <c r="AQ3">
-        <v>-21.53846153846154</v>
+        <v>-31.38173302107728</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Curtis Banks Group PLC (AIM:CBP)</t>
+          <t>IntegraFin Holdings plc (LSE:IHP)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,109 +850,112 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.32</v>
+        <v>0.0815</v>
+      </c>
+      <c r="E4">
+        <v>0.0868</v>
       </c>
       <c r="G4">
-        <v>0.2535286458333333</v>
+        <v>0.5127582017010937</v>
       </c>
       <c r="H4">
-        <v>0.2486979166666667</v>
+        <v>0.5127582017010937</v>
       </c>
       <c r="I4">
-        <v>0.1640625</v>
+        <v>0.5072904009720535</v>
       </c>
       <c r="J4">
-        <v>0.1640625</v>
+        <v>0.3387498401227857</v>
       </c>
       <c r="K4">
-        <v>-4.67</v>
+        <v>60.9</v>
       </c>
       <c r="L4">
-        <v>-0.06080729166666667</v>
+        <v>0.3699878493317132</v>
       </c>
       <c r="M4">
-        <v>8.41</v>
+        <v>42.93</v>
       </c>
       <c r="N4">
-        <v>0.03303220738413197</v>
+        <v>0.03354954673335418</v>
       </c>
       <c r="O4">
-        <v>-1.800856531049251</v>
+        <v>0.7049261083743843</v>
       </c>
       <c r="P4">
-        <v>7.27</v>
+        <v>41.1</v>
       </c>
       <c r="Q4">
-        <v>0.02855459544383346</v>
+        <v>0.03211941231634886</v>
       </c>
       <c r="R4">
-        <v>-1.556745182012848</v>
+        <v>0.6748768472906405</v>
       </c>
       <c r="S4">
-        <v>1.140000000000001</v>
+        <v>1.829999999999998</v>
       </c>
       <c r="T4">
-        <v>0.1355529131985732</v>
+        <v>0.04262753319357089</v>
       </c>
       <c r="U4">
-        <v>487.6</v>
+        <v>217.1</v>
       </c>
       <c r="V4">
-        <v>1.91516103692066</v>
+        <v>0.1696623944982807</v>
       </c>
       <c r="W4">
-        <v>-0.04218608852755194</v>
+        <v>0.3155440414507772</v>
       </c>
       <c r="X4">
-        <v>0.05357055680560217</v>
+        <v>0.05192705781668288</v>
       </c>
       <c r="Y4">
-        <v>-0.09575664533315412</v>
+        <v>0.2636169836340943</v>
       </c>
       <c r="AB4">
-        <v>0.04958876040851903</v>
+        <v>0.05191775991611461</v>
       </c>
       <c r="AD4">
-        <v>117.7</v>
+        <v>1.34</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>117.7</v>
+        <v>1.34</v>
       </c>
       <c r="AG4">
-        <v>-369.9</v>
+        <v>-215.76</v>
       </c>
       <c r="AH4">
-        <v>0.3161428955143701</v>
+        <v>0.001046106765344201</v>
       </c>
       <c r="AI4">
-        <v>0.5803747534516766</v>
+        <v>0.005750085822176451</v>
       </c>
       <c r="AJ4">
-        <v>3.208152645273199</v>
+        <v>-0.2028124530004512</v>
       </c>
       <c r="AK4">
-        <v>1.298806179775281</v>
+        <v>-13.5357590966123</v>
       </c>
       <c r="AL4">
-        <v>0.749</v>
+        <v>0.122</v>
       </c>
       <c r="AM4">
-        <v>0.6919999999999999</v>
+        <v>-7.688</v>
       </c>
       <c r="AN4">
-        <v>7.35625</v>
+        <v>0.01587677725118483</v>
       </c>
       <c r="AO4">
-        <v>16.82242990654206</v>
+        <v>684.4262295081967</v>
       </c>
       <c r="AP4">
-        <v>-23.11875</v>
+        <v>-2.556398104265403</v>
       </c>
       <c r="AQ4">
-        <v>18.20809248554913</v>
+        <v>-10.86108220603538</v>
       </c>
     </row>
     <row r="5">
@@ -966,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amigo Holdings PLC (LSE:AMGO)</t>
+          <t>Wise plc (LSE:WISE)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -974,32 +974,35 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="F5">
+        <v>0.268</v>
+      </c>
       <c r="G5">
-        <v>4.470588235294118</v>
+        <v>0.1570670296019054</v>
       </c>
       <c r="H5">
-        <v>4.470588235294118</v>
+        <v>0.1532494045593739</v>
       </c>
       <c r="I5">
-        <v>3.308823529411765</v>
+        <v>0.2618179475411763</v>
       </c>
       <c r="J5">
-        <v>3.308823529411765</v>
+        <v>0.1965302000790262</v>
       </c>
       <c r="K5">
-        <v>171.2</v>
+        <v>265.2</v>
       </c>
       <c r="L5">
-        <v>3.147058823529412</v>
+        <v>0.1804695474651242</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>48.2</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.00422492001577771</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.1817496229260935</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1011,67 +1014,79 @@
         <v>-0</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>48.2</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
       </c>
       <c r="U5">
-        <v>143.1</v>
+        <v>1111.8</v>
       </c>
       <c r="V5">
-        <v>5.568093385214008</v>
+        <v>0.09745365297804269</v>
       </c>
       <c r="W5">
-        <v>-1.07808564231738</v>
+        <v>0.5203060623896409</v>
       </c>
       <c r="X5">
-        <v>0.06781985481135901</v>
+        <v>0.0522457175705609</v>
       </c>
       <c r="Y5">
-        <v>-1.145905497128739</v>
+        <v>0.46806034481908</v>
+      </c>
+      <c r="Z5">
+        <v>7.943559678540945</v>
+      </c>
+      <c r="AA5">
+        <v>1.561149372963337</v>
       </c>
       <c r="AB5">
-        <v>0.1046109115961805</v>
+        <v>0.05194781147751334</v>
+      </c>
+      <c r="AC5">
+        <v>1.509201561485823</v>
       </c>
       <c r="AD5">
-        <v>56.4</v>
+        <v>379.2</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>2.292630441207314</v>
       </c>
       <c r="AF5">
-        <v>56.4</v>
+        <v>381.4926304412073</v>
       </c>
       <c r="AG5">
-        <v>-86.69999999999999</v>
+        <v>-730.3073695587926</v>
       </c>
       <c r="AH5">
-        <v>0.6869671132764921</v>
+        <v>0.03235732560648183</v>
       </c>
       <c r="AI5">
-        <v>0.5899581589958159</v>
+        <v>0.2968138316565707</v>
       </c>
       <c r="AJ5">
-        <v>1.421311475409836</v>
+        <v>-0.06839241385071523</v>
       </c>
       <c r="AK5">
-        <v>1.825263157894737</v>
+        <v>-4.209443177508782</v>
       </c>
       <c r="AL5">
-        <v>9.69</v>
+        <v>20</v>
       </c>
       <c r="AM5">
-        <v>9.356</v>
+        <v>8</v>
       </c>
       <c r="AN5">
-        <v>0.3122923588039867</v>
+        <v>0.9690774341937132</v>
       </c>
       <c r="AO5">
-        <v>18.57585139318886</v>
+        <v>19.155</v>
       </c>
       <c r="AP5">
-        <v>-0.4800664451827242</v>
+        <v>-1.866361792892391</v>
       </c>
       <c r="AQ5">
-        <v>19.23899102180419</v>
+        <v>47.8875</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1097,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aquis Exchange PLC (AIM:AQX)</t>
+          <t>PayPoint plc (LSE:PAY)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1090,116 +1105,122 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>-0.00778</v>
+      </c>
+      <c r="E6">
+        <v>-0.0694</v>
+      </c>
       <c r="G6">
-        <v>0.2457847533632287</v>
+        <v>0.2802264006139678</v>
       </c>
       <c r="H6">
-        <v>0.2192825112107623</v>
+        <v>0.2785878741366078</v>
       </c>
       <c r="I6">
-        <v>0.1609865470852018</v>
+        <v>0.2079815809669992</v>
       </c>
       <c r="J6">
-        <v>0.1609865470852018</v>
+        <v>0.1635711376738345</v>
       </c>
       <c r="K6">
-        <v>4.86</v>
+        <v>37.2</v>
       </c>
       <c r="L6">
-        <v>0.2179372197309417</v>
+        <v>0.1427475057559478</v>
       </c>
       <c r="M6">
-        <v>2.47</v>
+        <v>32</v>
       </c>
       <c r="N6">
-        <v>0.01980753809141941</v>
+        <v>0.06711409395973154</v>
       </c>
       <c r="O6">
-        <v>0.5082304526748971</v>
+        <v>0.8602150537634408</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>32</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.06711409395973154</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.8602150537634408</v>
       </c>
       <c r="S6">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>16.2</v>
+        <v>24.8</v>
       </c>
       <c r="V6">
-        <v>0.1299117882919006</v>
+        <v>0.05201342281879195</v>
       </c>
       <c r="W6">
-        <v>0.2059322033898305</v>
+        <v>0.3772819472616634</v>
       </c>
       <c r="X6">
-        <v>0.0500600234820618</v>
+        <v>0.05465468611760857</v>
       </c>
       <c r="Y6">
-        <v>0.1558721799077687</v>
+        <v>0.3226272611440548</v>
       </c>
       <c r="Z6">
-        <v>3.78286683630195</v>
+        <v>3.323131854118849</v>
       </c>
       <c r="AA6">
-        <v>0.6089906700593722</v>
+        <v>0.5435684580183791</v>
       </c>
       <c r="AB6">
-        <v>0.04994648975733356</v>
+        <v>0.05117667738564125</v>
       </c>
       <c r="AC6">
-        <v>0.5590441803020387</v>
+        <v>0.4923917806327378</v>
       </c>
       <c r="AD6">
-        <v>4.43</v>
+        <v>132.7</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>4.43</v>
+        <v>132.7</v>
       </c>
       <c r="AG6">
-        <v>-11.77</v>
+        <v>107.9</v>
       </c>
       <c r="AH6">
-        <v>0.03430651281654147</v>
+        <v>0.2177194421657096</v>
       </c>
       <c r="AI6">
-        <v>0.1569252568189869</v>
+        <v>0.4953340798805524</v>
       </c>
       <c r="AJ6">
-        <v>-0.1042238554856991</v>
+        <v>0.1845390798700188</v>
       </c>
       <c r="AK6">
-        <v>-0.9783873649210306</v>
+        <v>0.4438502673796792</v>
       </c>
       <c r="AL6">
-        <v>0.09</v>
+        <v>6.88</v>
       </c>
       <c r="AM6">
-        <v>0.051</v>
+        <v>-0.08000000000000007</v>
       </c>
       <c r="AN6">
-        <v>1.08578431372549</v>
+        <v>1.906609195402299</v>
       </c>
       <c r="AO6">
-        <v>39.88888888888889</v>
+        <v>7.877906976744186</v>
       </c>
       <c r="AP6">
-        <v>-2.884803921568627</v>
+        <v>1.550287356321839</v>
       </c>
       <c r="AQ6">
-        <v>70.3921568627451</v>
+        <v>-677.4999999999994</v>
       </c>
     </row>
     <row r="7">
@@ -1210,7 +1231,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Appreciate Group plc (AIM:APP)</t>
+          <t>Aquis Exchange PLC (AIM:AQX)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1219,121 +1240,118 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.148</v>
-      </c>
-      <c r="E7">
-        <v>-0.0839</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G7">
-        <v>0.08679525222551927</v>
+        <v>0.2415073529411765</v>
       </c>
       <c r="H7">
-        <v>0.08679525222551927</v>
+        <v>0.2183823529411765</v>
       </c>
       <c r="I7">
-        <v>0.07863501483679525</v>
+        <v>0.2268382352941176</v>
       </c>
       <c r="J7">
-        <v>0.06173664779006025</v>
+        <v>0.2268382352941176</v>
       </c>
       <c r="K7">
-        <v>6.44</v>
+        <v>6.39</v>
       </c>
       <c r="L7">
-        <v>0.04777448071216617</v>
+        <v>0.2349264705882353</v>
       </c>
       <c r="M7">
-        <v>3.66</v>
+        <v>1.78</v>
       </c>
       <c r="N7">
-        <v>0.03935483870967742</v>
+        <v>0.01406003159557662</v>
       </c>
       <c r="O7">
-        <v>0.5683229813664596</v>
+        <v>0.2785602503912363</v>
       </c>
       <c r="P7">
-        <v>3.66</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.03935483870967742</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.5683229813664596</v>
+        <v>-0</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7">
-        <v>14.6</v>
+        <v>17.7</v>
       </c>
       <c r="V7">
-        <v>0.156989247311828</v>
+        <v>0.1398104265402844</v>
       </c>
       <c r="W7">
-        <v>0.331958762886598</v>
+        <v>0.2684873949579832</v>
       </c>
       <c r="X7">
-        <v>0.05023658298585082</v>
+        <v>0.05223224184784768</v>
       </c>
       <c r="Y7">
-        <v>0.2817221799007472</v>
+        <v>0.2162551531101355</v>
       </c>
       <c r="Z7">
-        <v>6.439285373077292</v>
+        <v>2.280157599128175</v>
       </c>
       <c r="AA7">
-        <v>0.3975398930973594</v>
+        <v>0.5172269259787073</v>
       </c>
       <c r="AB7">
-        <v>0.05004863235578875</v>
+        <v>0.05181113156626874</v>
       </c>
       <c r="AC7">
-        <v>0.3474912607415707</v>
+        <v>0.4654157944124386</v>
       </c>
       <c r="AD7">
-        <v>5.3</v>
+        <v>4.06</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>5.3</v>
+        <v>4.06</v>
       </c>
       <c r="AG7">
-        <v>-9.300000000000001</v>
+        <v>-13.64</v>
       </c>
       <c r="AH7">
-        <v>0.05391658189216684</v>
+        <v>0.0310730139292821</v>
       </c>
       <c r="AI7">
-        <v>0.2663316582914573</v>
+        <v>0.1158014831717056</v>
       </c>
       <c r="AJ7">
-        <v>-0.1111111111111111</v>
+        <v>-0.1207507082152975</v>
       </c>
       <c r="AK7">
-        <v>-1.754716981132076</v>
+        <v>-0.7857142857142858</v>
       </c>
       <c r="AL7">
-        <v>0.51</v>
+        <v>0.094</v>
       </c>
       <c r="AM7">
-        <v>-0.6000000000000001</v>
+        <v>-0.145</v>
       </c>
       <c r="AN7">
-        <v>0.456896551724138</v>
+        <v>0.608695652173913</v>
       </c>
       <c r="AO7">
-        <v>20.78431372549019</v>
+        <v>65.63829787234043</v>
       </c>
       <c r="AP7">
-        <v>-0.8017241379310346</v>
+        <v>-2.044977511244378</v>
       </c>
       <c r="AQ7">
-        <v>-17.66666666666666</v>
+        <v>-42.55172413793104</v>
       </c>
     </row>
     <row r="8">
@@ -1344,7 +1362,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Duke Royalty Limited (AIM:DUKE)</t>
+          <t>Equals Group plc (AIM:EQLS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1353,112 +1371,118 @@
         </is>
       </c>
       <c r="D8">
-        <v>1.363</v>
+        <v>0.313</v>
+      </c>
+      <c r="E8">
+        <v>0.253</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.1170915958451369</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.1170915958451369</v>
       </c>
       <c r="I8">
-        <v>0.8854166666666667</v>
+        <v>0.1000944287063267</v>
       </c>
       <c r="J8">
-        <v>0.8487573099415205</v>
+        <v>0.08980169971671387</v>
       </c>
       <c r="K8">
-        <v>27.3</v>
+        <v>9.34</v>
       </c>
       <c r="L8">
-        <v>0.7109375</v>
+        <v>0.08819641170915958</v>
       </c>
       <c r="M8">
-        <v>10.3</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.0612730517549078</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>0.3772893772893773</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>10.3</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.0612730517549078</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.3772893772893773</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>5.65</v>
+        <v>22.8</v>
       </c>
       <c r="V8">
-        <v>0.03361094586555622</v>
+        <v>0.07864780958951363</v>
       </c>
       <c r="W8">
-        <v>0.1653543307086614</v>
+        <v>0.1813592233009709</v>
       </c>
       <c r="X8">
-        <v>0.05166155380270943</v>
+        <v>0.05208099812935981</v>
       </c>
       <c r="Y8">
-        <v>0.113692776905952</v>
+        <v>0.1292782251716111</v>
       </c>
       <c r="Z8">
-        <v>0.2346815298302226</v>
+        <v>2.659467604218986</v>
       </c>
       <c r="AA8">
-        <v>0.1991876639516604</v>
+        <v>0.2388247112004018</v>
       </c>
       <c r="AB8">
-        <v>0.0496618186829745</v>
+        <v>0.05186093627615834</v>
       </c>
       <c r="AC8">
-        <v>0.1495258452686859</v>
+        <v>0.1869637749242435</v>
       </c>
       <c r="AD8">
-        <v>38.7</v>
+        <v>4.84</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>38.7</v>
+        <v>4.84</v>
       </c>
       <c r="AG8">
-        <v>33.05</v>
+        <v>-17.96</v>
       </c>
       <c r="AH8">
-        <v>0.187137330754352</v>
+        <v>0.01642125262943612</v>
       </c>
       <c r="AI8">
-        <v>0.1807566557683326</v>
+        <v>0.07340006066120716</v>
       </c>
       <c r="AJ8">
-        <v>0.1643052448421576</v>
+        <v>-0.06604398028976981</v>
       </c>
       <c r="AK8">
-        <v>0.1585512113216599</v>
+        <v>-0.4163189615206305</v>
       </c>
       <c r="AL8">
-        <v>3.35</v>
+        <v>0.231</v>
       </c>
       <c r="AM8">
-        <v>3.35</v>
+        <v>0.231</v>
+      </c>
+      <c r="AN8">
+        <v>0.2534031413612565</v>
       </c>
       <c r="AO8">
-        <v>10.14925373134328</v>
+        <v>45.88744588744589</v>
+      </c>
+      <c r="AP8">
+        <v>-0.9403141361256544</v>
       </c>
       <c r="AQ8">
-        <v>10.14925373134328</v>
+        <v>45.88744588744589</v>
       </c>
     </row>
     <row r="9">
@@ -1469,7 +1493,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>International Personal Finance plc (LSE:IPF)</t>
+          <t>Ramsdens Holdings PLC (AIM:RFX)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1477,122 +1501,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D9">
-        <v>-0.0603</v>
-      </c>
-      <c r="E9">
-        <v>-0.0596</v>
-      </c>
       <c r="G9">
-        <v>0.243262311274164</v>
+        <v>0.1183368869936034</v>
       </c>
       <c r="H9">
-        <v>0.243262311274164</v>
+        <v>0.1183368869936034</v>
       </c>
       <c r="I9">
-        <v>0.1995202483420347</v>
+        <v>0.1332622601279318</v>
       </c>
       <c r="J9">
-        <v>0.1707351488641174</v>
+        <v>0.1048329779673063</v>
       </c>
       <c r="K9">
-        <v>60.5</v>
+        <v>9.48</v>
       </c>
       <c r="L9">
-        <v>0.0853675744320587</v>
+        <v>0.1010660980810235</v>
       </c>
       <c r="M9">
-        <v>25.25</v>
+        <v>3.52</v>
       </c>
       <c r="N9">
-        <v>0.128892291985707</v>
+        <v>0.03915461624026696</v>
       </c>
       <c r="O9">
-        <v>0.4173553719008264</v>
+        <v>0.3713080168776371</v>
       </c>
       <c r="P9">
-        <v>21.6</v>
+        <v>3.52</v>
       </c>
       <c r="Q9">
-        <v>0.110260336906585</v>
+        <v>0.03915461624026696</v>
       </c>
       <c r="R9">
-        <v>0.3570247933884298</v>
+        <v>0.3713080168776371</v>
       </c>
       <c r="S9">
-        <v>3.649999999999999</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>0.1445544554455445</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>53.1</v>
+        <v>14.1</v>
       </c>
       <c r="V9">
-        <v>0.2710566615620215</v>
+        <v>0.1568409343715239</v>
       </c>
       <c r="W9">
-        <v>0.1206862158388191</v>
+        <v>0.1915151515151515</v>
       </c>
       <c r="X9">
-        <v>0.07667081576531239</v>
+        <v>0.05407248524196665</v>
       </c>
       <c r="Y9">
-        <v>0.04401540007350668</v>
+        <v>0.1374426662731849</v>
       </c>
       <c r="Z9">
-        <v>0.7036338363780779</v>
+        <v>1.883534136546185</v>
       </c>
       <c r="AA9">
-        <v>0.1201350277998411</v>
+        <v>0.1974564926372155</v>
       </c>
       <c r="AB9">
-        <v>0.05375680363335313</v>
+        <v>0.05130576287007881</v>
       </c>
       <c r="AC9">
-        <v>0.06637822416648802</v>
+        <v>0.1461507297671367</v>
       </c>
       <c r="AD9">
-        <v>640.7</v>
+        <v>19.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>640.7</v>
+        <v>19.7</v>
       </c>
       <c r="AG9">
-        <v>587.6</v>
+        <v>5.6</v>
       </c>
       <c r="AH9">
-        <v>0.7658379153717428</v>
+        <v>0.1797445255474452</v>
       </c>
       <c r="AI9">
-        <v>0.566289552766484</v>
+        <v>0.2702331961591221</v>
       </c>
       <c r="AJ9">
-        <v>0.7499680918953414</v>
+        <v>0.05863874345549738</v>
       </c>
       <c r="AK9">
-        <v>0.5449318371510712</v>
+        <v>0.09523809523809522</v>
       </c>
       <c r="AL9">
-        <v>70.7</v>
+        <v>0.773</v>
       </c>
       <c r="AM9">
-        <v>70.7</v>
+        <v>0.773</v>
       </c>
       <c r="AN9">
-        <v>4.314478114478114</v>
+        <v>1.397163120567376</v>
       </c>
       <c r="AO9">
-        <v>2</v>
+        <v>16.17076326002587</v>
       </c>
       <c r="AP9">
-        <v>3.956902356902357</v>
+        <v>0.3971631205673758</v>
       </c>
       <c r="AQ9">
-        <v>2</v>
+        <v>16.17076326002587</v>
       </c>
     </row>
     <row r="10">
@@ -1603,7 +1621,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>London Stock Exchange Group plc (LSE:LSEG)</t>
+          <t>De La Rue plc (LSE:DLAR)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1612,124 +1630,115 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.326</v>
-      </c>
-      <c r="E10">
-        <v>0.228</v>
-      </c>
-      <c r="F10">
-        <v>0.119</v>
+        <v>-0.073</v>
       </c>
       <c r="G10">
-        <v>0.4350038074007041</v>
+        <v>0.1255846917080085</v>
       </c>
       <c r="H10">
-        <v>0.3762705130610398</v>
+        <v>0.1195369714150721</v>
       </c>
       <c r="I10">
-        <v>0.231191992318983</v>
+        <v>0.07110796125679188</v>
       </c>
       <c r="J10">
-        <v>0.1907746139408612</v>
+        <v>0.07110796125679188</v>
       </c>
       <c r="K10">
-        <v>1156.8</v>
+        <v>-53.3</v>
       </c>
       <c r="L10">
-        <v>0.1276638009998565</v>
+        <v>-0.1259154264115284</v>
       </c>
       <c r="M10">
-        <v>642.8</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.01349759466479643</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.5556708160442601</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>642.8</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.01349759466479643</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.5556708160442601</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>3062.2</v>
+        <v>41.1</v>
       </c>
       <c r="V10">
-        <v>0.06430045796910334</v>
+        <v>0.1908964235949837</v>
       </c>
       <c r="W10">
-        <v>0.0363249272276808</v>
+        <v>-0.6967320261437908</v>
       </c>
       <c r="X10">
-        <v>0.05151364021358638</v>
+        <v>0.05903562689431271</v>
       </c>
       <c r="Y10">
-        <v>-0.01518871298590558</v>
+        <v>-0.7557676530381036</v>
       </c>
       <c r="Z10">
-        <v>0.5285837620897647</v>
+        <v>2.30054347826087</v>
       </c>
       <c r="AA10">
-        <v>0.1008403631480829</v>
+        <v>0.1635869565217391</v>
       </c>
       <c r="AB10">
-        <v>0.05041711343212005</v>
+        <v>0.05231969884954014</v>
       </c>
       <c r="AC10">
-        <v>0.05042324971596284</v>
+        <v>0.111267257672199</v>
       </c>
       <c r="AD10">
-        <v>10107.5</v>
+        <v>155.8</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>10107.5</v>
+        <v>155.8</v>
       </c>
       <c r="AG10">
-        <v>7045.3</v>
+        <v>114.7</v>
       </c>
       <c r="AH10">
-        <v>0.1750798533884859</v>
+        <v>0.4198329291296147</v>
       </c>
       <c r="AI10">
-        <v>0.229892508335949</v>
+        <v>0.9681227863046045</v>
       </c>
       <c r="AJ10">
-        <v>0.1288728813249287</v>
+        <v>0.3475757575757576</v>
       </c>
       <c r="AK10">
-        <v>0.1722398787404655</v>
+        <v>0.9571893515814071</v>
       </c>
       <c r="AL10">
-        <v>198.1</v>
+        <v>23.7</v>
       </c>
       <c r="AM10">
-        <v>189.59</v>
+        <v>22.846</v>
       </c>
       <c r="AN10">
-        <v>3.172373748469916</v>
+        <v>3.394335511982571</v>
       </c>
       <c r="AO10">
-        <v>10.57496214033317</v>
+        <v>1.270042194092827</v>
       </c>
       <c r="AP10">
-        <v>2.211261416779135</v>
+        <v>2.498910675381264</v>
       </c>
       <c r="AQ10">
-        <v>11.04963341948415</v>
+        <v>1.317517289678718</v>
       </c>
     </row>
     <row r="11">
@@ -1749,46 +1758,46 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0573</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="E11">
-        <v>-0.0334</v>
+        <v>0.102</v>
       </c>
       <c r="G11">
-        <v>0.1108017817371938</v>
+        <v>0.1168986083499006</v>
       </c>
       <c r="H11">
-        <v>0.1108017817371938</v>
+        <v>0.1168986083499006</v>
       </c>
       <c r="I11">
-        <v>0.09020044543429843</v>
+        <v>0.1168986083499006</v>
       </c>
       <c r="J11">
-        <v>0.06873124850448195</v>
+        <v>0.09334375767864722</v>
       </c>
       <c r="K11">
-        <v>9.18</v>
+        <v>21.3</v>
       </c>
       <c r="L11">
-        <v>0.05111358574610245</v>
+        <v>0.08469184890656063</v>
       </c>
       <c r="M11">
-        <v>5.74</v>
+        <v>8.08</v>
       </c>
       <c r="N11">
-        <v>0.02263406940063092</v>
+        <v>0.03390684011749895</v>
       </c>
       <c r="O11">
-        <v>0.6252723311546842</v>
+        <v>0.3793427230046948</v>
       </c>
       <c r="P11">
-        <v>5.74</v>
+        <v>8.08</v>
       </c>
       <c r="Q11">
-        <v>0.02263406940063092</v>
+        <v>0.03390684011749895</v>
       </c>
       <c r="R11">
-        <v>0.6252723311546842</v>
+        <v>0.3793427230046948</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1797,73 +1806,73 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>15.4</v>
+        <v>16.3</v>
       </c>
       <c r="V11">
-        <v>0.06072555205047319</v>
+        <v>0.06840117498950903</v>
       </c>
       <c r="W11">
-        <v>0.04890783164624401</v>
+        <v>0.1260355029585799</v>
       </c>
       <c r="X11">
-        <v>0.05133122827414036</v>
+        <v>0.05448864183306341</v>
       </c>
       <c r="Y11">
-        <v>-0.002423396627896354</v>
+        <v>0.07154686112551648</v>
       </c>
       <c r="Z11">
-        <v>1.247222222222222</v>
+        <v>1.41054402692092</v>
       </c>
       <c r="AA11">
-        <v>0.08572314049586777</v>
+        <v>0.1316654798439696</v>
       </c>
       <c r="AB11">
-        <v>0.04967735219250544</v>
+        <v>0.05121225807961279</v>
       </c>
       <c r="AC11">
-        <v>0.03604578830336232</v>
+        <v>0.08045322176435679</v>
       </c>
       <c r="AD11">
-        <v>48.2</v>
+        <v>62.3</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>48.2</v>
+        <v>62.3</v>
       </c>
       <c r="AG11">
-        <v>32.8</v>
+        <v>46</v>
       </c>
       <c r="AH11">
-        <v>0.1597084161696488</v>
+        <v>0.2072521623419827</v>
       </c>
       <c r="AI11">
-        <v>0.2219152854511971</v>
+        <v>0.2272064186725018</v>
       </c>
       <c r="AJ11">
-        <v>0.1145251396648045</v>
+        <v>0.1618009145269082</v>
       </c>
       <c r="AK11">
-        <v>0.1625371655104064</v>
+        <v>0.1783637068631252</v>
       </c>
       <c r="AL11">
-        <v>1.6</v>
+        <v>2.74</v>
       </c>
       <c r="AM11">
-        <v>1.59</v>
+        <v>2.716</v>
       </c>
       <c r="AN11">
-        <v>2.362745098039216</v>
+        <v>1.774928774928775</v>
       </c>
       <c r="AO11">
-        <v>10.125</v>
+        <v>10.72992700729927</v>
       </c>
       <c r="AP11">
-        <v>1.607843137254902</v>
+        <v>1.31054131054131</v>
       </c>
       <c r="AQ11">
-        <v>10.18867924528302</v>
+        <v>10.82474226804124</v>
       </c>
     </row>
     <row r="12">
@@ -1874,7 +1883,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vector Capital Plc (AIM:VCAP)</t>
+          <t>Paysafe Limited (NYSE:PSFE)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1883,115 +1892,115 @@
         </is>
       </c>
       <c r="G12">
-        <v>0.7837837837837838</v>
+        <v>0.1997070436887021</v>
       </c>
       <c r="H12">
-        <v>0.7837837837837838</v>
+        <v>0.1950070054770093</v>
       </c>
       <c r="I12">
-        <v>0.7937411095305832</v>
+        <v>0.09273160286197783</v>
       </c>
       <c r="J12">
-        <v>0.642824466571835</v>
+        <v>0.09273160286197783</v>
       </c>
       <c r="K12">
-        <v>3.04</v>
+        <v>-41.8</v>
       </c>
       <c r="L12">
-        <v>0.4324324324324324</v>
+        <v>-0.02662081263533307</v>
       </c>
       <c r="M12">
-        <v>1.35</v>
+        <v>14.8</v>
       </c>
       <c r="N12">
-        <v>0.0574468085106383</v>
+        <v>0.01876981610653139</v>
       </c>
       <c r="O12">
-        <v>0.4440789473684211</v>
+        <v>-0.354066985645933</v>
       </c>
       <c r="P12">
-        <v>1.35</v>
+        <v>-0</v>
       </c>
       <c r="Q12">
-        <v>0.0574468085106383</v>
+        <v>-0</v>
       </c>
       <c r="R12">
-        <v>0.4440789473684211</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>14.8</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12">
-        <v>0.896</v>
+        <v>226.5</v>
       </c>
       <c r="V12">
-        <v>0.03812765957446809</v>
+        <v>0.2872542802790108</v>
       </c>
       <c r="W12">
-        <v>0.095</v>
+        <v>-0.05507972064830676</v>
       </c>
       <c r="X12">
-        <v>0.06033888854711289</v>
+        <v>0.0837290167566255</v>
       </c>
       <c r="Y12">
-        <v>0.03466111145288711</v>
+        <v>-0.1388087374049323</v>
       </c>
       <c r="Z12">
-        <v>0.1352963818321786</v>
+        <v>1.372055693912207</v>
       </c>
       <c r="AA12">
-        <v>0.08697182448036954</v>
+        <v>0.1272329237123823</v>
       </c>
       <c r="AB12">
-        <v>0.05269707502834805</v>
+        <v>0.05264983086765448</v>
       </c>
       <c r="AC12">
-        <v>0.03427474945202149</v>
+        <v>0.07458309284472778</v>
       </c>
       <c r="AD12">
-        <v>30.2</v>
+        <v>2514.7</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>35.11418593061192</v>
       </c>
       <c r="AF12">
-        <v>30.2</v>
+        <v>2549.814185930612</v>
       </c>
       <c r="AG12">
-        <v>29.304</v>
+        <v>2323.314185930612</v>
       </c>
       <c r="AH12">
-        <v>0.5623836126629422</v>
+        <v>0.7638029388236889</v>
       </c>
       <c r="AI12">
-        <v>0.5033333333333333</v>
+        <v>0.743881796328461</v>
       </c>
       <c r="AJ12">
-        <v>0.554957957730475</v>
+        <v>0.7466108344241663</v>
       </c>
       <c r="AK12">
-        <v>0.4958040064970222</v>
+        <v>0.7257603056182917</v>
       </c>
       <c r="AL12">
-        <v>1.83</v>
+        <v>169.7</v>
       </c>
       <c r="AM12">
-        <v>1.828</v>
+        <v>169.7</v>
       </c>
       <c r="AN12">
-        <v>5.412186379928316</v>
+        <v>6.025687106127045</v>
       </c>
       <c r="AO12">
-        <v>3.049180327868852</v>
+        <v>0.8515026517383619</v>
       </c>
       <c r="AP12">
-        <v>5.251612903225806</v>
+        <v>5.567091236984189</v>
       </c>
       <c r="AQ12">
-        <v>3.052516411378556</v>
+        <v>0.8515026517383619</v>
       </c>
     </row>
     <row r="13">
@@ -2002,7 +2011,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ADVFN Plc (AIM:AFN)</t>
+          <t>London Stock Exchange Group plc (LSE:LSEG)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2011,118 +2020,124 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.008399999999999999</v>
+        <v>0.317</v>
+      </c>
+      <c r="E13">
+        <v>0.135</v>
+      </c>
+      <c r="F13">
+        <v>0.09179999999999999</v>
       </c>
       <c r="G13">
-        <v>0.04433962264150944</v>
+        <v>0.4841695501730103</v>
       </c>
       <c r="H13">
-        <v>0.0159329140461216</v>
+        <v>0.4111303344867359</v>
       </c>
       <c r="I13">
-        <v>0.005345911949685535</v>
+        <v>0.2015378700499808</v>
       </c>
       <c r="J13">
-        <v>0.005345911949685535</v>
+        <v>0.1617752657436751</v>
       </c>
       <c r="K13">
-        <v>-1.66</v>
+        <v>1432.2</v>
       </c>
       <c r="L13">
-        <v>-0.1740041928721174</v>
+        <v>0.1376585928489043</v>
       </c>
       <c r="M13">
-        <v>0.716</v>
+        <v>1649.5</v>
       </c>
       <c r="N13">
-        <v>0.06754716981132075</v>
+        <v>0.02581320597044822</v>
       </c>
       <c r="O13">
-        <v>-0.4313253012048193</v>
+        <v>1.151724619466555</v>
       </c>
       <c r="P13">
-        <v>0.716</v>
+        <v>752.3</v>
       </c>
       <c r="Q13">
-        <v>0.06754716981132075</v>
+        <v>0.01177282500852876</v>
       </c>
       <c r="R13">
-        <v>-0.4313253012048193</v>
+        <v>0.5252757994693478</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>897.2</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>0.5439224007274932</v>
       </c>
       <c r="U13">
-        <v>1.11</v>
+        <v>4447.8</v>
       </c>
       <c r="V13">
-        <v>0.1047169811320755</v>
+        <v>0.06960410883016648</v>
       </c>
       <c r="W13">
-        <v>-0.3851508120649652</v>
+        <v>0.0454699866974414</v>
       </c>
       <c r="X13">
-        <v>0.04990049807805914</v>
+        <v>0.05380073954282084</v>
       </c>
       <c r="Y13">
-        <v>-0.4350513101430243</v>
+        <v>-0.008330752845379444</v>
       </c>
       <c r="Z13">
-        <v>12.15286624203823</v>
+        <v>0.6468701037081251</v>
       </c>
       <c r="AA13">
-        <v>0.06496815286624212</v>
+        <v>0.1046475829290206</v>
       </c>
       <c r="AB13">
-        <v>0.05003028618354206</v>
+        <v>0.05191008885250501</v>
       </c>
       <c r="AC13">
-        <v>0.01493786668270006</v>
+        <v>0.05273749407651562</v>
       </c>
       <c r="AD13">
-        <v>0.171</v>
+        <v>12237.7</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0.171</v>
+        <v>12237.7</v>
       </c>
       <c r="AG13">
-        <v>-0.9390000000000001</v>
+        <v>7789.900000000001</v>
       </c>
       <c r="AH13">
-        <v>0.01587596323461146</v>
+        <v>0.1607281935299997</v>
       </c>
       <c r="AI13">
-        <v>0.09601347557551937</v>
+        <v>0.2651498573251665</v>
       </c>
       <c r="AJ13">
-        <v>-0.0971949073594866</v>
+        <v>0.1086589307210219</v>
       </c>
       <c r="AK13">
-        <v>-1.399403874813711</v>
+        <v>0.1867808306218995</v>
       </c>
       <c r="AL13">
-        <v>0.017</v>
+        <v>270.7</v>
       </c>
       <c r="AM13">
-        <v>0.017</v>
+        <v>174.1</v>
       </c>
       <c r="AN13">
-        <v>1.125</v>
+        <v>2.984149820771051</v>
       </c>
       <c r="AO13">
-        <v>3</v>
+        <v>7.74584410786849</v>
       </c>
       <c r="AP13">
-        <v>-6.177631578947369</v>
+        <v>1.899558633470702</v>
       </c>
       <c r="AQ13">
-        <v>3</v>
+        <v>12.04365307294658</v>
       </c>
     </row>
     <row r="14">
@@ -2133,7 +2148,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ramsdens Holdings PLC (AIM:RFX)</t>
+          <t>International Personal Finance plc (LSE:IPF)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2141,116 +2156,122 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D14">
+        <v>-0.0291</v>
+      </c>
+      <c r="E14">
+        <v>-0.0279</v>
+      </c>
       <c r="G14">
-        <v>0.0106015037593985</v>
+        <v>0.1975575489030585</v>
       </c>
       <c r="H14">
-        <v>0.0106015037593985</v>
+        <v>0.1975575489030585</v>
       </c>
       <c r="I14">
-        <v>0.03233082706766917</v>
+        <v>0.2161461147735869</v>
       </c>
       <c r="J14">
-        <v>0.02464909008814464</v>
+        <v>0.1187340359684694</v>
       </c>
       <c r="K14">
-        <v>2.92</v>
+        <v>56.8</v>
       </c>
       <c r="L14">
-        <v>0.04390977443609023</v>
+        <v>0.06138549659569869</v>
       </c>
       <c r="M14">
-        <v>0.496</v>
+        <v>26.581</v>
       </c>
       <c r="N14">
-        <v>0.006500655307994757</v>
+        <v>0.07829455081001473</v>
       </c>
       <c r="O14">
-        <v>0.1698630136986301</v>
+        <v>0.467975352112676</v>
       </c>
       <c r="P14">
-        <v>0.496</v>
+        <v>26.2</v>
       </c>
       <c r="Q14">
-        <v>0.006500655307994757</v>
+        <v>0.07717231222385862</v>
       </c>
       <c r="R14">
-        <v>0.1698630136986301</v>
+        <v>0.4612676056338028</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>0.3810000000000002</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>0.01433354651818969</v>
       </c>
       <c r="U14">
-        <v>14.1</v>
+        <v>35.8</v>
       </c>
       <c r="V14">
-        <v>0.1847968545216252</v>
+        <v>0.1054491899852724</v>
       </c>
       <c r="W14">
-        <v>0.05971370143149284</v>
+        <v>0.1157530059099246</v>
       </c>
       <c r="X14">
-        <v>0.05132025179237969</v>
+        <v>0.07196279063920882</v>
       </c>
       <c r="Y14">
-        <v>0.008393449639113156</v>
+        <v>0.04379021527071578</v>
       </c>
       <c r="Z14">
-        <v>1.650124069478908</v>
+        <v>0.8813220306695875</v>
       </c>
       <c r="AA14">
-        <v>0.04067405684520146</v>
+        <v>0.1046429216893273</v>
       </c>
       <c r="AB14">
-        <v>0.04967788637626656</v>
+        <v>0.0525605731435109</v>
       </c>
       <c r="AC14">
-        <v>-0.009003829531065106</v>
+        <v>0.05208234854581643</v>
       </c>
       <c r="AD14">
-        <v>14.4</v>
+        <v>691.8</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>14.4</v>
+        <v>691.8</v>
       </c>
       <c r="AG14">
-        <v>0.3000000000000007</v>
+        <v>656</v>
       </c>
       <c r="AH14">
-        <v>0.1587651598676957</v>
+        <v>0.6708038398138272</v>
       </c>
       <c r="AI14">
-        <v>0.2253521126760563</v>
+        <v>0.540426529177408</v>
       </c>
       <c r="AJ14">
-        <v>0.003916449086161889</v>
+        <v>0.6589653440482169</v>
       </c>
       <c r="AK14">
-        <v>0.006024096385542183</v>
+        <v>0.5272040504701438</v>
       </c>
       <c r="AL14">
-        <v>0.618</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AM14">
-        <v>0.618</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AN14">
-        <v>3.645569620253164</v>
+        <v>3.322766570605187</v>
       </c>
       <c r="AO14">
-        <v>3.478964401294498</v>
+        <v>2.070393374741201</v>
       </c>
       <c r="AP14">
-        <v>0.07594936708860778</v>
+        <v>3.150816522574448</v>
       </c>
       <c r="AQ14">
-        <v>3.478964401294498</v>
+        <v>2.070393374741201</v>
       </c>
     </row>
     <row r="15">
@@ -2261,7 +2282,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Funding Circle Holdings plc (LSE:FCH)</t>
+          <t>W.A.G payment solutions plc (LSE:WPS)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2270,34 +2291,34 @@
         </is>
       </c>
       <c r="F15">
-        <v>-0.232</v>
+        <v>0.16</v>
       </c>
       <c r="G15">
-        <v>0.461729490022173</v>
+        <v>0.03486888147873698</v>
       </c>
       <c r="H15">
-        <v>0.4186252771618625</v>
+        <v>0.02177761310773537</v>
       </c>
       <c r="I15">
-        <v>0.1596452328159645</v>
+        <v>0.01811370466427895</v>
       </c>
       <c r="J15">
-        <v>0.1596452328159645</v>
+        <v>0.01109823809589155</v>
       </c>
       <c r="K15">
-        <v>42.4</v>
+        <v>14.2</v>
       </c>
       <c r="L15">
-        <v>0.1880266075388027</v>
+        <v>0.005845786505290025</v>
       </c>
       <c r="M15">
-        <v>5.59</v>
+        <v>-0</v>
       </c>
       <c r="N15">
-        <v>0.02386848847139197</v>
+        <v>-0</v>
       </c>
       <c r="O15">
-        <v>0.1318396226415094</v>
+        <v>-0</v>
       </c>
       <c r="P15">
         <v>-0</v>
@@ -2309,79 +2330,76 @@
         <v>-0</v>
       </c>
       <c r="S15">
-        <v>5.59</v>
-      </c>
-      <c r="T15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>243.9</v>
+        <v>87.8</v>
       </c>
       <c r="V15">
-        <v>1.041417591801879</v>
+        <v>0.1111673841478855</v>
       </c>
       <c r="W15">
-        <v>0.1208321459105158</v>
+        <v>0.04628422425032594</v>
       </c>
       <c r="X15">
-        <v>0.05463587069527358</v>
+        <v>0.05732629668165312</v>
       </c>
       <c r="Y15">
-        <v>0.06619627521524224</v>
+        <v>-0.01104207243132718</v>
       </c>
       <c r="Z15">
-        <v>0.2603324867236204</v>
+        <v>8.419757365684575</v>
       </c>
       <c r="AA15">
-        <v>0.04156084045255137</v>
+        <v>0.09344447195400403</v>
       </c>
       <c r="AB15">
-        <v>0.05170428738347061</v>
+        <v>0.05071073866744052</v>
       </c>
       <c r="AC15">
-        <v>-0.01014344693091924</v>
+        <v>0.04273373328656351</v>
       </c>
       <c r="AD15">
-        <v>138.6</v>
+        <v>434.3</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>138.6</v>
+        <v>434.3</v>
       </c>
       <c r="AG15">
-        <v>-105.3</v>
+        <v>346.5</v>
       </c>
       <c r="AH15">
-        <v>0.3717811158798284</v>
+        <v>0.3547912752226126</v>
       </c>
       <c r="AI15">
-        <v>0.2759307186940076</v>
+        <v>0.5484970952260673</v>
       </c>
       <c r="AJ15">
-        <v>-0.8169123351435224</v>
+        <v>0.3049370764762827</v>
       </c>
       <c r="AK15">
-        <v>-0.4075077399380806</v>
+        <v>0.4921875</v>
       </c>
       <c r="AL15">
-        <v>1.22</v>
+        <v>12.4</v>
       </c>
       <c r="AM15">
-        <v>0.612</v>
+        <v>12.064</v>
       </c>
       <c r="AN15">
-        <v>3.818181818181818</v>
+        <v>6.482089552238806</v>
       </c>
       <c r="AO15">
-        <v>29.50819672131147</v>
+        <v>3.548387096774194</v>
       </c>
       <c r="AP15">
-        <v>-2.900826446280992</v>
+        <v>5.171641791044777</v>
       </c>
       <c r="AQ15">
-        <v>58.82352941176471</v>
+        <v>3.647214854111406</v>
       </c>
     </row>
     <row r="16">
@@ -2392,7 +2410,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Paragon Banking Group PLC (LSE:PAG)</t>
+          <t>Vector Capital Plc (AIM:VCAP)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2400,110 +2418,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D16">
-        <v>0.0885</v>
-      </c>
-      <c r="E16">
-        <v>0.218</v>
-      </c>
       <c r="G16">
-        <v>0</v>
+        <v>0.7503392130257802</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>0.7503392130257802</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>0.7530529172320217</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>0.5911817294157927</v>
       </c>
       <c r="K16">
-        <v>349.4</v>
+        <v>2.52</v>
       </c>
       <c r="L16">
-        <v>0.7835837631755999</v>
+        <v>0.3419267299864315</v>
       </c>
       <c r="M16">
-        <v>165.4</v>
+        <v>1.46</v>
       </c>
       <c r="N16">
-        <v>0.1059645076558396</v>
+        <v>0.07684210526315789</v>
       </c>
       <c r="O16">
-        <v>0.4733829421866056</v>
+        <v>0.5793650793650793</v>
       </c>
       <c r="P16">
-        <v>76.8</v>
+        <v>1.46</v>
       </c>
       <c r="Q16">
-        <v>0.04920238324043821</v>
+        <v>0.07684210526315789</v>
       </c>
       <c r="R16">
-        <v>0.2198053806525472</v>
+        <v>0.5793650793650793</v>
       </c>
       <c r="S16">
-        <v>88.59999999999998</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>0.5356711003627569</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>2151.6</v>
+        <v>0.609</v>
       </c>
       <c r="V16">
-        <v>1.378435517970402</v>
+        <v>0.03205263157894737</v>
       </c>
       <c r="W16">
-        <v>0.2083730916030534</v>
+        <v>0.08456375838926174</v>
       </c>
       <c r="X16">
-        <v>0.07395155039203966</v>
+        <v>0.05191675589446192</v>
       </c>
       <c r="Y16">
-        <v>0.1344215412110138</v>
+        <v>0.03264700249479981</v>
       </c>
       <c r="Z16">
-        <v>0.0782198365084377</v>
+        <v>0.1246954520844613</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>0.07371767301357593</v>
       </c>
       <c r="AB16">
-        <v>0.0493452160921329</v>
+        <v>0.05191675589446192</v>
       </c>
       <c r="AC16">
-        <v>-0.0493452160921329</v>
+        <v>0.02180091711911401</v>
       </c>
       <c r="AD16">
-        <v>4589</v>
+        <v>0</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>4589</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>2437.4</v>
+        <v>-0.609</v>
       </c>
       <c r="AH16">
-        <v>0.7461909949755281</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>0.743965111943323</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>0.6096090838606407</v>
+        <v>-0.03311402316350389</v>
       </c>
       <c r="AK16">
-        <v>0.606816540941569</v>
+        <v>-0.01927764236649679</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>2.336</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>2.371794871794872</v>
+      </c>
+      <c r="AP16">
+        <v>-0.1097297297297297</v>
+      </c>
+      <c r="AQ16">
+        <v>2.375856164383562</v>
       </c>
     </row>
     <row r="17">
@@ -2514,7 +2538,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OSB Group Plc (LSE:OSB)</t>
+          <t>M&amp;G plc (LSE:MNG)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2522,110 +2546,104 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D17">
-        <v>0.268</v>
-      </c>
-      <c r="E17">
-        <v>0.3</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
+      <c r="F17">
+        <v>0.122</v>
       </c>
       <c r="K17">
-        <v>477.2</v>
-      </c>
-      <c r="L17">
-        <v>0.5689079637577492</v>
+        <v>-527.4</v>
       </c>
       <c r="M17">
-        <v>195.4</v>
+        <v>1120.8</v>
       </c>
       <c r="N17">
-        <v>0.07878396903475526</v>
+        <v>0.1700062189998028</v>
       </c>
       <c r="O17">
-        <v>0.4094719195305951</v>
+        <v>-2.12514220705347</v>
       </c>
       <c r="P17">
-        <v>147.3</v>
+        <v>589.6</v>
       </c>
       <c r="Q17">
-        <v>0.05939037174421419</v>
+        <v>0.08943225082287985</v>
       </c>
       <c r="R17">
-        <v>0.3086756077116513</v>
+        <v>-1.117937049677664</v>
       </c>
       <c r="S17">
-        <v>48.09999999999999</v>
+        <v>531.2000000000002</v>
       </c>
       <c r="T17">
-        <v>0.2461617195496417</v>
+        <v>0.4739471805852963</v>
       </c>
       <c r="U17">
-        <v>3600.6</v>
+        <v>6027.4</v>
       </c>
       <c r="V17">
-        <v>1.451737763083622</v>
+        <v>0.9142536441822015</v>
       </c>
       <c r="W17">
-        <v>0.2014692223254243</v>
+        <v>-0.1106356198867212</v>
       </c>
       <c r="X17">
-        <v>0.07092244382264945</v>
+        <v>0.06746240065023396</v>
       </c>
       <c r="Y17">
-        <v>0.1305467785027749</v>
+        <v>-0.1780980205369552</v>
       </c>
       <c r="Z17">
-        <v>0.1630542542231207</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>0.05522232935548905</v>
       </c>
       <c r="AB17">
-        <v>0.04936003524736748</v>
+        <v>0.05189135182495597</v>
       </c>
       <c r="AC17">
-        <v>-0.04936003524736748</v>
+        <v>0.003330977530533075</v>
       </c>
       <c r="AD17">
-        <v>6378.4</v>
+        <v>10418</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>6378.4</v>
+        <v>10418</v>
       </c>
       <c r="AG17">
-        <v>2777.8</v>
+        <v>4390.6</v>
       </c>
       <c r="AH17">
-        <v>0.7200234800081278</v>
+        <v>0.6124380536956151</v>
       </c>
       <c r="AI17">
-        <v>0.7203894241086052</v>
+        <v>0.6698256961545138</v>
       </c>
       <c r="AJ17">
-        <v>0.5282997337390642</v>
+        <v>0.3997523512969691</v>
       </c>
       <c r="AK17">
-        <v>0.52875226039783</v>
+        <v>0.4609118298533472</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>377.4</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>377.4</v>
+      </c>
+      <c r="AN17">
+        <v>16.46073629325328</v>
+      </c>
+      <c r="AO17">
+        <v>1.16852146263911</v>
+      </c>
+      <c r="AP17">
+        <v>6.937272870911677</v>
+      </c>
+      <c r="AQ17">
+        <v>1.16852146263911</v>
       </c>
     </row>
     <row r="18">
@@ -2645,13 +2663,13 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.06</v>
+        <v>0.125</v>
       </c>
       <c r="E18">
-        <v>0.0256</v>
+        <v>0.0253</v>
       </c>
       <c r="G18">
-        <v>0.001596516690856313</v>
+        <v>0</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -2663,28 +2681,28 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="L18">
-        <v>0.2685050798258345</v>
+        <v>0.2619047619047619</v>
       </c>
       <c r="M18">
-        <v>0.78</v>
+        <v>0.824</v>
       </c>
       <c r="N18">
-        <v>0.06446280991735538</v>
+        <v>0.08158415841584159</v>
       </c>
       <c r="O18">
-        <v>0.4216216216216216</v>
+        <v>0.3745454545454545</v>
       </c>
       <c r="P18">
-        <v>0.78</v>
+        <v>0.824</v>
       </c>
       <c r="Q18">
-        <v>0.06446280991735538</v>
+        <v>0.08158415841584159</v>
       </c>
       <c r="R18">
-        <v>0.4216216216216216</v>
+        <v>0.3745454545454545</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2693,61 +2711,61 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>5.84</v>
+        <v>3.28</v>
       </c>
       <c r="V18">
-        <v>0.4826446280991736</v>
+        <v>0.3247524752475248</v>
       </c>
       <c r="W18">
-        <v>0.08409090909090909</v>
+        <v>0.1083743842364532</v>
       </c>
       <c r="X18">
-        <v>0.07091026831185523</v>
+        <v>0.09545529464315855</v>
       </c>
       <c r="Y18">
-        <v>0.01318064077905386</v>
+        <v>0.01291908959329466</v>
       </c>
       <c r="Z18">
-        <v>0.1909645232815965</v>
+        <v>0.1843722563652327</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.04936010098146149</v>
+        <v>0.04914402612898727</v>
       </c>
       <c r="AC18">
-        <v>-0.04936010098146149</v>
+        <v>-0.04914402612898727</v>
       </c>
       <c r="AD18">
-        <v>31.1</v>
+        <v>44.7</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>31.1</v>
+        <v>44.7</v>
       </c>
       <c r="AG18">
-        <v>25.26</v>
+        <v>41.42</v>
       </c>
       <c r="AH18">
-        <v>0.7199074074074074</v>
+        <v>0.8156934306569343</v>
       </c>
       <c r="AI18">
-        <v>0.6050583657587548</v>
+        <v>0.6622222222222223</v>
       </c>
       <c r="AJ18">
-        <v>0.6761241970021413</v>
+        <v>0.8039596273291926</v>
       </c>
       <c r="AK18">
-        <v>0.5544337137840211</v>
+        <v>0.6449704142011835</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-0.001</v>
+        <v>-0.012</v>
       </c>
       <c r="AQ18">
         <v>-0</v>
@@ -2761,7 +2779,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S&amp;U plc (LSE:SUS)</t>
+          <t>Paragon Banking Group PLC (LSE:PAG)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2770,10 +2788,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.0583</v>
+        <v>0.049</v>
       </c>
       <c r="E19">
-        <v>0.117</v>
+        <v>0.0109</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2788,85 +2806,85 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>47.4</v>
+        <v>187.8</v>
       </c>
       <c r="L19">
-        <v>0.4336688014638609</v>
+        <v>0.39125</v>
       </c>
       <c r="M19">
-        <v>18.6</v>
+        <v>229.9</v>
       </c>
       <c r="N19">
-        <v>0.0607843137254902</v>
+        <v>0.1206254263077811</v>
       </c>
       <c r="O19">
-        <v>0.3924050632911393</v>
+        <v>1.224174653887114</v>
       </c>
       <c r="P19">
-        <v>18.6</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="Q19">
-        <v>0.0607843137254902</v>
+        <v>0.04349651083477622</v>
       </c>
       <c r="R19">
-        <v>0.3924050632911393</v>
+        <v>0.4414270500532481</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>0.6394084384515006</v>
       </c>
       <c r="U19">
-        <v>1.39</v>
+        <v>3654</v>
       </c>
       <c r="V19">
-        <v>0.004542483660130718</v>
+        <v>1.917204470328978</v>
       </c>
       <c r="W19">
-        <v>0.1804339550818424</v>
+        <v>0.1189134426644716</v>
       </c>
       <c r="X19">
-        <v>0.05487803927626576</v>
+        <v>0.07134980888795307</v>
       </c>
       <c r="Y19">
-        <v>0.1255559158055767</v>
+        <v>0.04756363377651854</v>
       </c>
       <c r="Z19">
-        <v>0.2577836268481765</v>
+        <v>0.1252119473066388</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.04955079101201422</v>
+        <v>0.04965997345076335</v>
       </c>
       <c r="AC19">
-        <v>-0.04955079101201422</v>
+        <v>-0.04965997345076335</v>
       </c>
       <c r="AD19">
-        <v>190.1</v>
+        <v>3764.9</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>190.1</v>
+        <v>3764.9</v>
       </c>
       <c r="AG19">
-        <v>188.71</v>
+        <v>110.9000000000001</v>
       </c>
       <c r="AH19">
-        <v>0.3831888732110461</v>
+        <v>0.6639098539888552</v>
       </c>
       <c r="AI19">
-        <v>0.4236683753064407</v>
+        <v>0.6862366257769352</v>
       </c>
       <c r="AJ19">
-        <v>0.3814558023892786</v>
+        <v>0.05498809996033324</v>
       </c>
       <c r="AK19">
-        <v>0.4218774451722518</v>
+        <v>0.06052502319489171</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2883,7 +2901,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Distribution Finance Capital Holdings plc (AIM:DFCH)</t>
+          <t>S&amp;U plc (LSE:SUS)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2891,6 +2909,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D20">
+        <v>-0.00104</v>
+      </c>
+      <c r="E20">
+        <v>0.0442</v>
+      </c>
       <c r="G20">
         <v>0</v>
       </c>
@@ -2904,82 +2928,85 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>-1.62</v>
+        <v>42.2</v>
       </c>
       <c r="L20">
-        <v>-0.09818181818181819</v>
+        <v>0.3977379830348728</v>
       </c>
       <c r="M20">
-        <v>-0</v>
+        <v>20.8</v>
       </c>
       <c r="N20">
-        <v>-0</v>
+        <v>0.06150206978119457</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>0.4928909952606635</v>
       </c>
       <c r="P20">
-        <v>-0</v>
+        <v>20.8</v>
       </c>
       <c r="Q20">
-        <v>-0</v>
+        <v>0.06150206978119457</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>0.4928909952606635</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
       <c r="U20">
-        <v>83.2</v>
+        <v>0.001</v>
       </c>
       <c r="V20">
-        <v>1.170182841068917</v>
+        <v>2.956830277942046e-06</v>
       </c>
       <c r="W20">
-        <v>-0.01342170671085336</v>
+        <v>0.1631863882443929</v>
       </c>
       <c r="X20">
-        <v>0.04983790867631634</v>
+        <v>0.05884552124202438</v>
       </c>
       <c r="Y20">
-        <v>-0.0632596153871697</v>
+        <v>0.1043408670023685</v>
       </c>
       <c r="Z20">
-        <v>0.2249979545640494</v>
+        <v>0.2371956808477342</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.04976301200890947</v>
+        <v>0.05051200808030974</v>
       </c>
       <c r="AC20">
-        <v>-0.04976301200890947</v>
+        <v>-0.05051200808030974</v>
       </c>
       <c r="AD20">
-        <v>0.606</v>
+        <v>238.2</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>0.606</v>
+        <v>238.2</v>
       </c>
       <c r="AG20">
-        <v>-82.59400000000001</v>
+        <v>238.199</v>
       </c>
       <c r="AH20">
-        <v>0.008451175633838173</v>
+        <v>0.4132546842470506</v>
       </c>
       <c r="AI20">
-        <v>0.005760127749367907</v>
+        <v>0.4469881778945393</v>
       </c>
       <c r="AJ20">
-        <v>7.185836088393937</v>
+        <v>0.413253666297131</v>
       </c>
       <c r="AK20">
-        <v>-3.753249113878036</v>
+        <v>0.4469871401522615</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2996,7 +3023,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Time Finance plc (AIM:TIME)</t>
+          <t>Nationwide Building Society (LSE:NBS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3005,10 +3032,10 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.05690000000000001</v>
+        <v>0.09630000000000001</v>
       </c>
       <c r="E21">
-        <v>-0.225</v>
+        <v>0.199</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3023,91 +3050,91 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>1.16</v>
+        <v>2023.3</v>
       </c>
       <c r="L21">
-        <v>0.04142857142857143</v>
+        <v>0.3357672712789791</v>
       </c>
       <c r="M21">
-        <v>-0</v>
+        <v>438.1</v>
       </c>
       <c r="N21">
-        <v>-0</v>
+        <v>0.2743612224448898</v>
       </c>
       <c r="O21">
-        <v>-0</v>
+        <v>0.2165274551475313</v>
       </c>
       <c r="P21">
-        <v>-0</v>
+        <v>222.1</v>
       </c>
       <c r="Q21">
-        <v>-0</v>
+        <v>0.1390906813627255</v>
       </c>
       <c r="R21">
-        <v>-0</v>
+        <v>0.1097711659170662</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>216</v>
+      </c>
+      <c r="T21">
+        <v>0.4930381191508788</v>
       </c>
       <c r="U21">
-        <v>3.99</v>
+        <v>35398.9</v>
       </c>
       <c r="V21">
-        <v>0.1734782608695652</v>
+        <v>22.1686497995992</v>
       </c>
       <c r="W21">
-        <v>0.01430332922318126</v>
+        <v>0.1114790408604046</v>
       </c>
       <c r="X21">
-        <v>0.05168477842645464</v>
+        <v>0.3357485510995897</v>
       </c>
       <c r="Y21">
-        <v>-0.03738144920327338</v>
+        <v>-0.2242695102391851</v>
       </c>
       <c r="Z21">
-        <v>0.7541071909507137</v>
+        <v>0.2046326670605894</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.05075223147187594</v>
+        <v>0.05079515034544582</v>
       </c>
       <c r="AC21">
-        <v>-0.05075223147187594</v>
+        <v>-0.05079515034544582</v>
       </c>
       <c r="AD21">
-        <v>5.36</v>
+        <v>46070.6</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>5.36</v>
+        <v>46070.6</v>
       </c>
       <c r="AG21">
-        <v>1.37</v>
+        <v>10671.7</v>
       </c>
       <c r="AH21">
-        <v>0.1889985895627645</v>
+        <v>0.9665012146666274</v>
       </c>
       <c r="AI21">
-        <v>0.06831506500127454</v>
+        <v>0.6850850582916964</v>
       </c>
       <c r="AJ21">
-        <v>0.05621665982765696</v>
+        <v>0.8698455393894935</v>
       </c>
       <c r="AK21">
-        <v>0.01839666979991943</v>
+        <v>0.3350706927354304</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-0.001</v>
-      </c>
-      <c r="AQ21">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3118,7 +3145,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nationwide Building Society (LSE:NBS)</t>
+          <t>Distribution Finance Capital Holdings plc (AIM:DFCH)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3126,12 +3153,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D22">
-        <v>0.0507</v>
-      </c>
-      <c r="E22">
-        <v>0.123</v>
-      </c>
       <c r="G22">
         <v>0</v>
       </c>
@@ -3145,85 +3166,82 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>1443</v>
+        <v>15.3</v>
       </c>
       <c r="L22">
-        <v>0.3215742205780759</v>
+        <v>0.4872611464968153</v>
       </c>
       <c r="M22">
-        <v>207.3</v>
+        <v>-0</v>
       </c>
       <c r="N22">
-        <v>0.1302790346907994</v>
+        <v>-0</v>
       </c>
       <c r="O22">
-        <v>0.1436590436590437</v>
+        <v>-0</v>
       </c>
       <c r="P22">
-        <v>207.3</v>
+        <v>-0</v>
       </c>
       <c r="Q22">
-        <v>0.1302790346907994</v>
+        <v>-0</v>
       </c>
       <c r="R22">
-        <v>0.1436590436590437</v>
+        <v>-0</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
       <c r="U22">
-        <v>37507.1</v>
+        <v>59.3</v>
       </c>
       <c r="V22">
-        <v>23.5715811965812</v>
+        <v>1.167322834645669</v>
       </c>
       <c r="W22">
-        <v>0.07172395967950375</v>
+        <v>0.1462715105162524</v>
       </c>
       <c r="X22">
-        <v>0.3020690273052963</v>
+        <v>0.05219948911699019</v>
       </c>
       <c r="Y22">
-        <v>-0.2303450676257925</v>
+        <v>0.09407202139926221</v>
       </c>
       <c r="Z22">
-        <v>0.1254350238581759</v>
+        <v>1.424941005627156</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.05197937462730839</v>
+        <v>0.05182179079435752</v>
       </c>
       <c r="AC22">
-        <v>-0.05197937462730839</v>
+        <v>-0.05182179079435752</v>
       </c>
       <c r="AD22">
-        <v>48804.9</v>
+        <v>1.46</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>48804.9</v>
+        <v>1.46</v>
       </c>
       <c r="AG22">
-        <v>11297.8</v>
+        <v>-57.84</v>
       </c>
       <c r="AH22">
-        <v>0.9684261282123022</v>
+        <v>0.02793723689246077</v>
       </c>
       <c r="AI22">
-        <v>0.7289263604388054</v>
+        <v>0.01149063434597828</v>
       </c>
       <c r="AJ22">
-        <v>0.8765458918457599</v>
+        <v>8.215909090909092</v>
       </c>
       <c r="AK22">
-        <v>0.383660357111324</v>
+        <v>-0.8536009445100354</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3240,7 +3258,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Provident Financial plc (LSE:PFG)</t>
+          <t>Time Finance plc (AIM:TIME)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3249,10 +3267,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>-0.0668</v>
+        <v>-0.0211</v>
       </c>
       <c r="E23">
-        <v>-0.283</v>
+        <v>-0.116</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3267,91 +3285,91 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>47.4</v>
+        <v>4.27</v>
       </c>
       <c r="L23">
-        <v>0.08735716918540361</v>
+        <v>0.1286144578313253</v>
       </c>
       <c r="M23">
-        <v>36.6</v>
+        <v>-0</v>
       </c>
       <c r="N23">
-        <v>0.06329989622967831</v>
+        <v>-0</v>
       </c>
       <c r="O23">
-        <v>0.7721518987341772</v>
+        <v>-0</v>
       </c>
       <c r="P23">
-        <v>36.6</v>
+        <v>-0</v>
       </c>
       <c r="Q23">
-        <v>0.06329989622967831</v>
+        <v>-0</v>
       </c>
       <c r="R23">
-        <v>0.7721518987341772</v>
+        <v>-0</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
       <c r="U23">
-        <v>679.9</v>
+        <v>4.67</v>
       </c>
       <c r="V23">
-        <v>1.175890695261155</v>
+        <v>0.1096244131455399</v>
       </c>
       <c r="W23">
-        <v>0.0569164265129683</v>
+        <v>0.05841313269493844</v>
       </c>
       <c r="X23">
-        <v>0.08098533434674891</v>
+        <v>0.05293515190669039</v>
       </c>
       <c r="Y23">
-        <v>-0.02406890783378061</v>
+        <v>0.005477980788248051</v>
       </c>
       <c r="Z23">
-        <v>0.2256414521561942</v>
+        <v>0.826487428429176</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.05389021797611744</v>
+        <v>0.05200679173149277</v>
       </c>
       <c r="AC23">
-        <v>-0.05389021797611744</v>
+        <v>-0.05200679173149277</v>
       </c>
       <c r="AD23">
-        <v>2194.3</v>
+        <v>4.41</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>2194.3</v>
+        <v>4.41</v>
       </c>
       <c r="AG23">
-        <v>1514.4</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="AH23">
-        <v>0.7914517583408477</v>
+        <v>0.09380982769623483</v>
       </c>
       <c r="AI23">
-        <v>0.7501880341880343</v>
+        <v>0.05457245390421978</v>
       </c>
       <c r="AJ23">
-        <v>0.7236930134760584</v>
+        <v>-0.00614076523382144</v>
       </c>
       <c r="AK23">
-        <v>0.6745356554273751</v>
+        <v>-0.003414762280010504</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>-0.001</v>
+      </c>
+      <c r="AQ23">
+        <v>-0</v>
       </c>
     </row>
     <row r="24">
@@ -3362,7 +3380,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LendInvest plc (AIM:LINV)</t>
+          <t>Develop North PLC (LSE:DVNO)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3370,8 +3388,14 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D24">
+        <v>-0.161</v>
+      </c>
+      <c r="E24">
+        <v>-0.31</v>
+      </c>
       <c r="G24">
-        <v>0.02453245324532453</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -3383,28 +3407,28 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>16.7</v>
+        <v>0.245</v>
       </c>
       <c r="L24">
-        <v>0.1837183718371837</v>
+        <v>0.2683461117196057</v>
       </c>
       <c r="M24">
-        <v>6.8</v>
+        <v>1.33</v>
       </c>
       <c r="N24">
-        <v>0.05</v>
+        <v>0.05115384615384615</v>
       </c>
       <c r="O24">
-        <v>0.407185628742515</v>
+        <v>5.428571428571429</v>
       </c>
       <c r="P24">
-        <v>6.8</v>
+        <v>1.33</v>
       </c>
       <c r="Q24">
-        <v>0.05</v>
+        <v>0.05115384615384615</v>
       </c>
       <c r="R24">
-        <v>0.407185628742515</v>
+        <v>5.428571428571429</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -3413,64 +3437,61 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>126.2</v>
+        <v>1</v>
       </c>
       <c r="V24">
-        <v>0.9279411764705883</v>
+        <v>0.03846153846153846</v>
       </c>
       <c r="W24">
-        <v>0.1160528144544823</v>
+        <v>0.008687943262411348</v>
       </c>
       <c r="X24">
-        <v>0.1324557212632135</v>
+        <v>0.05327509686545572</v>
       </c>
       <c r="Y24">
-        <v>-0.0164029068087312</v>
+        <v>-0.04458715360304438</v>
       </c>
       <c r="Z24">
-        <v>0.06283265362549251</v>
+        <v>0.02919544640573037</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.05450519949981583</v>
+        <v>0.05227606160534334</v>
       </c>
       <c r="AC24">
-        <v>-0.05450519949981583</v>
+        <v>-0.05227606160534334</v>
       </c>
       <c r="AD24">
-        <v>1367.1</v>
+        <v>3.59</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>1367.1</v>
+        <v>3.59</v>
       </c>
       <c r="AG24">
-        <v>1240.9</v>
+        <v>2.59</v>
       </c>
       <c r="AH24">
-        <v>0.9095203246623644</v>
+        <v>0.1213247718823927</v>
       </c>
       <c r="AI24">
-        <v>0.9532143355180589</v>
+        <v>0.1189135475322955</v>
       </c>
       <c r="AJ24">
-        <v>0.9012273948725398</v>
+        <v>0.09059111577474641</v>
       </c>
       <c r="AK24">
-        <v>0.9487003058103977</v>
+        <v>0.08872901678657073</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-0.223</v>
-      </c>
-      <c r="AQ24">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3481,7 +3502,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Morses Club PLC (AIM:MCL)</t>
+          <t>OSB Group Plc (LSE:OSB)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3490,7 +3511,10 @@
         </is>
       </c>
       <c r="D25">
-        <v>-0.0108</v>
+        <v>0.177</v>
+      </c>
+      <c r="E25">
+        <v>0.136</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3499,91 +3523,91 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0.0006976399905056576</v>
+        <v>0.0003217211803234367</v>
       </c>
       <c r="J25">
-        <v>0.0006976399905056576</v>
+        <v>0.0002463154524965877</v>
       </c>
       <c r="K25">
-        <v>-60.7</v>
+        <v>330.9</v>
       </c>
       <c r="L25">
-        <v>-0.5148430873621713</v>
+        <v>0.45616211745244</v>
       </c>
       <c r="M25">
-        <v>1.58</v>
+        <v>314.8</v>
       </c>
       <c r="N25">
-        <v>0.8229166666666667</v>
+        <v>0.1356487266772956</v>
       </c>
       <c r="O25">
-        <v>-0.02602965403624382</v>
+        <v>0.9513448171653067</v>
       </c>
       <c r="P25">
-        <v>1.58</v>
+        <v>185.2</v>
       </c>
       <c r="Q25">
-        <v>0.8229166666666667</v>
+        <v>0.07980350756237342</v>
       </c>
       <c r="R25">
-        <v>-0.02602965403624382</v>
+        <v>0.5596857056512542</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>129.6</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>0.4116899618805591</v>
       </c>
       <c r="U25">
-        <v>9.359999999999999</v>
+        <v>4009.5</v>
       </c>
       <c r="V25">
-        <v>4.875</v>
+        <v>1.727711466367906</v>
       </c>
       <c r="W25">
-        <v>-0.6450584484590861</v>
+        <v>0.1336591671042534</v>
       </c>
       <c r="X25">
-        <v>0.1264298841819819</v>
+        <v>0.08337491899218422</v>
       </c>
       <c r="Y25">
-        <v>-0.771488332641068</v>
+        <v>0.05028424811206914</v>
       </c>
       <c r="Z25">
-        <v>1.267690938518407</v>
+        <v>0.1380626058562147</v>
       </c>
       <c r="AA25">
-        <v>0.0008843918943120895</v>
+        <v>3.400695323433158e-05</v>
       </c>
       <c r="AB25">
-        <v>0.06469932512492069</v>
+        <v>0.05264788703177176</v>
       </c>
       <c r="AC25">
-        <v>-0.06381493323060859</v>
+        <v>-0.05261388007853742</v>
       </c>
       <c r="AD25">
-        <v>17.8</v>
+        <v>7420.4</v>
       </c>
       <c r="AE25">
-        <v>0.09374122559691486</v>
+        <v>0.638117278966895</v>
       </c>
       <c r="AF25">
-        <v>17.89374122559692</v>
+        <v>7421.038117278967</v>
       </c>
       <c r="AG25">
-        <v>8.533741225596916</v>
+        <v>3411.538117278967</v>
       </c>
       <c r="AH25">
-        <v>0.9030975534534793</v>
+        <v>0.7617776240685671</v>
       </c>
       <c r="AI25">
-        <v>0.4916708374299167</v>
+        <v>0.7386882563051335</v>
       </c>
       <c r="AJ25">
-        <v>0.8163336973275453</v>
+        <v>0.5951494071740321</v>
       </c>
       <c r="AK25">
-        <v>0.3156700049165499</v>
+        <v>0.5651293879246003</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -3592,10 +3616,10 @@
         <v>0</v>
       </c>
       <c r="AN25">
-        <v>176.2376237623762</v>
+        <v>20555.12465373961</v>
       </c>
       <c r="AP25">
-        <v>84.49248738214769</v>
+        <v>9450.244092185503</v>
       </c>
     </row>
     <row r="26">
@@ -3606,7 +3630,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Non-Standard Finance plc (LSE:NSF)</t>
+          <t>Vanquis Banking Group plc (LSE:VANQ)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3615,10 +3639,10 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.0756</v>
+        <v>-0.0795</v>
       </c>
       <c r="G26">
-        <v>0.07415730337078652</v>
+        <v>0.002731770273177028</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -3630,82 +3654,85 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>-70.90000000000001</v>
+        <v>57.8</v>
       </c>
       <c r="L26">
-        <v>-0.6127917026793431</v>
+        <v>0.1243278124327812</v>
       </c>
       <c r="M26">
-        <v>-0</v>
+        <v>49.99</v>
       </c>
       <c r="N26">
-        <v>-0</v>
+        <v>0.1198226270373921</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>0.8648788927335641</v>
       </c>
       <c r="P26">
-        <v>-0</v>
+        <v>49.1</v>
       </c>
       <c r="Q26">
-        <v>-0</v>
+        <v>0.1176893576222435</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>0.8494809688581315</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>0.8900000000000006</v>
+      </c>
+      <c r="T26">
+        <v>0.01780356071214244</v>
       </c>
       <c r="U26">
-        <v>135.4</v>
+        <v>568.4</v>
       </c>
       <c r="V26">
-        <v>71.64021164021165</v>
+        <v>1.36241610738255</v>
       </c>
       <c r="W26">
-        <v>2.802371541501977</v>
+        <v>0.07910223073764883</v>
       </c>
       <c r="X26">
-        <v>1.836822515088024</v>
+        <v>0.1185773543729684</v>
       </c>
       <c r="Y26">
-        <v>0.9655490264139523</v>
+        <v>-0.03947512363531956</v>
       </c>
       <c r="Z26">
-        <v>0.388255033557047</v>
+        <v>0.2153710738441582</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.06622572312752834</v>
+        <v>0.05275310049350043</v>
       </c>
       <c r="AC26">
-        <v>-0.06622572312752834</v>
+        <v>-0.05275310049350043</v>
       </c>
       <c r="AD26">
-        <v>410.6</v>
+        <v>2827</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>410.6</v>
+        <v>2827</v>
       </c>
       <c r="AG26">
-        <v>275.2</v>
+        <v>2258.6</v>
       </c>
       <c r="AH26">
-        <v>0.9954180707411089</v>
+        <v>0.8714012699586956</v>
       </c>
       <c r="AI26">
-        <v>1.296904611497157</v>
+        <v>0.7915663325306602</v>
       </c>
       <c r="AJ26">
-        <v>0.9931791114800246</v>
+        <v>0.8440840122580163</v>
       </c>
       <c r="AK26">
-        <v>1.518763796909492</v>
+        <v>0.7521145521145521</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -3722,7 +3749,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TruFin plc (AIM:TRU)</t>
+          <t>LendInvest plc (AIM:LINV)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3730,116 +3757,104 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D27">
-        <v>0.421</v>
-      </c>
       <c r="G27">
-        <v>-0.07613636363636364</v>
+        <v>0.06813953488372093</v>
       </c>
       <c r="H27">
-        <v>-0.07613636363636364</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>-0.1443181818181818</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>-0.1443181818181818</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>-6.99</v>
+        <v>-14.9</v>
       </c>
       <c r="L27">
-        <v>-0.3971590909090909</v>
+        <v>-0.3465116279069768</v>
       </c>
       <c r="M27">
-        <v>-0</v>
+        <v>2.07</v>
       </c>
       <c r="N27">
-        <v>-0</v>
+        <v>0.043125</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>-0.1389261744966443</v>
       </c>
       <c r="P27">
-        <v>-0</v>
+        <v>2.07</v>
       </c>
       <c r="Q27">
-        <v>-0</v>
+        <v>0.043125</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>-0.1389261744966443</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
       <c r="U27">
-        <v>15.7</v>
+        <v>107.4</v>
       </c>
       <c r="V27">
-        <v>0.2079470198675497</v>
+        <v>2.2375</v>
       </c>
       <c r="W27">
-        <v>-0.1509719222462203</v>
+        <v>-0.2220566318926975</v>
       </c>
       <c r="X27">
-        <v>0.05199041145181046</v>
+        <v>0.2660273009404678</v>
       </c>
       <c r="Y27">
-        <v>-0.2029623336980308</v>
+        <v>-0.4880839328331653</v>
       </c>
       <c r="Z27">
-        <v>0.7242798353909465</v>
+        <v>0.03287461773700306</v>
       </c>
       <c r="AA27">
-        <v>-0.1045267489711934</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.05087579699253563</v>
+        <v>0.05283436501117021</v>
       </c>
       <c r="AC27">
-        <v>-0.155402545963729</v>
+        <v>-0.05283436501117021</v>
       </c>
       <c r="AD27">
-        <v>20.4</v>
+        <v>1044.7</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>20.4</v>
+        <v>1044.7</v>
       </c>
       <c r="AG27">
-        <v>4.699999999999999</v>
+        <v>937.3000000000001</v>
       </c>
       <c r="AH27">
-        <v>0.2127215849843587</v>
+        <v>0.9560721149446325</v>
       </c>
       <c r="AI27">
-        <v>0.2837273991655076</v>
+        <v>0.9268920237778369</v>
       </c>
       <c r="AJ27">
-        <v>0.05860349127182043</v>
+        <v>0.9512838729321019</v>
       </c>
       <c r="AK27">
-        <v>0.08362989323843414</v>
+        <v>0.9191919191919192</v>
       </c>
       <c r="AL27">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>7.25</v>
-      </c>
-      <c r="AN27">
-        <v>-17.14285714285714</v>
-      </c>
-      <c r="AO27">
-        <v>-0.3503448275862069</v>
-      </c>
-      <c r="AP27">
-        <v>-3.949579831932773</v>
-      </c>
-      <c r="AQ27">
-        <v>-0.3503448275862069</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -3850,7 +3865,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M&amp;G plc (LSE:MNG)</t>
+          <t>Funding Circle Holdings plc (LSE:FCH)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3858,104 +3873,119 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="F28">
-        <v>-0.07980000000000001</v>
+      <c r="D28">
+        <v>0.05690000000000001</v>
+      </c>
+      <c r="G28">
+        <v>0.01177072671443194</v>
+      </c>
+      <c r="H28">
+        <v>-0.06960081883316274</v>
+      </c>
+      <c r="I28">
+        <v>-0.1970317297850563</v>
+      </c>
+      <c r="J28">
+        <v>-0.1970317297850563</v>
       </c>
       <c r="K28">
-        <v>-871.3</v>
+        <v>-40.8</v>
+      </c>
+      <c r="L28">
+        <v>-0.2088024564994882</v>
       </c>
       <c r="M28">
-        <v>670.8</v>
+        <v>7.5</v>
       </c>
       <c r="N28">
-        <v>0.1292012558023074</v>
+        <v>0.0416204217536071</v>
       </c>
       <c r="O28">
-        <v>-0.7698840812578905</v>
+        <v>-0.1838235294117647</v>
       </c>
       <c r="P28">
-        <v>567.5</v>
+        <v>-0</v>
       </c>
       <c r="Q28">
-        <v>0.1093048787534429</v>
+        <v>-0</v>
       </c>
       <c r="R28">
-        <v>-0.6513256054171928</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>103.3</v>
+        <v>7.5</v>
       </c>
       <c r="T28">
-        <v>0.1539952295766249</v>
+        <v>1</v>
       </c>
       <c r="U28">
-        <v>6911.7</v>
+        <v>258.6</v>
       </c>
       <c r="V28">
-        <v>1.331246749744795</v>
+        <v>1.435072142064373</v>
       </c>
       <c r="W28">
-        <v>-0.1239420190898875</v>
+        <v>-0.1121803684355238</v>
       </c>
       <c r="X28">
-        <v>0.06581833473781512</v>
+        <v>0.05560174905293659</v>
       </c>
       <c r="Y28">
-        <v>-0.1897603538277026</v>
+        <v>-0.1677821174884604</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>0.7561919504643964</v>
       </c>
       <c r="AA28">
-        <v>-0.1363449766919969</v>
+        <v>-0.1489938080495356</v>
       </c>
       <c r="AB28">
-        <v>0.05221982390853745</v>
+        <v>0.05217829993836916</v>
       </c>
       <c r="AC28">
-        <v>-0.1885648006005343</v>
+        <v>-0.2011721079879047</v>
       </c>
       <c r="AD28">
-        <v>10130.6</v>
+        <v>67.5</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>10130.6</v>
+        <v>67.5</v>
       </c>
       <c r="AG28">
-        <v>3218.900000000001</v>
+        <v>-191.1</v>
       </c>
       <c r="AH28">
-        <v>0.6611584271496166</v>
+        <v>0.2725070649979814</v>
       </c>
       <c r="AI28">
-        <v>0.6775278719661859</v>
+        <v>0.1674107142857143</v>
       </c>
       <c r="AJ28">
-        <v>0.382710324820469</v>
+        <v>17.53211009174307</v>
       </c>
       <c r="AK28">
-        <v>0.4003308210830038</v>
+        <v>-1.321576763485478</v>
       </c>
       <c r="AL28">
-        <v>390.1</v>
+        <v>1.14</v>
       </c>
       <c r="AM28">
-        <v>390.1</v>
+        <v>-1.78</v>
       </c>
       <c r="AN28">
-        <v>-7.655558074510694</v>
+        <v>-1.945244956772334</v>
       </c>
       <c r="AO28">
-        <v>-3.831325301204819</v>
+        <v>-33.7719298245614</v>
       </c>
       <c r="AP28">
-        <v>-2.432479407541752</v>
+        <v>5.507204610951009</v>
       </c>
       <c r="AQ28">
-        <v>-3.831325301204819</v>
+        <v>21.62921348314607</v>
       </c>
     </row>
     <row r="29">
@@ -3966,7 +3996,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Insig AI Plc (AIM:INSG)</t>
+          <t>TruFin plc (AIM:TRU)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3974,23 +4004,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D29">
+        <v>0.359</v>
+      </c>
       <c r="G29">
-        <v>-1.360406091370558</v>
+        <v>-0.1373390557939914</v>
       </c>
       <c r="H29">
-        <v>-1.360406091370558</v>
+        <v>-0.1373390557939914</v>
       </c>
       <c r="I29">
-        <v>-3.548223350253807</v>
+        <v>-0.1991416309012875</v>
       </c>
       <c r="J29">
-        <v>-3.548223350253807</v>
+        <v>-0.1991416309012875</v>
       </c>
       <c r="K29">
-        <v>-7.07</v>
+        <v>-11.3</v>
       </c>
       <c r="L29">
-        <v>-3.588832487309645</v>
+        <v>-0.4849785407725322</v>
       </c>
       <c r="M29">
         <v>-0</v>
@@ -4014,73 +4047,73 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>0.167</v>
+        <v>6.35</v>
       </c>
       <c r="V29">
-        <v>0.008652849740932642</v>
+        <v>0.1058333333333333</v>
       </c>
       <c r="W29">
-        <v>-0.1526997840172786</v>
+        <v>-0.2494481236203091</v>
       </c>
       <c r="X29">
-        <v>0.05050087887194694</v>
+        <v>0.05632726506397474</v>
       </c>
       <c r="Y29">
-        <v>-0.2032006628892256</v>
+        <v>-0.3057753886842838</v>
       </c>
       <c r="Z29">
-        <v>0.04482162358937022</v>
+        <v>0.8381294964028781</v>
       </c>
       <c r="AA29">
-        <v>-0.1590371314160903</v>
+        <v>-0.166906474820144</v>
       </c>
       <c r="AB29">
-        <v>0.05042721441917038</v>
+        <v>0.05283349791854744</v>
       </c>
       <c r="AC29">
-        <v>-0.2094643458352607</v>
+        <v>-0.2197399727386914</v>
       </c>
       <c r="AD29">
-        <v>1.72</v>
+        <v>26.9</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>1.72</v>
+        <v>26.9</v>
       </c>
       <c r="AG29">
-        <v>1.553</v>
+        <v>20.55</v>
       </c>
       <c r="AH29">
-        <v>0.08182683158896289</v>
+        <v>0.3095512082853855</v>
       </c>
       <c r="AI29">
-        <v>0.04709748083242059</v>
+        <v>0.3821022727272727</v>
       </c>
       <c r="AJ29">
-        <v>0.0744736968301923</v>
+        <v>0.25512104283054</v>
       </c>
       <c r="AK29">
-        <v>0.04271999559871262</v>
+        <v>0.3208430913348946</v>
       </c>
       <c r="AL29">
-        <v>0.016</v>
+        <v>5.77</v>
       </c>
       <c r="AM29">
-        <v>0.016</v>
+        <v>5.77</v>
       </c>
       <c r="AN29">
-        <v>-0.296551724137931</v>
+        <v>-9.572953736654803</v>
       </c>
       <c r="AO29">
-        <v>-436.875</v>
+        <v>-0.804159445407279</v>
       </c>
       <c r="AP29">
-        <v>-0.2677586206896552</v>
+        <v>-7.313167259786476</v>
       </c>
       <c r="AQ29">
-        <v>-436.875</v>
+        <v>-0.804159445407279</v>
       </c>
     </row>
     <row r="30">
@@ -4091,7 +4124,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>City of London Group plc (AIM:CIN)</t>
+          <t>Software Circle plc (AIM:SFT)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4099,23 +4132,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D30">
+        <v>-0.0159</v>
+      </c>
       <c r="G30">
-        <v>-2.582677165354331</v>
+        <v>0.07615384615384617</v>
       </c>
       <c r="H30">
-        <v>-2.582677165354331</v>
+        <v>0.01956043956043956</v>
       </c>
       <c r="I30">
-        <v>-2.236220472440945</v>
+        <v>-0.0554945054945055</v>
       </c>
       <c r="J30">
-        <v>-2.236220472440945</v>
+        <v>-0.0554945054945055</v>
       </c>
       <c r="K30">
-        <v>-16.3</v>
+        <v>-3.06</v>
       </c>
       <c r="L30">
-        <v>-2.566929133858268</v>
+        <v>-0.1681318681318681</v>
       </c>
       <c r="M30">
         <v>-0</v>
@@ -4139,73 +4175,784 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>63.2</v>
+        <v>22.8</v>
       </c>
       <c r="V30">
-        <v>1.726775956284153</v>
+        <v>0.3397913561847988</v>
       </c>
       <c r="W30">
-        <v>-0.2730318257956449</v>
+        <v>-1.53</v>
       </c>
       <c r="X30">
-        <v>0.04995096928615156</v>
+        <v>0.0540719307638575</v>
       </c>
       <c r="Y30">
-        <v>-0.3229827950817964</v>
+        <v>-1.584071930763858</v>
       </c>
       <c r="Z30">
-        <v>0.2003154574132491</v>
+        <v>3.221238938053097</v>
       </c>
       <c r="AA30">
-        <v>-0.44794952681388</v>
+        <v>-0.1787610619469026</v>
       </c>
       <c r="AB30">
-        <v>0.04988125724766303</v>
+        <v>0.05244896054804059</v>
       </c>
       <c r="AC30">
-        <v>-0.497830784061543</v>
+        <v>-0.2312100224949432</v>
       </c>
       <c r="AD30">
-        <v>0.8149999999999999</v>
+        <v>14.7</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>0.8149999999999999</v>
+        <v>14.7</v>
       </c>
       <c r="AG30">
-        <v>-62.38500000000001</v>
+        <v>-8.100000000000001</v>
       </c>
       <c r="AH30">
-        <v>0.02178270747026594</v>
+        <v>0.1797066014669927</v>
       </c>
       <c r="AI30">
-        <v>0.01798521460884917</v>
+        <v>0.3491686460807601</v>
       </c>
       <c r="AJ30">
-        <v>2.419429901105294</v>
+        <v>-0.1372881355932204</v>
       </c>
       <c r="AK30">
-        <v>3.488118535085266</v>
+        <v>-0.4196891191709846</v>
       </c>
       <c r="AL30">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AM30">
-        <v>2.11</v>
+        <v>1.791</v>
       </c>
       <c r="AN30">
-        <v>-0.05821428571428571</v>
+        <v>6.176470588235294</v>
       </c>
       <c r="AO30">
-        <v>-6.729857819905213</v>
+        <v>-0.5101010101010101</v>
       </c>
       <c r="AP30">
-        <v>4.456071428571429</v>
+        <v>-3.403361344537816</v>
       </c>
       <c r="AQ30">
-        <v>-6.729857819905213</v>
+        <v>-0.5639307649357901</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Insig AI Plc (AIM:INSG)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G31">
+        <v>-2.340080971659919</v>
+      </c>
+      <c r="H31">
+        <v>-2.340080971659919</v>
+      </c>
+      <c r="I31">
+        <v>-1.890688259109311</v>
+      </c>
+      <c r="J31">
+        <v>-1.890688259109311</v>
+      </c>
+      <c r="K31">
+        <v>-21.4</v>
+      </c>
+      <c r="L31">
+        <v>-8.663967611336032</v>
+      </c>
+      <c r="M31">
+        <v>-0</v>
+      </c>
+      <c r="N31">
+        <v>-0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>-0</v>
+      </c>
+      <c r="Q31">
+        <v>-0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0.805</v>
+      </c>
+      <c r="V31">
+        <v>0.03049242424242424</v>
+      </c>
+      <c r="W31">
+        <v>-0.6131805157593123</v>
+      </c>
+      <c r="X31">
+        <v>0.05298249231088696</v>
+      </c>
+      <c r="Y31">
+        <v>-0.6661630080701992</v>
+      </c>
+      <c r="Z31">
+        <v>0.1999514288027201</v>
+      </c>
+      <c r="AA31">
+        <v>-0.3780458188294343</v>
+      </c>
+      <c r="AB31">
+        <v>0.05220622775197077</v>
+      </c>
+      <c r="AC31">
+        <v>-0.4302520465814051</v>
+      </c>
+      <c r="AD31">
+        <v>2.86</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>2.86</v>
+      </c>
+      <c r="AG31">
+        <v>2.055</v>
+      </c>
+      <c r="AH31">
+        <v>0.09774436090225565</v>
+      </c>
+      <c r="AI31">
+        <v>0.1377649325626204</v>
+      </c>
+      <c r="AJ31">
+        <v>0.07221929362150764</v>
+      </c>
+      <c r="AK31">
+        <v>0.102981708844901</v>
+      </c>
+      <c r="AL31">
+        <v>0.16</v>
+      </c>
+      <c r="AM31">
+        <v>0.16</v>
+      </c>
+      <c r="AN31">
+        <v>-0.4680851063829787</v>
+      </c>
+      <c r="AO31">
+        <v>-29.1875</v>
+      </c>
+      <c r="AP31">
+        <v>-0.3363338788870703</v>
+      </c>
+      <c r="AQ31">
+        <v>-29.1875</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CAB Payments Holdings Limited (LSE:CABP)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G32">
+        <v>-0.3427109974424553</v>
+      </c>
+      <c r="H32">
+        <v>-0.3427109974424553</v>
+      </c>
+      <c r="I32">
+        <v>-0.1254475703324808</v>
+      </c>
+      <c r="J32">
+        <v>-0.08718431420042887</v>
+      </c>
+      <c r="K32">
+        <v>46.2</v>
+      </c>
+      <c r="L32">
+        <v>0.5907928388746804</v>
+      </c>
+      <c r="M32">
+        <v>16.3</v>
+      </c>
+      <c r="N32">
+        <v>0.06082089552238806</v>
+      </c>
+      <c r="O32">
+        <v>0.3528138528138528</v>
+      </c>
+      <c r="P32">
+        <v>16.3</v>
+      </c>
+      <c r="Q32">
+        <v>0.06082089552238806</v>
+      </c>
+      <c r="R32">
+        <v>0.3528138528138528</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>818.5</v>
+      </c>
+      <c r="V32">
+        <v>3.05410447761194</v>
+      </c>
+      <c r="X32">
+        <v>0.051967779096029</v>
+      </c>
+      <c r="AB32">
+        <v>0.05193203676043481</v>
+      </c>
+      <c r="AD32">
+        <v>1.39</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>1.39</v>
+      </c>
+      <c r="AG32">
+        <v>-817.11</v>
+      </c>
+      <c r="AH32">
+        <v>0.005159805486469431</v>
+      </c>
+      <c r="AI32">
+        <v>0.008671782394410131</v>
+      </c>
+      <c r="AJ32">
+        <v>1.488062501138205</v>
+      </c>
+      <c r="AK32">
+        <v>1.241412315218547</v>
+      </c>
+      <c r="AL32">
+        <v>27.3</v>
+      </c>
+      <c r="AM32">
+        <v>27.3</v>
+      </c>
+      <c r="AN32">
+        <v>-0.1177966101694915</v>
+      </c>
+      <c r="AO32">
+        <v>-0.3593406593406593</v>
+      </c>
+      <c r="AP32">
+        <v>69.24661016949152</v>
+      </c>
+      <c r="AQ32">
+        <v>-0.3593406593406593</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cornerstone FS plc (AIM:CSFS)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G33">
+        <v>-0.7061445783132531</v>
+      </c>
+      <c r="H33">
+        <v>-0.791566265060241</v>
+      </c>
+      <c r="I33">
+        <v>-0.4072289156626506</v>
+      </c>
+      <c r="J33">
+        <v>-0.4072289156626506</v>
+      </c>
+      <c r="K33">
+        <v>-3.25</v>
+      </c>
+      <c r="L33">
+        <v>-0.3915662650602409</v>
+      </c>
+      <c r="M33">
+        <v>-0</v>
+      </c>
+      <c r="N33">
+        <v>-0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>-0</v>
+      </c>
+      <c r="Q33">
+        <v>-0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>1.04</v>
+      </c>
+      <c r="V33">
+        <v>0.06190476190476191</v>
+      </c>
+      <c r="W33">
+        <v>-2.152317880794702</v>
+      </c>
+      <c r="X33">
+        <v>0.0535329276028867</v>
+      </c>
+      <c r="Y33">
+        <v>-2.205850808397589</v>
+      </c>
+      <c r="AB33">
+        <v>0.05311300561702897</v>
+      </c>
+      <c r="AD33">
+        <v>2.76</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>2.76</v>
+      </c>
+      <c r="AG33">
+        <v>1.72</v>
+      </c>
+      <c r="AH33">
+        <v>0.1411042944785276</v>
+      </c>
+      <c r="AI33">
+        <v>0.8458473797119215</v>
+      </c>
+      <c r="AJ33">
+        <v>0.09287257019438444</v>
+      </c>
+      <c r="AK33">
+        <v>0.7737291947818263</v>
+      </c>
+      <c r="AL33">
+        <v>0.163</v>
+      </c>
+      <c r="AM33">
+        <v>0.115</v>
+      </c>
+      <c r="AN33">
+        <v>-0.8189910979228485</v>
+      </c>
+      <c r="AO33">
+        <v>-20.7361963190184</v>
+      </c>
+      <c r="AP33">
+        <v>-0.5103857566765577</v>
+      </c>
+      <c r="AQ33">
+        <v>-29.39130434782609</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PCI-PAL PLC (AIM:PCIP)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>0.494</v>
+      </c>
+      <c r="G34">
+        <v>-0.03105263157894737</v>
+      </c>
+      <c r="H34">
+        <v>-0.09526315789473684</v>
+      </c>
+      <c r="I34">
+        <v>-0.17</v>
+      </c>
+      <c r="J34">
+        <v>-0.17</v>
+      </c>
+      <c r="K34">
+        <v>-6.22</v>
+      </c>
+      <c r="L34">
+        <v>-0.3273684210526316</v>
+      </c>
+      <c r="M34">
+        <v>-0</v>
+      </c>
+      <c r="N34">
+        <v>-0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>-0</v>
+      </c>
+      <c r="Q34">
+        <v>-0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>1.49</v>
+      </c>
+      <c r="V34">
+        <v>0.02838095238095238</v>
+      </c>
+      <c r="W34">
+        <v>-27.64444444444444</v>
+      </c>
+      <c r="X34">
+        <v>0.05193268338376234</v>
+      </c>
+      <c r="Y34">
+        <v>-27.6963771278282</v>
+      </c>
+      <c r="AB34">
+        <v>0.05191830729563532</v>
+      </c>
+      <c r="AD34">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AG34">
+        <v>-1.405</v>
+      </c>
+      <c r="AH34">
+        <v>0.001616430541028811</v>
+      </c>
+      <c r="AI34">
+        <v>-0.01655306718597858</v>
+      </c>
+      <c r="AJ34">
+        <v>-0.02749779821900382</v>
+      </c>
+      <c r="AK34">
+        <v>0.2120754716981132</v>
+      </c>
+      <c r="AL34">
+        <v>0.006</v>
+      </c>
+      <c r="AM34">
+        <v>0.002</v>
+      </c>
+      <c r="AN34">
+        <v>-0.04696132596685083</v>
+      </c>
+      <c r="AO34">
+        <v>-538.3333333333334</v>
+      </c>
+      <c r="AP34">
+        <v>0.7762430939226519</v>
+      </c>
+      <c r="AQ34">
+        <v>-1615</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ADVFN Plc (AIM:AFN)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>-0.09960000000000001</v>
+      </c>
+      <c r="G35">
+        <v>-0.1057803468208093</v>
+      </c>
+      <c r="H35">
+        <v>-0.1408959537572254</v>
+      </c>
+      <c r="I35">
+        <v>-0.1411849710982659</v>
+      </c>
+      <c r="J35">
+        <v>-0.1411849710982659</v>
+      </c>
+      <c r="K35">
+        <v>-2.76</v>
+      </c>
+      <c r="L35">
+        <v>-0.3988439306358381</v>
+      </c>
+      <c r="M35">
+        <v>-0</v>
+      </c>
+      <c r="N35">
+        <v>-0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>-0</v>
+      </c>
+      <c r="Q35">
+        <v>-0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>7.06</v>
+      </c>
+      <c r="V35">
+        <v>0.7300930713547052</v>
+      </c>
+      <c r="W35">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="X35">
+        <v>0.0519554143787424</v>
+      </c>
+      <c r="Y35">
+        <v>-1.766241128664456</v>
+      </c>
+      <c r="AB35">
+        <v>0.05192834816386582</v>
+      </c>
+      <c r="AD35">
+        <v>0.038</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0.038</v>
+      </c>
+      <c r="AG35">
+        <v>-7.021999999999999</v>
+      </c>
+      <c r="AH35">
+        <v>0.003914297486608982</v>
+      </c>
+      <c r="AI35">
+        <v>0.005631298162418494</v>
+      </c>
+      <c r="AJ35">
+        <v>-2.651812688821751</v>
+      </c>
+      <c r="AK35">
+        <v>22.5064102564103</v>
+      </c>
+      <c r="AL35">
+        <v>0.014</v>
+      </c>
+      <c r="AM35">
+        <v>-0.016</v>
+      </c>
+      <c r="AN35">
+        <v>-0.03897435897435898</v>
+      </c>
+      <c r="AO35">
+        <v>-69.78571428571428</v>
+      </c>
+      <c r="AP35">
+        <v>7.202051282051282</v>
+      </c>
+      <c r="AQ35">
+        <v>61.0625</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Amigo Holdings PLC (LSE:AMGO)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>-0.52</v>
+      </c>
+      <c r="G36">
+        <v>-5.162548764629389</v>
+      </c>
+      <c r="H36">
+        <v>-5.162548764629389</v>
+      </c>
+      <c r="I36">
+        <v>-4.902470741222367</v>
+      </c>
+      <c r="J36">
+        <v>-4.902470741222367</v>
+      </c>
+      <c r="K36">
+        <v>-35.3</v>
+      </c>
+      <c r="L36">
+        <v>-4.59037711313394</v>
+      </c>
+      <c r="M36">
+        <v>-0</v>
+      </c>
+      <c r="N36">
+        <v>-0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>-0</v>
+      </c>
+      <c r="Q36">
+        <v>-0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>148.4</v>
+      </c>
+      <c r="V36">
+        <v>122.6446280991736</v>
+      </c>
+      <c r="W36">
+        <v>-0.9005102040816325</v>
+      </c>
+      <c r="X36">
+        <v>0.05191675589446192</v>
+      </c>
+      <c r="Y36">
+        <v>-0.9524269599760944</v>
+      </c>
+      <c r="AB36">
+        <v>0.05191675589446192</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>-148.4</v>
+      </c>
+      <c r="AH36">
+        <v>0</v>
+      </c>
+      <c r="AI36">
+        <v>0</v>
+      </c>
+      <c r="AJ36">
+        <v>1.008220667164889</v>
+      </c>
+      <c r="AK36">
+        <v>1.050099065949618</v>
+      </c>
+      <c r="AL36">
+        <v>2.2</v>
+      </c>
+      <c r="AM36">
+        <v>-2.8</v>
+      </c>
+      <c r="AN36">
+        <v>-0</v>
+      </c>
+      <c r="AO36">
+        <v>-17.13636363636364</v>
+      </c>
+      <c r="AP36">
+        <v>3.978552278820376</v>
+      </c>
+      <c r="AQ36">
+        <v>13.46428571428572</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07780000000000001</v>
+        <v>0.08990000000000001</v>
       </c>
       <c r="E2">
-        <v>0.0725</v>
+        <v>0.0253</v>
       </c>
       <c r="F2">
-        <v>0.128</v>
+        <v>0.134</v>
       </c>
       <c r="G2">
-        <v>0.2298088914483595</v>
+        <v>0.2004688035005493</v>
       </c>
       <c r="H2">
-        <v>0.2289832079235108</v>
+        <v>0.1971570115335773</v>
       </c>
       <c r="I2">
-        <v>0.1475407394818246</v>
+        <v>0.1418937400887118</v>
       </c>
       <c r="J2">
-        <v>0.108638311525027</v>
+        <v>0.1168388563988931</v>
       </c>
       <c r="K2">
-        <v>2387.2</v>
+        <v>3831.16</v>
       </c>
       <c r="L2">
-        <v>0.09104257323412418</v>
+        <v>0.1076130149289618</v>
       </c>
       <c r="M2">
-        <v>3917.7</v>
+        <v>4785.947999999999</v>
       </c>
       <c r="N2">
-        <v>0.04696873786128414</v>
+        <v>0.04549151473276675</v>
       </c>
       <c r="O2">
-        <v>1.641127680965148</v>
+        <v>1.249216425312438</v>
       </c>
       <c r="P2">
-        <v>1599.2</v>
+        <v>2039.098</v>
       </c>
       <c r="Q2">
-        <v>0.01917257717226067</v>
+        <v>0.01938208620498075</v>
       </c>
       <c r="R2">
-        <v>0.6699061662198392</v>
+        <v>0.5322403658421992</v>
       </c>
       <c r="S2">
-        <v>2318.5</v>
+        <v>2746.85</v>
       </c>
       <c r="T2">
-        <v>0.5918013119942824</v>
+        <v>0.5739406278547113</v>
       </c>
       <c r="U2">
-        <v>50753.4</v>
+        <v>62579.53</v>
       </c>
       <c r="V2">
-        <v>0.608475161489879</v>
+        <v>0.5948325412153704</v>
       </c>
       <c r="W2">
-        <v>0.03453140216026841</v>
+        <v>0.0821174075330845</v>
       </c>
       <c r="X2">
-        <v>0.07757361247519262</v>
+        <v>0.06060969506067813</v>
       </c>
       <c r="Y2">
-        <v>-0.04304221031492422</v>
+        <v>0.02150771247240637</v>
       </c>
       <c r="Z2">
-        <v>0.4601895532959192</v>
+        <v>0.4883459555739683</v>
       </c>
       <c r="AA2">
-        <v>0.0937252564234432</v>
+        <v>2.040365259127968E-05</v>
       </c>
       <c r="AB2">
-        <v>0.05660344347465013</v>
+        <v>0.05751340943596429</v>
       </c>
       <c r="AC2">
-        <v>0.03712181294879309</v>
+        <v>-0.05281611167364651</v>
       </c>
       <c r="AD2">
-        <v>88332.39999999999</v>
+        <v>102364.63</v>
       </c>
       <c r="AE2">
-        <v>23.14266134460699</v>
+        <v>130.4882389597281</v>
       </c>
       <c r="AF2">
-        <v>88355.5426613446</v>
+        <v>102495.1182389597</v>
       </c>
       <c r="AG2">
-        <v>37602.1426613446</v>
+        <v>39915.58823895972</v>
       </c>
       <c r="AH2">
-        <v>0.5143938055172242</v>
+        <v>0.4934757668893885</v>
       </c>
       <c r="AI2">
-        <v>0.5864626044220657</v>
+        <v>0.5862919516668986</v>
       </c>
       <c r="AJ2">
-        <v>0.310728272814375</v>
+        <v>0.2750506248538112</v>
       </c>
       <c r="AK2">
-        <v>0.3763788259298114</v>
+        <v>0.3556280153339209</v>
       </c>
       <c r="AL2">
-        <v>996.4</v>
+        <v>1181.055</v>
       </c>
       <c r="AM2">
-        <v>733.5</v>
+        <v>864.7220000000001</v>
       </c>
       <c r="AN2">
-        <v>16.39808790086787</v>
+        <v>15.3373747695415</v>
       </c>
       <c r="AO2">
-        <v>3.878763548775592</v>
+        <v>4.255254835718913</v>
       </c>
       <c r="AP2">
-        <v>6.980487800871509</v>
+        <v>5.980584660615959</v>
       </c>
       <c r="AQ2">
-        <v>5.268984321745058</v>
+        <v>5.811914118063378</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Paysafe Limited (NYSE:PSFE)</t>
+          <t>Wise plc (LSE:WISE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,32 +724,35 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="F3">
+        <v>0.137</v>
+      </c>
       <c r="G3">
-        <v>0.2569587477196493</v>
+        <v>0.2980824270177447</v>
       </c>
       <c r="H3">
-        <v>0.2516330253633849</v>
+        <v>0.2932169433314253</v>
       </c>
       <c r="I3">
-        <v>0.09375711630146449</v>
+        <v>0.3760831032113335</v>
       </c>
       <c r="J3">
-        <v>0.09375711630146449</v>
+        <v>0.2798352647478768</v>
       </c>
       <c r="K3">
-        <v>-23.5</v>
+        <v>578.1</v>
       </c>
       <c r="L3">
-        <v>-0.01382922379803449</v>
+        <v>0.2757584430452204</v>
       </c>
       <c r="M3">
-        <v>32.3</v>
+        <v>99.5</v>
       </c>
       <c r="N3">
-        <v>0.0310816012317167</v>
+        <v>0.007306774371213512</v>
       </c>
       <c r="O3">
-        <v>-1.374468085106383</v>
+        <v>0.1721155509427435</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,82 +761,82 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>32.3</v>
+        <v>99.5</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>241.4</v>
+        <v>1422.3</v>
       </c>
       <c r="V3">
-        <v>0.2322940723633564</v>
+        <v>0.1044464843032862</v>
       </c>
       <c r="W3">
-        <v>-0.02676842464973232</v>
+        <v>0.6396326620933835</v>
       </c>
       <c r="X3">
-        <v>0.07987341715197471</v>
+        <v>0.05820719506269216</v>
       </c>
       <c r="Y3">
-        <v>-0.106641841801707</v>
+        <v>0.5814254670306914</v>
       </c>
       <c r="Z3">
-        <v>1.417686901026673</v>
+        <v>7.53837927892438</v>
       </c>
       <c r="AA3">
-        <v>0.1329182356586206</v>
+        <v>2.109504361287713</v>
       </c>
       <c r="AB3">
-        <v>0.06682568749027462</v>
+        <v>0.05804954618515386</v>
       </c>
       <c r="AC3">
-        <v>0.06609254816834595</v>
+        <v>2.051454815102559</v>
       </c>
       <c r="AD3">
-        <v>2431.8</v>
+        <v>70.2</v>
       </c>
       <c r="AE3">
-        <v>23.14266134460699</v>
+        <v>106.8969121388022</v>
       </c>
       <c r="AF3">
-        <v>2454.942661344607</v>
+        <v>177.0969121388022</v>
       </c>
       <c r="AG3">
-        <v>2213.542661344607</v>
+        <v>-1245.203087861198</v>
       </c>
       <c r="AH3">
-        <v>0.7025879877497337</v>
+        <v>0.01283813606637267</v>
       </c>
       <c r="AI3">
-        <v>0.7367901884463743</v>
+        <v>0.1011926316253945</v>
       </c>
       <c r="AJ3">
-        <v>0.6805157652494959</v>
+        <v>-0.100644455649904</v>
       </c>
       <c r="AK3">
-        <v>0.716231064864692</v>
+        <v>-3.798702921685635</v>
       </c>
       <c r="AL3">
-        <v>150.9</v>
+        <v>27.3</v>
       </c>
       <c r="AM3">
-        <v>150.9</v>
+        <v>-10.6</v>
       </c>
       <c r="AN3">
-        <v>5.53877690468056</v>
+        <v>0.0861878453038674</v>
       </c>
       <c r="AO3">
-        <v>1.030483764082174</v>
+        <v>28.07692307692308</v>
       </c>
       <c r="AP3">
-        <v>5.041664187096246</v>
+        <v>-1.528794460234742</v>
       </c>
       <c r="AQ3">
-        <v>1.030483764082174</v>
+        <v>-72.311320754717</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>London Stock Exchange Group plc (LSE:LSEG)</t>
+          <t>Finseta Plc (AIM:FIN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -852,125 +855,113 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.311</v>
-      </c>
-      <c r="E4">
-        <v>0.0725</v>
-      </c>
-      <c r="F4">
-        <v>0.115</v>
-      </c>
       <c r="G4">
-        <v>0.3424046726302891</v>
+        <v>0.1494285714285714</v>
       </c>
       <c r="H4">
-        <v>0.3412438851373137</v>
+        <v>0.08714285714285715</v>
       </c>
       <c r="I4">
-        <v>0.2014242678286825</v>
+        <v>0.1021428571428571</v>
       </c>
       <c r="J4">
-        <v>0.1426116056590065</v>
+        <v>0.1021428571428571</v>
       </c>
       <c r="K4">
-        <v>860.6</v>
+        <v>3.22</v>
       </c>
       <c r="L4">
-        <v>0.07928362829004947</v>
+        <v>0.23</v>
       </c>
       <c r="M4">
-        <v>3069.8</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.04088689043597321</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>3.567046246804555</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>783.6</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.01043682563868285</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.9105275389263304</v>
+        <v>-0</v>
       </c>
       <c r="S4">
-        <v>2286.2</v>
-      </c>
-      <c r="T4">
-        <v>0.7447390709492475</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>4620.4</v>
+        <v>3.5</v>
       </c>
       <c r="V4">
-        <v>0.06153944510077876</v>
+        <v>0.1411290322580645</v>
       </c>
       <c r="W4">
-        <v>0.02756486840545916</v>
+        <v>6.401590457256462</v>
       </c>
       <c r="X4">
-        <v>0.05978887345104975</v>
+        <v>0.05942508176087307</v>
       </c>
       <c r="Y4">
-        <v>-0.03222400504559059</v>
+        <v>6.342165375495589</v>
       </c>
       <c r="Z4">
-        <v>0.7510499768209399</v>
+        <v>16.6073546856465</v>
       </c>
       <c r="AA4">
-        <v>0.1071084431245939</v>
+        <v>1.69632265717675</v>
       </c>
       <c r="AB4">
-        <v>0.05751892745696689</v>
+        <v>0.05855073565698923</v>
       </c>
       <c r="AC4">
-        <v>0.04958951566762698</v>
+        <v>1.637771921519761</v>
       </c>
       <c r="AD4">
-        <v>13809.4</v>
+        <v>3.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>13809.4</v>
+        <v>3.6</v>
       </c>
       <c r="AG4">
-        <v>9189</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.1553543323917169</v>
+        <v>0.1267605633802817</v>
       </c>
       <c r="AI4">
-        <v>0.3039067245310258</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="AJ4">
-        <v>0.1090432696130145</v>
+        <v>0.004016064257028116</v>
       </c>
       <c r="AK4">
-        <v>0.2251146519285042</v>
+        <v>0.0335570469798658</v>
       </c>
       <c r="AL4">
-        <v>419.6</v>
+        <v>0.222</v>
       </c>
       <c r="AM4">
-        <v>156.7</v>
+        <v>-0.305</v>
       </c>
       <c r="AN4">
-        <v>4.288500357131766</v>
+        <v>2.482758620689655</v>
       </c>
       <c r="AO4">
-        <v>5.21067683508103</v>
+        <v>6.441441441441441</v>
       </c>
       <c r="AP4">
-        <v>2.853638085773734</v>
+        <v>0.06896551724137938</v>
       </c>
       <c r="AQ4">
-        <v>13.95277600510529</v>
+        <v>-4.688524590163934</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M&amp;G plc (LSE:MNG)</t>
+          <t>PayPoint plc (LSE:PAY)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,124 +981,124 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.228</v>
+        <v>0.119</v>
       </c>
       <c r="E5">
-        <v>-0.272</v>
+        <v>-0.0154</v>
       </c>
       <c r="F5">
-        <v>0.141</v>
+        <v>0.14</v>
       </c>
       <c r="G5">
-        <v>0.2387321339776364</v>
+        <v>0.2234576932455498</v>
       </c>
       <c r="H5">
-        <v>0.2387321339776364</v>
+        <v>0.2070226773957571</v>
       </c>
       <c r="I5">
-        <v>0.1941706723106935</v>
+        <v>0.1850768105340161</v>
       </c>
       <c r="J5">
-        <v>0.09708533615534674</v>
+        <v>0.1373397573342078</v>
       </c>
       <c r="K5">
-        <v>211.1</v>
+        <v>53.9</v>
       </c>
       <c r="L5">
-        <v>0.02691537784804478</v>
+        <v>0.1314313582053158</v>
       </c>
       <c r="M5">
-        <v>585.1</v>
+        <v>43.12</v>
       </c>
       <c r="N5">
-        <v>0.100962865819989</v>
+        <v>0.06200747771067013</v>
       </c>
       <c r="O5">
-        <v>2.77167219327333</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="P5">
-        <v>585.1</v>
+        <v>37.2</v>
       </c>
       <c r="Q5">
-        <v>0.100962865819989</v>
+        <v>0.05349439171699742</v>
       </c>
       <c r="R5">
-        <v>2.77167219327333</v>
+        <v>0.6901669758812616</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>5.920000000000002</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.137291280148423</v>
       </c>
       <c r="U5">
-        <v>6824.5</v>
+        <v>27.4</v>
       </c>
       <c r="V5">
-        <v>1.177612506902264</v>
+        <v>0.03940178314639057</v>
       </c>
       <c r="W5">
-        <v>0.04149793591507765</v>
+        <v>0.3986686390532544</v>
       </c>
       <c r="X5">
-        <v>0.07527380779841054</v>
+        <v>0.06006986051434157</v>
       </c>
       <c r="Y5">
-        <v>-0.0337758718833329</v>
+        <v>0.3385987785389128</v>
       </c>
       <c r="Z5">
-        <v>0.8275407276103655</v>
+        <v>4.10921843687375</v>
       </c>
       <c r="AA5">
-        <v>0.08034206972229256</v>
+        <v>0.5643590629534936</v>
       </c>
       <c r="AB5">
-        <v>0.05568795949233336</v>
+        <v>0.05710133655764432</v>
       </c>
       <c r="AC5">
-        <v>0.0246541102299592</v>
+        <v>0.5072577263958493</v>
       </c>
       <c r="AD5">
-        <v>10799.1</v>
+        <v>149.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>10799.1</v>
+        <v>149.6</v>
       </c>
       <c r="AG5">
-        <v>3974.6</v>
+        <v>122.2</v>
       </c>
       <c r="AH5">
-        <v>0.6507716505064993</v>
+        <v>0.1770414201183432</v>
       </c>
       <c r="AI5">
-        <v>0.6956210868052871</v>
+        <v>0.5171102661596959</v>
       </c>
       <c r="AJ5">
-        <v>0.4068251141272084</v>
+        <v>0.1494618395303327</v>
       </c>
       <c r="AK5">
-        <v>0.4568558259290336</v>
+        <v>0.466590301641848</v>
       </c>
       <c r="AL5">
-        <v>425.9</v>
+        <v>10.1</v>
       </c>
       <c r="AM5">
-        <v>425.9</v>
+        <v>-3</v>
       </c>
       <c r="AN5">
-        <v>6.250926140310257</v>
+        <v>1.523421588594705</v>
       </c>
       <c r="AO5">
-        <v>3.575722000469594</v>
+        <v>7.514851485148515</v>
       </c>
       <c r="AP5">
-        <v>2.30064829821718</v>
+        <v>1.244399185336049</v>
       </c>
       <c r="AQ5">
-        <v>3.575722000469594</v>
+        <v>-25.3</v>
       </c>
     </row>
     <row r="6">
@@ -1118,118 +1109,3023 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>TruFin plc (AIM:TRU)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.4429999999999999</v>
+      </c>
+      <c r="G6">
+        <v>-0.03904555314533623</v>
+      </c>
+      <c r="H6">
+        <v>-0.03904555314533623</v>
+      </c>
+      <c r="I6">
+        <v>0.3817787418655098</v>
+      </c>
+      <c r="J6">
+        <v>0.3817787418655098</v>
+      </c>
+      <c r="K6">
+        <v>3.22</v>
+      </c>
+      <c r="L6">
+        <v>0.06984815618221259</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>-0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>-0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>12.9</v>
+      </c>
+      <c r="V6">
+        <v>0.1172727272727273</v>
+      </c>
+      <c r="W6">
+        <v>0.08944444444444445</v>
+      </c>
+      <c r="X6">
+        <v>0.05852131319707713</v>
+      </c>
+      <c r="Y6">
+        <v>0.03092313124736732</v>
+      </c>
+      <c r="Z6">
+        <v>1.244264507422402</v>
+      </c>
+      <c r="AA6">
+        <v>0.475033738191633</v>
+      </c>
+      <c r="AB6">
+        <v>0.05795492887143974</v>
+      </c>
+      <c r="AC6">
+        <v>0.4170788093201933</v>
+      </c>
+      <c r="AD6">
+        <v>5.18</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>5.18</v>
+      </c>
+      <c r="AG6">
+        <v>-7.720000000000001</v>
+      </c>
+      <c r="AH6">
+        <v>0.04497308560513977</v>
+      </c>
+      <c r="AI6">
+        <v>0.0961395694135115</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.07547907704341025</v>
+      </c>
+      <c r="AK6">
+        <v>-0.1883845778428502</v>
+      </c>
+      <c r="AL6">
+        <v>20</v>
+      </c>
+      <c r="AM6">
+        <v>20</v>
+      </c>
+      <c r="AN6">
+        <v>0.2784946236559139</v>
+      </c>
+      <c r="AO6">
+        <v>0.8800000000000001</v>
+      </c>
+      <c r="AP6">
+        <v>-0.4150537634408602</v>
+      </c>
+      <c r="AQ6">
+        <v>0.8800000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Aquis Exchange PLC (AIM:AQX)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.313</v>
+      </c>
+      <c r="G7">
+        <v>0.2517549668874172</v>
+      </c>
+      <c r="H7">
+        <v>0.2248344370860927</v>
+      </c>
+      <c r="I7">
+        <v>0.1950331125827814</v>
+      </c>
+      <c r="J7">
+        <v>0.1899531803480671</v>
+      </c>
+      <c r="K7">
+        <v>6.28</v>
+      </c>
+      <c r="L7">
+        <v>0.2079470198675497</v>
+      </c>
+      <c r="M7">
+        <v>1.8</v>
+      </c>
+      <c r="N7">
+        <v>0.007805724197745013</v>
+      </c>
+      <c r="O7">
+        <v>0.286624203821656</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>-0</v>
+      </c>
+      <c r="S7">
+        <v>1.8</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>18.4</v>
+      </c>
+      <c r="V7">
+        <v>0.07979184735472679</v>
+      </c>
+      <c r="W7">
+        <v>0.2025806451612903</v>
+      </c>
+      <c r="X7">
+        <v>0.05822721759887323</v>
+      </c>
+      <c r="Y7">
+        <v>0.1443534275624171</v>
+      </c>
+      <c r="Z7">
+        <v>1.750217328310634</v>
+      </c>
+      <c r="AA7">
+        <v>0.3324593478129022</v>
+      </c>
+      <c r="AB7">
+        <v>0.05807135838120171</v>
+      </c>
+      <c r="AC7">
+        <v>0.2743879894317005</v>
+      </c>
+      <c r="AD7">
+        <v>3.5</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>3.5</v>
+      </c>
+      <c r="AG7">
+        <v>-14.9</v>
+      </c>
+      <c r="AH7">
+        <v>0.0149508756941478</v>
+      </c>
+      <c r="AI7">
+        <v>0.08663366336633664</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.06907742234585072</v>
+      </c>
+      <c r="AK7">
+        <v>-0.6772727272727272</v>
+      </c>
+      <c r="AL7">
+        <v>0.112</v>
+      </c>
+      <c r="AM7">
+        <v>-0.554</v>
+      </c>
+      <c r="AN7">
+        <v>0.5434782608695652</v>
+      </c>
+      <c r="AO7">
+        <v>52.58928571428571</v>
+      </c>
+      <c r="AP7">
+        <v>-2.313664596273291</v>
+      </c>
+      <c r="AQ7">
+        <v>-10.63176895306859</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Equals Group plc (AIM:EQLS)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.32</v>
+      </c>
+      <c r="E8">
+        <v>0.528</v>
+      </c>
+      <c r="G8">
+        <v>0.1587982832618026</v>
+      </c>
+      <c r="H8">
+        <v>0.1587982832618026</v>
+      </c>
+      <c r="I8">
+        <v>0.09871244635193133</v>
+      </c>
+      <c r="J8">
+        <v>0.08191540910978817</v>
+      </c>
+      <c r="K8">
+        <v>10.3</v>
+      </c>
+      <c r="L8">
+        <v>0.07367668097281831</v>
+      </c>
+      <c r="M8">
+        <v>3.545</v>
+      </c>
+      <c r="N8">
+        <v>0.01115832546427447</v>
+      </c>
+      <c r="O8">
+        <v>0.3441747572815534</v>
+      </c>
+      <c r="P8">
+        <v>3.54</v>
+      </c>
+      <c r="Q8">
+        <v>0.01114258734655335</v>
+      </c>
+      <c r="R8">
+        <v>0.3436893203883495</v>
+      </c>
+      <c r="S8">
+        <v>0.004999999999999893</v>
+      </c>
+      <c r="T8">
+        <v>0.001410437235542988</v>
+      </c>
+      <c r="U8">
+        <v>25.9</v>
+      </c>
+      <c r="V8">
+        <v>0.08152344979540446</v>
+      </c>
+      <c r="W8">
+        <v>0.1685761047463175</v>
+      </c>
+      <c r="X8">
+        <v>0.05820569484022292</v>
+      </c>
+      <c r="Y8">
+        <v>0.1103704099060946</v>
+      </c>
+      <c r="Z8">
+        <v>3.240611961057024</v>
+      </c>
+      <c r="AA8">
+        <v>0.2654560545560591</v>
+      </c>
+      <c r="AB8">
+        <v>0.05805001335610099</v>
+      </c>
+      <c r="AC8">
+        <v>0.2074060411999581</v>
+      </c>
+      <c r="AD8">
+        <v>4.08</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>4.08</v>
+      </c>
+      <c r="AG8">
+        <v>-21.82</v>
+      </c>
+      <c r="AH8">
+        <v>0.01267947044564609</v>
+      </c>
+      <c r="AI8">
+        <v>0.04946653734238603</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.07374611328917129</v>
+      </c>
+      <c r="AK8">
+        <v>-0.3856486390950866</v>
+      </c>
+      <c r="AL8">
+        <v>0.22</v>
+      </c>
+      <c r="AM8">
+        <v>0.22</v>
+      </c>
+      <c r="AN8">
+        <v>0.1714285714285714</v>
+      </c>
+      <c r="AO8">
+        <v>62.72727272727273</v>
+      </c>
+      <c r="AP8">
+        <v>-0.9168067226890756</v>
+      </c>
+      <c r="AQ8">
+        <v>62.72727272727273</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ramsdens Holdings PLC (AIM:RFX)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>0.1394101876675603</v>
+      </c>
+      <c r="H9">
+        <v>0.1394101876675603</v>
+      </c>
+      <c r="I9">
+        <v>0.1322609472743521</v>
+      </c>
+      <c r="J9">
+        <v>0.09879491970644784</v>
+      </c>
+      <c r="K9">
+        <v>9.82</v>
+      </c>
+      <c r="L9">
+        <v>0.08775692582663092</v>
+      </c>
+      <c r="M9">
+        <v>4.17</v>
+      </c>
+      <c r="N9">
+        <v>0.04493534482758621</v>
+      </c>
+      <c r="O9">
+        <v>0.4246435845213849</v>
+      </c>
+      <c r="P9">
+        <v>4.17</v>
+      </c>
+      <c r="Q9">
+        <v>0.04493534482758621</v>
+      </c>
+      <c r="R9">
+        <v>0.4246435845213849</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>17.2</v>
+      </c>
+      <c r="V9">
+        <v>0.1853448275862069</v>
+      </c>
+      <c r="W9">
+        <v>0.1845864661654135</v>
+      </c>
+      <c r="X9">
+        <v>0.06060969506067813</v>
+      </c>
+      <c r="Y9">
+        <v>0.1239767711047354</v>
+      </c>
+      <c r="Z9">
+        <v>1.903061224489796</v>
+      </c>
+      <c r="AA9">
+        <v>0.1880127808699237</v>
+      </c>
+      <c r="AB9">
+        <v>0.0568905435622014</v>
+      </c>
+      <c r="AC9">
+        <v>0.1311222373077223</v>
+      </c>
+      <c r="AD9">
+        <v>25.4</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>25.4</v>
+      </c>
+      <c r="AG9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AH9">
+        <v>0.2148900169204738</v>
+      </c>
+      <c r="AI9">
+        <v>0.2963827304550758</v>
+      </c>
+      <c r="AJ9">
+        <v>0.08118811881188118</v>
+      </c>
+      <c r="AK9">
+        <v>0.1197080291970803</v>
+      </c>
+      <c r="AL9">
+        <v>1.3</v>
+      </c>
+      <c r="AM9">
+        <v>1.3</v>
+      </c>
+      <c r="AN9">
+        <v>1.494117647058824</v>
+      </c>
+      <c r="AO9">
+        <v>11.38461538461539</v>
+      </c>
+      <c r="AP9">
+        <v>0.4823529411764705</v>
+      </c>
+      <c r="AQ9">
+        <v>11.38461538461539</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H&amp;T Group plc (AIM:HAT)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.102</v>
+      </c>
+      <c r="E10">
+        <v>0.138</v>
+      </c>
+      <c r="G10">
+        <v>0.1477234401349072</v>
+      </c>
+      <c r="H10">
+        <v>0.1477234401349072</v>
+      </c>
+      <c r="I10">
+        <v>0.1564924114671163</v>
+      </c>
+      <c r="J10">
+        <v>0.1236605741333813</v>
+      </c>
+      <c r="K10">
+        <v>27.5</v>
+      </c>
+      <c r="L10">
+        <v>0.09274873524451939</v>
+      </c>
+      <c r="M10">
+        <v>9.25</v>
+      </c>
+      <c r="N10">
+        <v>0.04792746113989637</v>
+      </c>
+      <c r="O10">
+        <v>0.3363636363636364</v>
+      </c>
+      <c r="P10">
+        <v>9.25</v>
+      </c>
+      <c r="Q10">
+        <v>0.04792746113989637</v>
+      </c>
+      <c r="R10">
+        <v>0.3363636363636364</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>20</v>
+      </c>
+      <c r="V10">
+        <v>0.1036269430051813</v>
+      </c>
+      <c r="W10">
+        <v>0.1297781972628598</v>
+      </c>
+      <c r="X10">
+        <v>0.06318691356694903</v>
+      </c>
+      <c r="Y10">
+        <v>0.0665912836959108</v>
+      </c>
+      <c r="Z10">
+        <v>1.284105673451711</v>
+      </c>
+      <c r="AA10">
+        <v>0.1587932448269708</v>
+      </c>
+      <c r="AB10">
+        <v>0.05770639530717193</v>
+      </c>
+      <c r="AC10">
+        <v>0.1010868495197988</v>
+      </c>
+      <c r="AD10">
+        <v>106.8</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>106.8</v>
+      </c>
+      <c r="AG10">
+        <v>86.8</v>
+      </c>
+      <c r="AH10">
+        <v>0.3562374916611074</v>
+      </c>
+      <c r="AI10">
+        <v>0.3188059701492537</v>
+      </c>
+      <c r="AJ10">
+        <v>0.3102215868477484</v>
+      </c>
+      <c r="AK10">
+        <v>0.2755555555555556</v>
+      </c>
+      <c r="AL10">
+        <v>6.42</v>
+      </c>
+      <c r="AM10">
+        <v>6.277</v>
+      </c>
+      <c r="AN10">
+        <v>2.015094339622642</v>
+      </c>
+      <c r="AO10">
+        <v>7.227414330218068</v>
+      </c>
+      <c r="AP10">
+        <v>1.637735849056604</v>
+      </c>
+      <c r="AQ10">
+        <v>7.392066273697626</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Paysafe Limited (NYSE:PSFE)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>0.2569587477196493</v>
+      </c>
+      <c r="H11">
+        <v>0.2516330253633849</v>
+      </c>
+      <c r="I11">
+        <v>0.09375711630146449</v>
+      </c>
+      <c r="J11">
+        <v>0.09375711630146449</v>
+      </c>
+      <c r="K11">
+        <v>-23.5</v>
+      </c>
+      <c r="L11">
+        <v>-0.01382922379803449</v>
+      </c>
+      <c r="M11">
+        <v>32.3</v>
+      </c>
+      <c r="N11">
+        <v>0.0310816012317167</v>
+      </c>
+      <c r="O11">
+        <v>-1.374468085106383</v>
+      </c>
+      <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>-0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>32.3</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>241.4</v>
+      </c>
+      <c r="V11">
+        <v>0.2322940723633564</v>
+      </c>
+      <c r="W11">
+        <v>-0.02676842464973232</v>
+      </c>
+      <c r="X11">
+        <v>0.07985750453023685</v>
+      </c>
+      <c r="Y11">
+        <v>-0.1066259291799692</v>
+      </c>
+      <c r="Z11">
+        <v>1.417686901026673</v>
+      </c>
+      <c r="AA11">
+        <v>0.1329182356586206</v>
+      </c>
+      <c r="AB11">
+        <v>0.06682095488542339</v>
+      </c>
+      <c r="AC11">
+        <v>0.06609728077319718</v>
+      </c>
+      <c r="AD11">
+        <v>2431.8</v>
+      </c>
+      <c r="AE11">
+        <v>23.14266134460699</v>
+      </c>
+      <c r="AF11">
+        <v>2454.942661344607</v>
+      </c>
+      <c r="AG11">
+        <v>2213.542661344607</v>
+      </c>
+      <c r="AH11">
+        <v>0.7025879877497337</v>
+      </c>
+      <c r="AI11">
+        <v>0.7367901884463743</v>
+      </c>
+      <c r="AJ11">
+        <v>0.6805157652494959</v>
+      </c>
+      <c r="AK11">
+        <v>0.716231064864692</v>
+      </c>
+      <c r="AL11">
+        <v>150.9</v>
+      </c>
+      <c r="AM11">
+        <v>150.9</v>
+      </c>
+      <c r="AN11">
+        <v>5.53877690468056</v>
+      </c>
+      <c r="AO11">
+        <v>1.030483764082174</v>
+      </c>
+      <c r="AP11">
+        <v>5.041664187096246</v>
+      </c>
+      <c r="AQ11">
+        <v>1.030483764082174</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>London Stock Exchange Group plc (LSE:LSEG)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.311</v>
+      </c>
+      <c r="E12">
+        <v>0.0725</v>
+      </c>
+      <c r="F12">
+        <v>0.115</v>
+      </c>
+      <c r="G12">
+        <v>0.3424046726302891</v>
+      </c>
+      <c r="H12">
+        <v>0.3412438851373137</v>
+      </c>
+      <c r="I12">
+        <v>0.2014242678286825</v>
+      </c>
+      <c r="J12">
+        <v>0.1426116056590065</v>
+      </c>
+      <c r="K12">
+        <v>860.6</v>
+      </c>
+      <c r="L12">
+        <v>0.07928362829004947</v>
+      </c>
+      <c r="M12">
+        <v>3069.8</v>
+      </c>
+      <c r="N12">
+        <v>0.04088689043597321</v>
+      </c>
+      <c r="O12">
+        <v>3.567046246804555</v>
+      </c>
+      <c r="P12">
+        <v>783.6</v>
+      </c>
+      <c r="Q12">
+        <v>0.01043682563868285</v>
+      </c>
+      <c r="R12">
+        <v>0.9105275389263304</v>
+      </c>
+      <c r="S12">
+        <v>2286.2</v>
+      </c>
+      <c r="T12">
+        <v>0.7447390709492475</v>
+      </c>
+      <c r="U12">
+        <v>4620.4</v>
+      </c>
+      <c r="V12">
+        <v>0.06153944510077876</v>
+      </c>
+      <c r="W12">
+        <v>0.02756486840545916</v>
+      </c>
+      <c r="X12">
+        <v>0.0597823405092326</v>
+      </c>
+      <c r="Y12">
+        <v>-0.03221747210377343</v>
+      </c>
+      <c r="Z12">
+        <v>0.7510499768209399</v>
+      </c>
+      <c r="AA12">
+        <v>0.1071084431245939</v>
+      </c>
+      <c r="AB12">
+        <v>0.05751340943596429</v>
+      </c>
+      <c r="AC12">
+        <v>0.04959503368862957</v>
+      </c>
+      <c r="AD12">
+        <v>13809.4</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>13809.4</v>
+      </c>
+      <c r="AG12">
+        <v>9189</v>
+      </c>
+      <c r="AH12">
+        <v>0.1553543323917169</v>
+      </c>
+      <c r="AI12">
+        <v>0.3039067245310258</v>
+      </c>
+      <c r="AJ12">
+        <v>0.1090432696130145</v>
+      </c>
+      <c r="AK12">
+        <v>0.2251146519285042</v>
+      </c>
+      <c r="AL12">
+        <v>419.6</v>
+      </c>
+      <c r="AM12">
+        <v>156.7</v>
+      </c>
+      <c r="AN12">
+        <v>4.288500357131766</v>
+      </c>
+      <c r="AO12">
+        <v>5.21067683508103</v>
+      </c>
+      <c r="AP12">
+        <v>2.853638085773734</v>
+      </c>
+      <c r="AQ12">
+        <v>13.95277600510529</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>International Personal Finance plc (LSE:IPF)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>-0.0322</v>
+      </c>
+      <c r="E13">
+        <v>-0.07200000000000001</v>
+      </c>
+      <c r="G13">
+        <v>0.2220254219629089</v>
+      </c>
+      <c r="H13">
+        <v>0.2220254219629089</v>
+      </c>
+      <c r="I13">
+        <v>0.2200458428839341</v>
+      </c>
+      <c r="J13">
+        <v>0.1304677938171985</v>
+      </c>
+      <c r="K13">
+        <v>61.9</v>
+      </c>
+      <c r="L13">
+        <v>0.06449260262554699</v>
+      </c>
+      <c r="M13">
+        <v>31.1</v>
+      </c>
+      <c r="N13">
+        <v>0.08800226372382569</v>
+      </c>
+      <c r="O13">
+        <v>0.5024232633279483</v>
+      </c>
+      <c r="P13">
+        <v>29.2</v>
+      </c>
+      <c r="Q13">
+        <v>0.08262591963780419</v>
+      </c>
+      <c r="R13">
+        <v>0.4717285945072698</v>
+      </c>
+      <c r="S13">
+        <v>1.899999999999999</v>
+      </c>
+      <c r="T13">
+        <v>0.0610932475884244</v>
+      </c>
+      <c r="U13">
+        <v>109.3</v>
+      </c>
+      <c r="V13">
+        <v>0.3092812676853424</v>
+      </c>
+      <c r="W13">
+        <v>0.105218425973143</v>
+      </c>
+      <c r="X13">
+        <v>0.07675566422647352</v>
+      </c>
+      <c r="Y13">
+        <v>0.02846276174666944</v>
+      </c>
+      <c r="Z13">
+        <v>0.7902190021406225</v>
+      </c>
+      <c r="AA13">
+        <v>0.1030981298417151</v>
+      </c>
+      <c r="AB13">
+        <v>0.05611607793805935</v>
+      </c>
+      <c r="AC13">
+        <v>0.04698205190365574</v>
+      </c>
+      <c r="AD13">
+        <v>715.9</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>715.9</v>
+      </c>
+      <c r="AG13">
+        <v>606.6</v>
+      </c>
+      <c r="AH13">
+        <v>0.6695034134480501</v>
+      </c>
+      <c r="AI13">
+        <v>0.5411186696900983</v>
+      </c>
+      <c r="AJ13">
+        <v>0.6318750000000001</v>
+      </c>
+      <c r="AK13">
+        <v>0.4997940182911758</v>
+      </c>
+      <c r="AL13">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="AM13">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="AN13">
+        <v>3.262989972652689</v>
+      </c>
+      <c r="AO13">
+        <v>2.268528464017186</v>
+      </c>
+      <c r="AP13">
+        <v>2.764813126709207</v>
+      </c>
+      <c r="AQ13">
+        <v>2.268528464017186</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M&amp;G plc (LSE:MNG)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>-0.228</v>
+      </c>
+      <c r="E14">
+        <v>-0.272</v>
+      </c>
+      <c r="F14">
+        <v>0.141</v>
+      </c>
+      <c r="G14">
+        <v>0.2387321339776364</v>
+      </c>
+      <c r="H14">
+        <v>0.2387321339776364</v>
+      </c>
+      <c r="I14">
+        <v>0.1941706723106935</v>
+      </c>
+      <c r="J14">
+        <v>0.09708533615534674</v>
+      </c>
+      <c r="K14">
+        <v>211.1</v>
+      </c>
+      <c r="L14">
+        <v>0.02691537784804478</v>
+      </c>
+      <c r="M14">
+        <v>585.1</v>
+      </c>
+      <c r="N14">
+        <v>0.100962865819989</v>
+      </c>
+      <c r="O14">
+        <v>2.77167219327333</v>
+      </c>
+      <c r="P14">
+        <v>585.1</v>
+      </c>
+      <c r="Q14">
+        <v>0.100962865819989</v>
+      </c>
+      <c r="R14">
+        <v>2.77167219327333</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>6824.5</v>
+      </c>
+      <c r="V14">
+        <v>1.177612506902264</v>
+      </c>
+      <c r="W14">
+        <v>0.04149793591507765</v>
+      </c>
+      <c r="X14">
+        <v>0.07526004323958808</v>
+      </c>
+      <c r="Y14">
+        <v>-0.03376210732451044</v>
+      </c>
+      <c r="Z14">
+        <v>0.8275407276103655</v>
+      </c>
+      <c r="AA14">
+        <v>0.08034206972229256</v>
+      </c>
+      <c r="AB14">
+        <v>0.05568315251817429</v>
+      </c>
+      <c r="AC14">
+        <v>0.02465891720411827</v>
+      </c>
+      <c r="AD14">
+        <v>10799.1</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>10799.1</v>
+      </c>
+      <c r="AG14">
+        <v>3974.6</v>
+      </c>
+      <c r="AH14">
+        <v>0.6507716505064993</v>
+      </c>
+      <c r="AI14">
+        <v>0.6956210868052871</v>
+      </c>
+      <c r="AJ14">
+        <v>0.4068251141272084</v>
+      </c>
+      <c r="AK14">
+        <v>0.4568558259290336</v>
+      </c>
+      <c r="AL14">
+        <v>425.9</v>
+      </c>
+      <c r="AM14">
+        <v>425.9</v>
+      </c>
+      <c r="AN14">
+        <v>6.250926140310257</v>
+      </c>
+      <c r="AO14">
+        <v>3.575722000469594</v>
+      </c>
+      <c r="AP14">
+        <v>2.30064829821718</v>
+      </c>
+      <c r="AQ14">
+        <v>3.575722000469594</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>W.A.G payment solutions plc (LSE:WPS)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="F15">
+        <v>0.158</v>
+      </c>
+      <c r="G15">
+        <v>0.04296103240993736</v>
+      </c>
+      <c r="H15">
+        <v>0.02127033502879482</v>
+      </c>
+      <c r="I15">
+        <v>0.01605784185968305</v>
+      </c>
+      <c r="J15">
+        <v>0.01605784185968305</v>
+      </c>
+      <c r="K15">
+        <v>-51.9</v>
+      </c>
+      <c r="L15">
+        <v>-0.02181680608684686</v>
+      </c>
+      <c r="M15">
+        <v>-0</v>
+      </c>
+      <c r="N15">
+        <v>-0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>-0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>103.3</v>
+      </c>
+      <c r="V15">
+        <v>0.1496017378711079</v>
+      </c>
+      <c r="W15">
+        <v>-0.148795871559633</v>
+      </c>
+      <c r="X15">
+        <v>0.06408243266290833</v>
+      </c>
+      <c r="Y15">
+        <v>-0.2128783042225414</v>
+      </c>
+      <c r="Z15">
+        <v>3.421400834172299</v>
+      </c>
+      <c r="AA15">
+        <v>0.05494031353372645</v>
+      </c>
+      <c r="AB15">
+        <v>0.05589223998187764</v>
+      </c>
+      <c r="AC15">
+        <v>-0.0009519264481511955</v>
+      </c>
+      <c r="AD15">
+        <v>449.2</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>449.2</v>
+      </c>
+      <c r="AG15">
+        <v>345.9</v>
+      </c>
+      <c r="AH15">
+        <v>0.3941388084583662</v>
+      </c>
+      <c r="AI15">
+        <v>0.6126568466993998</v>
+      </c>
+      <c r="AJ15">
+        <v>0.333751447317638</v>
+      </c>
+      <c r="AK15">
+        <v>0.5491347832989363</v>
+      </c>
+      <c r="AL15">
+        <v>25.7</v>
+      </c>
+      <c r="AM15">
+        <v>25.309</v>
+      </c>
+      <c r="AN15">
+        <v>6.694485842026826</v>
+      </c>
+      <c r="AO15">
+        <v>1.486381322957198</v>
+      </c>
+      <c r="AP15">
+        <v>5.154992548435171</v>
+      </c>
+      <c r="AQ15">
+        <v>1.509344501955826</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>West Bromwich Building Society (BDL:WBROM)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.118</v>
+      </c>
+      <c r="E16">
+        <v>0.29</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>36.5</v>
+      </c>
+      <c r="L16">
+        <v>0.2913008778930567</v>
+      </c>
+      <c r="M16">
+        <v>12.87</v>
+      </c>
+      <c r="N16">
+        <v>0.1772727272727273</v>
+      </c>
+      <c r="O16">
+        <v>0.3526027397260274</v>
+      </c>
+      <c r="P16">
+        <v>7.64</v>
+      </c>
+      <c r="Q16">
+        <v>0.1052341597796143</v>
+      </c>
+      <c r="R16">
+        <v>0.2093150684931507</v>
+      </c>
+      <c r="S16">
+        <v>5.230000000000001</v>
+      </c>
+      <c r="T16">
+        <v>0.4063714063714065</v>
+      </c>
+      <c r="U16">
+        <v>877.4</v>
+      </c>
+      <c r="V16">
+        <v>12.08539944903581</v>
+      </c>
+      <c r="W16">
+        <v>0.06828811973807297</v>
+      </c>
+      <c r="X16">
+        <v>0.2210216224625048</v>
+      </c>
+      <c r="Y16">
+        <v>-0.1527335027244318</v>
+      </c>
+      <c r="Z16">
+        <v>0.186264308012487</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.05281611167364651</v>
+      </c>
+      <c r="AC16">
+        <v>-0.05281611167364651</v>
+      </c>
+      <c r="AD16">
+        <v>1283.6</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>1283.6</v>
+      </c>
+      <c r="AG16">
+        <v>406.1999999999999</v>
+      </c>
+      <c r="AH16">
+        <v>0.9464680725556703</v>
+      </c>
+      <c r="AI16">
+        <v>0.6813525134030469</v>
+      </c>
+      <c r="AJ16">
+        <v>0.8483709273182957</v>
+      </c>
+      <c r="AK16">
+        <v>0.4035767511177347</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>Nationwide Building Society (LSE:NBS)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D6">
+      <c r="D17">
         <v>0.07780000000000001</v>
       </c>
-      <c r="E6">
+      <c r="E17">
         <v>0.161</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
         <v>1339</v>
       </c>
-      <c r="L6">
+      <c r="L17">
         <v>0.2299265059413421</v>
       </c>
-      <c r="M6">
+      <c r="M17">
         <v>230.5</v>
       </c>
-      <c r="N6">
+      <c r="N17">
         <v>0.1540672414945525</v>
       </c>
-      <c r="O6">
+      <c r="O17">
         <v>0.1721433905899925</v>
       </c>
-      <c r="P6">
+      <c r="P17">
         <v>230.5</v>
       </c>
-      <c r="Q6">
+      <c r="Q17">
         <v>0.1540672414945525</v>
       </c>
-      <c r="R6">
+      <c r="R17">
         <v>0.1721433905899925</v>
       </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
         <v>39067.1</v>
       </c>
-      <c r="V6">
+      <c r="V17">
         <v>26.11262616135285</v>
       </c>
-      <c r="W6">
+      <c r="W17">
         <v>0.06322778055851992</v>
       </c>
-      <c r="X6">
-        <v>0.4358097234694614</v>
-      </c>
-      <c r="Y6">
-        <v>-0.3725819429109415</v>
-      </c>
-      <c r="Z6">
+      <c r="X17">
+        <v>0.4356275850835172</v>
+      </c>
+      <c r="Y17">
+        <v>-0.3723998045249973</v>
+      </c>
+      <c r="Z17">
         <v>0.1828497508563821</v>
       </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.05389963745399518</v>
-      </c>
-      <c r="AC6">
-        <v>-0.05389963745399518</v>
-      </c>
-      <c r="AD6">
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0.05389529751051517</v>
+      </c>
+      <c r="AC17">
+        <v>-0.05389529751051517</v>
+      </c>
+      <c r="AD17">
         <v>61292.1</v>
       </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
         <v>61292.1</v>
       </c>
-      <c r="AG6">
+      <c r="AG17">
         <v>22225</v>
       </c>
-      <c r="AH6">
+      <c r="AH17">
         <v>0.9761722744082487</v>
       </c>
-      <c r="AI6">
+      <c r="AI17">
         <v>0.7097073382544506</v>
       </c>
-      <c r="AJ6">
+      <c r="AJ17">
         <v>0.9369295690334766</v>
       </c>
-      <c r="AK6">
+      <c r="AK17">
         <v>0.4699188504590298</v>
       </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>OSB Group Plc (LSE:OSB)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0.229</v>
+      </c>
+      <c r="E18">
+        <v>0.243</v>
+      </c>
+      <c r="F18">
+        <v>0.0858</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0.0001655815096044589</v>
+      </c>
+      <c r="J18">
+        <v>0.0001234021058217932</v>
+      </c>
+      <c r="K18">
+        <v>507.5</v>
+      </c>
+      <c r="L18">
+        <v>0.5084660855625689</v>
+      </c>
+      <c r="M18">
+        <v>352.6</v>
+      </c>
+      <c r="N18">
+        <v>0.1843370974487662</v>
+      </c>
+      <c r="O18">
+        <v>0.6947783251231527</v>
+      </c>
+      <c r="P18">
+        <v>171.2</v>
+      </c>
+      <c r="Q18">
+        <v>0.08950230029276453</v>
+      </c>
+      <c r="R18">
+        <v>0.3373399014778325</v>
+      </c>
+      <c r="S18">
+        <v>181.4</v>
+      </c>
+      <c r="T18">
+        <v>0.5144639818491209</v>
+      </c>
+      <c r="U18">
+        <v>4344</v>
+      </c>
+      <c r="V18">
+        <v>2.271016311166876</v>
+      </c>
+      <c r="W18">
+        <v>0.1933186042968155</v>
+      </c>
+      <c r="X18">
+        <v>0.0833883180369423</v>
+      </c>
+      <c r="Y18">
+        <v>0.1099302862598732</v>
+      </c>
+      <c r="Z18">
+        <v>0.1653428234097148</v>
+      </c>
+      <c r="AA18">
+        <v>2.040365259127968E-05</v>
+      </c>
+      <c r="AB18">
+        <v>0.05592908690447368</v>
+      </c>
+      <c r="AC18">
+        <v>-0.0559086832518824</v>
+      </c>
+      <c r="AD18">
+        <v>5251.1</v>
+      </c>
+      <c r="AE18">
+        <v>0.4486654763189479</v>
+      </c>
+      <c r="AF18">
+        <v>5251.548665476319</v>
+      </c>
+      <c r="AG18">
+        <v>907.548665476319</v>
+      </c>
+      <c r="AH18">
+        <v>0.7330113190585723</v>
+      </c>
+      <c r="AI18">
+        <v>0.6551865532806789</v>
+      </c>
+      <c r="AJ18">
+        <v>0.3217859822033905</v>
+      </c>
+      <c r="AK18">
+        <v>0.2471976235900695</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>20592.54901960784</v>
+      </c>
+      <c r="AP18">
+        <v>3559.014374416937</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>S&amp;U plc (LSE:SUS)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>-0.0308</v>
+      </c>
+      <c r="E19">
+        <v>-0.07969999999999999</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>24.2</v>
+      </c>
+      <c r="L19">
+        <v>0.2827102803738318</v>
+      </c>
+      <c r="M19">
+        <v>18.7</v>
+      </c>
+      <c r="N19">
+        <v>0.08534915563669557</v>
+      </c>
+      <c r="O19">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="P19">
+        <v>18.7</v>
+      </c>
+      <c r="Q19">
+        <v>0.08534915563669557</v>
+      </c>
+      <c r="R19">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0.003</v>
+      </c>
+      <c r="V19">
+        <v>1.369237790963031E-05</v>
+      </c>
+      <c r="W19">
+        <v>0.0821174075330845</v>
+      </c>
+      <c r="X19">
+        <v>0.07106729323539468</v>
+      </c>
+      <c r="Y19">
+        <v>0.01105011429768982</v>
+      </c>
+      <c r="Z19">
+        <v>0.1606308137189223</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.05636547067352377</v>
+      </c>
+      <c r="AC19">
+        <v>-0.05636547067352377</v>
+      </c>
+      <c r="AD19">
+        <v>308.6</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>308.6</v>
+      </c>
+      <c r="AG19">
+        <v>308.597</v>
+      </c>
+      <c r="AH19">
+        <v>0.5848019708167519</v>
+      </c>
+      <c r="AI19">
+        <v>0.5073154693407859</v>
+      </c>
+      <c r="AJ19">
+        <v>0.5847996103824733</v>
+      </c>
+      <c r="AK19">
+        <v>0.5073130395185247</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Paragon Banking Group PLC (LSE:PAG)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>0.0767</v>
+      </c>
+      <c r="E20">
+        <v>0.0786</v>
+      </c>
+      <c r="F20">
+        <v>0.0694</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>249.3</v>
+      </c>
+      <c r="L20">
+        <v>0.40629074315515</v>
+      </c>
+      <c r="M20">
+        <v>231.9</v>
+      </c>
+      <c r="N20">
+        <v>0.1233248245054244</v>
+      </c>
+      <c r="O20">
+        <v>0.9302045728038507</v>
+      </c>
+      <c r="P20">
+        <v>111.9</v>
+      </c>
+      <c r="Q20">
+        <v>0.05950861518825782</v>
+      </c>
+      <c r="R20">
+        <v>0.4488567990373045</v>
+      </c>
+      <c r="S20">
+        <v>120</v>
+      </c>
+      <c r="T20">
+        <v>0.517464424320828</v>
+      </c>
+      <c r="U20">
+        <v>3384.8</v>
+      </c>
+      <c r="V20">
+        <v>1.800042544139545</v>
+      </c>
+      <c r="W20">
+        <v>0.1448239804810038</v>
+      </c>
+      <c r="X20">
+        <v>0.06539741585318508</v>
+      </c>
+      <c r="Y20">
+        <v>0.07942656462781876</v>
+      </c>
+      <c r="Z20">
+        <v>0.3620913489909123</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.0567849062368642</v>
+      </c>
+      <c r="AC20">
+        <v>-0.0567849062368642</v>
+      </c>
+      <c r="AD20">
+        <v>1491.6</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>1491.6</v>
+      </c>
+      <c r="AG20">
+        <v>-1893.2</v>
+      </c>
+      <c r="AH20">
+        <v>0.4423487544483986</v>
+      </c>
+      <c r="AI20">
+        <v>0.4394555418066113</v>
+      </c>
+      <c r="AJ20">
+        <v>147.9062499999979</v>
+      </c>
+      <c r="AK20">
+        <v>-201.4042553191568</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Vanquis Banking Group plc (LSE:VANQ)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>-0.123</v>
+      </c>
+      <c r="G21">
+        <v>0.002498144941874845</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>-32.7</v>
+      </c>
+      <c r="L21">
+        <v>-0.08088053425674005</v>
+      </c>
+      <c r="M21">
+        <v>19.126</v>
+      </c>
+      <c r="N21">
+        <v>0.1348801128349788</v>
+      </c>
+      <c r="O21">
+        <v>-0.5848929663608563</v>
+      </c>
+      <c r="P21">
+        <v>19</v>
+      </c>
+      <c r="Q21">
+        <v>0.1339915373765867</v>
+      </c>
+      <c r="R21">
+        <v>-0.581039755351682</v>
+      </c>
+      <c r="S21">
+        <v>0.1260000000000012</v>
+      </c>
+      <c r="T21">
+        <v>0.00658789082923775</v>
+      </c>
+      <c r="U21">
+        <v>976.7</v>
+      </c>
+      <c r="V21">
+        <v>6.88787023977433</v>
+      </c>
+      <c r="W21">
+        <v>-0.0439279957012359</v>
+      </c>
+      <c r="X21">
+        <v>0.2624597992904533</v>
+      </c>
+      <c r="Y21">
+        <v>-0.3063877949916892</v>
+      </c>
+      <c r="Z21">
+        <v>0.1388154506437768</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0.05706411177647634</v>
+      </c>
+      <c r="AC21">
+        <v>-0.05706411177647634</v>
+      </c>
+      <c r="AD21">
+        <v>3144.7</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>3144.7</v>
+      </c>
+      <c r="AG21">
+        <v>2168</v>
+      </c>
+      <c r="AH21">
+        <v>0.9568537958314316</v>
+      </c>
+      <c r="AI21">
+        <v>0.8244933273904722</v>
+      </c>
+      <c r="AJ21">
+        <v>0.9386094034115507</v>
+      </c>
+      <c r="AK21">
+        <v>0.7640797913582857</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LendInvest plc (AIM:LINV)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>0.1578571428571429</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>-12.7</v>
+      </c>
+      <c r="L22">
+        <v>-0.4535714285714286</v>
+      </c>
+      <c r="M22">
+        <v>5.9</v>
+      </c>
+      <c r="N22">
+        <v>0.1428571428571429</v>
+      </c>
+      <c r="O22">
+        <v>-0.4645669291338583</v>
+      </c>
+      <c r="P22">
+        <v>5.9</v>
+      </c>
+      <c r="Q22">
+        <v>0.1428571428571429</v>
+      </c>
+      <c r="R22">
+        <v>-0.4645669291338583</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>96</v>
+      </c>
+      <c r="V22">
+        <v>2.324455205811138</v>
+      </c>
+      <c r="W22">
+        <v>-0.154126213592233</v>
+      </c>
+      <c r="X22">
+        <v>0.2398537948910681</v>
+      </c>
+      <c r="Y22">
+        <v>-0.3939800084833011</v>
+      </c>
+      <c r="Z22">
+        <v>0.02745905658527017</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0.05706957317324023</v>
+      </c>
+      <c r="AC22">
+        <v>-0.05706957317324023</v>
+      </c>
+      <c r="AD22">
+        <v>814.6</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>814.6</v>
+      </c>
+      <c r="AG22">
+        <v>718.6</v>
+      </c>
+      <c r="AH22">
+        <v>0.9517466993807688</v>
+      </c>
+      <c r="AI22">
+        <v>0.9150752639856212</v>
+      </c>
+      <c r="AJ22">
+        <v>0.9456507435188841</v>
+      </c>
+      <c r="AK22">
+        <v>0.9048098715688743</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Orchard Funding Group plc (AIM:ORCH)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>0.0594</v>
+      </c>
+      <c r="E23">
+        <v>-0.00683</v>
+      </c>
+      <c r="G23">
+        <v>0.01174377224199288</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>2.03</v>
+      </c>
+      <c r="L23">
+        <v>0.2408066429418742</v>
+      </c>
+      <c r="M23">
+        <v>0.548</v>
+      </c>
+      <c r="N23">
+        <v>0.07316421895861148</v>
+      </c>
+      <c r="O23">
+        <v>0.2699507389162562</v>
+      </c>
+      <c r="P23">
+        <v>0.548</v>
+      </c>
+      <c r="Q23">
+        <v>0.07316421895861148</v>
+      </c>
+      <c r="R23">
+        <v>0.2699507389162562</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>1.9</v>
+      </c>
+      <c r="V23">
+        <v>0.253671562082777</v>
+      </c>
+      <c r="W23">
+        <v>0.08903508771929823</v>
+      </c>
+      <c r="X23">
+        <v>0.1215747040080652</v>
+      </c>
+      <c r="Y23">
+        <v>-0.03253961628876696</v>
+      </c>
+      <c r="Z23">
+        <v>0.131267517907194</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0.05715352171028055</v>
+      </c>
+      <c r="AC23">
+        <v>-0.05715352171028055</v>
+      </c>
+      <c r="AD23">
+        <v>51.6</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>51.6</v>
+      </c>
+      <c r="AG23">
+        <v>49.7</v>
+      </c>
+      <c r="AH23">
+        <v>0.8732442037569809</v>
+      </c>
+      <c r="AI23">
+        <v>0.6798418972332015</v>
+      </c>
+      <c r="AJ23">
+        <v>0.8690330477356181</v>
+      </c>
+      <c r="AK23">
+        <v>0.6716216216216216</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>-0.008</v>
+      </c>
+      <c r="AQ23">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Distribution Finance Capital Holdings plc (AIM:DFCH)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>0.5429999999999999</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="L24">
+        <v>0.2142222222222222</v>
+      </c>
+      <c r="M24">
+        <v>0.259</v>
+      </c>
+      <c r="N24">
+        <v>0.003166259168704157</v>
+      </c>
+      <c r="O24">
+        <v>0.02686721991701245</v>
+      </c>
+      <c r="P24">
+        <v>-0</v>
+      </c>
+      <c r="Q24">
+        <v>-0</v>
+      </c>
+      <c r="R24">
+        <v>-0</v>
+      </c>
+      <c r="S24">
+        <v>0.259</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
+        <v>108.7</v>
+      </c>
+      <c r="V24">
+        <v>1.328850855745721</v>
+      </c>
+      <c r="W24">
+        <v>0.07675159235668791</v>
+      </c>
+      <c r="X24">
+        <v>0.05976596622475479</v>
+      </c>
+      <c r="Y24">
+        <v>0.01698562613193311</v>
+      </c>
+      <c r="Z24">
+        <v>0.6641086186540733</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0.05763366316844634</v>
+      </c>
+      <c r="AC24">
+        <v>-0.05763366316844634</v>
+      </c>
+      <c r="AD24">
+        <v>14.9</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>14.9</v>
+      </c>
+      <c r="AG24">
+        <v>-93.8</v>
+      </c>
+      <c r="AH24">
+        <v>0.1540847983453981</v>
+      </c>
+      <c r="AI24">
+        <v>0.09880636604774536</v>
+      </c>
+      <c r="AJ24">
+        <v>7.816666666666666</v>
+      </c>
+      <c r="AK24">
+        <v>-2.228028503562945</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Develop North PLC (LSE:DVNO)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>0.00279</v>
+      </c>
+      <c r="E25">
+        <v>0.0253</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>1.1</v>
+      </c>
+      <c r="L25">
+        <v>0.5978260869565217</v>
+      </c>
+      <c r="M25">
+        <v>3.16</v>
+      </c>
+      <c r="N25">
+        <v>0.1295081967213115</v>
+      </c>
+      <c r="O25">
+        <v>2.872727272727273</v>
+      </c>
+      <c r="P25">
+        <v>1.35</v>
+      </c>
+      <c r="Q25">
+        <v>0.05532786885245902</v>
+      </c>
+      <c r="R25">
+        <v>1.227272727272727</v>
+      </c>
+      <c r="S25">
+        <v>1.81</v>
+      </c>
+      <c r="T25">
+        <v>0.5727848101265822</v>
+      </c>
+      <c r="U25">
+        <v>0.304</v>
+      </c>
+      <c r="V25">
+        <v>0.01245901639344262</v>
+      </c>
+      <c r="W25">
+        <v>0.04135338345864661</v>
+      </c>
+      <c r="X25">
+        <v>0.05862743576723579</v>
+      </c>
+      <c r="Y25">
+        <v>-0.01727405230858917</v>
+      </c>
+      <c r="Z25">
+        <v>0.0630352860568688</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0.05777901486996211</v>
+      </c>
+      <c r="AC25">
+        <v>-0.05777901486996211</v>
+      </c>
+      <c r="AD25">
+        <v>1.43</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>1.43</v>
+      </c>
+      <c r="AG25">
+        <v>1.126</v>
+      </c>
+      <c r="AH25">
+        <v>0.05536198219125048</v>
+      </c>
+      <c r="AI25">
+        <v>0.05349794238683128</v>
+      </c>
+      <c r="AJ25">
+        <v>0.04411188592023819</v>
+      </c>
+      <c r="AK25">
+        <v>0.04260955119957617</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mortgage Advice Bureau (Holdings) plc (AIM:MAB1)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>0.14</v>
+      </c>
+      <c r="E26">
+        <v>-0.0421</v>
+      </c>
+      <c r="F26">
+        <v>0.131</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>13.6</v>
+      </c>
+      <c r="L26">
+        <v>0.04422764227642276</v>
+      </c>
+      <c r="M26">
+        <v>20.3</v>
+      </c>
+      <c r="N26">
+        <v>0.04586534116583823</v>
+      </c>
+      <c r="O26">
+        <v>1.492647058823529</v>
+      </c>
+      <c r="P26">
+        <v>20.3</v>
+      </c>
+      <c r="Q26">
+        <v>0.04586534116583823</v>
+      </c>
+      <c r="R26">
+        <v>1.492647058823529</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>31</v>
+      </c>
+      <c r="V26">
+        <v>0.07004066877541798</v>
+      </c>
+      <c r="W26">
+        <v>0.1583236321303841</v>
+      </c>
+      <c r="X26">
+        <v>0.05872239628061712</v>
+      </c>
+      <c r="Y26">
+        <v>0.09960123584976702</v>
+      </c>
+      <c r="Z26">
+        <v>13.31168831168831</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0.05789752737255677</v>
+      </c>
+      <c r="AC26">
+        <v>-0.05789752737255677</v>
+      </c>
+      <c r="AD26">
+        <v>30.5</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>30.5</v>
+      </c>
+      <c r="AG26">
+        <v>-0.5</v>
+      </c>
+      <c r="AH26">
+        <v>0.06446839991545128</v>
+      </c>
+      <c r="AI26">
+        <v>0.2526926263463132</v>
+      </c>
+      <c r="AJ26">
+        <v>-0.001130965844831486</v>
+      </c>
+      <c r="AK26">
+        <v>-0.005574136008918617</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-0.576</v>
+      </c>
+      <c r="AQ26">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Time Finance plc (AIM:TIME)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>0.009039999999999999</v>
+      </c>
+      <c r="E27">
+        <v>-0.06900000000000001</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>5.65</v>
+      </c>
+      <c r="L27">
+        <v>0.1342042755344418</v>
+      </c>
+      <c r="M27">
+        <v>-0</v>
+      </c>
+      <c r="N27">
+        <v>-0</v>
+      </c>
+      <c r="O27">
+        <v>-0</v>
+      </c>
+      <c r="P27">
+        <v>-0</v>
+      </c>
+      <c r="Q27">
+        <v>-0</v>
+      </c>
+      <c r="R27">
+        <v>-0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>2.02</v>
+      </c>
+      <c r="V27">
+        <v>0.02825174825174825</v>
+      </c>
+      <c r="W27">
+        <v>0.07395287958115183</v>
+      </c>
+      <c r="X27">
+        <v>0.05839410049473386</v>
+      </c>
+      <c r="Y27">
+        <v>0.01555877908641797</v>
+      </c>
+      <c r="Z27">
+        <v>0.9943316013226263</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0.05799249521001752</v>
+      </c>
+      <c r="AC27">
+        <v>-0.05799249521001752</v>
+      </c>
+      <c r="AD27">
+        <v>2.38</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>2.38</v>
+      </c>
+      <c r="AG27">
+        <v>0.3599999999999999</v>
+      </c>
+      <c r="AH27">
+        <v>0.03221440173253926</v>
+      </c>
+      <c r="AI27">
+        <v>0.02752081406105458</v>
+      </c>
+      <c r="AJ27">
+        <v>0.005009741163373224</v>
+      </c>
+      <c r="AK27">
+        <v>0.004262372720814585</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-0.122</v>
+      </c>
+      <c r="AQ27">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Funding Circle Holdings plc (LSE:FCH)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>0.032</v>
+      </c>
+      <c r="G28">
+        <v>-0.05440742302825811</v>
+      </c>
+      <c r="H28">
+        <v>-0.1408688317165753</v>
+      </c>
+      <c r="I28">
+        <v>-0.1185153943483762</v>
+      </c>
+      <c r="J28">
+        <v>-0.1185153943483762</v>
+      </c>
+      <c r="K28">
+        <v>-41.3</v>
+      </c>
+      <c r="L28">
+        <v>-0.1741881062842682</v>
+      </c>
+      <c r="M28">
+        <v>10.4</v>
+      </c>
+      <c r="N28">
+        <v>0.01900584795321637</v>
+      </c>
+      <c r="O28">
+        <v>-0.25181598062954</v>
+      </c>
+      <c r="P28">
+        <v>-0</v>
+      </c>
+      <c r="Q28">
+        <v>-0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>10.4</v>
+      </c>
+      <c r="T28">
+        <v>1</v>
+      </c>
+      <c r="U28">
+        <v>242.8</v>
+      </c>
+      <c r="V28">
+        <v>0.4437134502923977</v>
+      </c>
+      <c r="W28">
+        <v>-0.1230265117664581</v>
+      </c>
+      <c r="X28">
+        <v>0.05979841334723957</v>
+      </c>
+      <c r="Y28">
+        <v>-0.1828249251136977</v>
+      </c>
+      <c r="Z28">
+        <v>1.639695712309821</v>
+      </c>
+      <c r="AA28">
+        <v>-0.19432918395574</v>
+      </c>
+      <c r="AB28">
+        <v>0.05791988590211866</v>
+      </c>
+      <c r="AC28">
+        <v>-0.2522490698578587</v>
+      </c>
+      <c r="AD28">
+        <v>101.6</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>101.6</v>
+      </c>
+      <c r="AG28">
+        <v>-141.2</v>
+      </c>
+      <c r="AH28">
+        <v>0.156596794081381</v>
+      </c>
+      <c r="AI28">
+        <v>0.259846547314578</v>
+      </c>
+      <c r="AJ28">
+        <v>-0.3477832512315271</v>
+      </c>
+      <c r="AK28">
+        <v>-0.9527665317139005</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
+        <v>-3.6415770609319</v>
+      </c>
+      <c r="AP28">
+        <v>5.060931899641578</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Insig AI Plc (AIM:INSG)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K29">
+        <v>-21.2</v>
+      </c>
+      <c r="M29">
+        <v>-0</v>
+      </c>
+      <c r="N29">
+        <v>-0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>-0</v>
+      </c>
+      <c r="Q29">
+        <v>-0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0.303</v>
+      </c>
+      <c r="V29">
+        <v>0.01174418604651163</v>
+      </c>
+      <c r="W29">
+        <v>-1.184357541899441</v>
+      </c>
+      <c r="X29">
+        <v>0.05885887751755019</v>
+      </c>
+      <c r="Y29">
+        <v>-1.243216419416992</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>-0.3520309477756287</v>
+      </c>
+      <c r="AB29">
+        <v>0.05800473386788627</v>
+      </c>
+      <c r="AC29">
+        <v>-0.4100356816435149</v>
+      </c>
+      <c r="AD29">
+        <v>2.16</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>2.16</v>
+      </c>
+      <c r="AG29">
+        <v>1.857</v>
+      </c>
+      <c r="AH29">
+        <v>0.07725321888412018</v>
+      </c>
+      <c r="AI29">
+        <v>0.5983379501385041</v>
+      </c>
+      <c r="AJ29">
+        <v>0.06714394185920383</v>
+      </c>
+      <c r="AK29">
+        <v>0.5615361354702147</v>
+      </c>
+      <c r="AL29">
+        <v>0.181</v>
+      </c>
+      <c r="AM29">
+        <v>0.181</v>
+      </c>
+      <c r="AN29">
+        <v>-0.4909090909090909</v>
+      </c>
+      <c r="AO29">
+        <v>-15.0828729281768</v>
+      </c>
+      <c r="AP29">
+        <v>-0.4220454545454546</v>
+      </c>
+      <c r="AQ29">
+        <v>-15.0828729281768</v>
       </c>
     </row>
   </sheetData>
